--- a/artfynd/A 39408-2026 artfynd.xlsx
+++ b/artfynd/A 39408-2026 artfynd.xlsx
@@ -21216,14 +21216,14 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Minst tvååriga fruktkropp på kolad keloved. Rosa porlager med tydligt orange subiculum som reagerar körsbärsrött på koh.</t>
+          <t>Minst tvååriga fruktkropp på kolad keloved. Rosa porlager med tydligt orange subiculum som reagerar körsbärsrött på koh. Då den har en kraftig färg mot andra fynd kommer den skickas på mikroskopiering för att bekräftas.</t>
         </is>
       </c>
       <c r="AD185" t="b">
         <v>0</v>
       </c>
       <c r="AE185" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">

--- a/artfynd/A 39408-2026 artfynd.xlsx
+++ b/artfynd/A 39408-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ186"/>
+  <dimension ref="A1:AZ187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21128,51 +21128,48 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>136949417</v>
+        <v>136949446</v>
       </c>
       <c r="B185" t="n">
-        <v>92535</v>
+        <v>87367</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>260575</v>
+        <v>249254</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Laxrosa ticka</t>
+          <t>Mospindling</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Aurantiporus priscus</t>
+          <t>Cortinarius areni-silvae</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Niemelä &amp; al.</t>
+          <t>(Brandrud) Brandrud</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Dödåsen, Hjd</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>436999</v>
+        <v>437118</v>
       </c>
       <c r="R185" t="n">
-        <v>6851612</v>
+        <v>6852026</v>
       </c>
       <c r="S185" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21201,7 +21198,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -21211,12 +21208,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>Minst tvååriga fruktkropp på kolad keloved. Rosa porlager med tydligt orange subiculum som reagerar körsbärsrött på koh. Då den har en kraftig färg mot andra fynd kommer den skickas på mikroskopiering för att bekräftas.</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21237,55 +21229,63 @@
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949417</t>
+          <t>https://artportalen.se/Sighting/136949446</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>136944329</v>
+        <v>136949417</v>
       </c>
       <c r="B186" t="n">
-        <v>80370</v>
+        <v>92535</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>266179</v>
+        <v>260575</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Laxrosa ticka</t>
+        </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Lecidea subhumida</t>
+          <t>Aurantiporus priscus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Vain.</t>
+          <t>Niemelä &amp; al.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Dödåsen, Hjd</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>437364</v>
+        <v>436999</v>
       </c>
       <c r="R186" t="n">
-        <v>6851913</v>
+        <v>6851612</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -21324,7 +21324,12 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>Minst tvååriga fruktkropp på kolad keloved. Rosa porlager med tydligt orange subiculum som reagerar körsbärsrött på koh. Den kommer skickas på sekvensering.</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21333,22 +21338,130 @@
       <c r="AE186" t="b">
         <v>0</v>
       </c>
+      <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="b">
         <v>0</v>
       </c>
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136949417</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>136944329</v>
+      </c>
+      <c r="B187" t="n">
+        <v>80370</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Dödåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>437364</v>
+      </c>
+      <c r="R187" t="n">
+        <v>6851913</v>
+      </c>
+      <c r="S187" t="n">
+        <v>10</v>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT187" t="inlineStr"/>
+      <c r="AW187" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX187" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136944329</t>
         </is>
@@ -21541,6 +21654,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39408-2026 artfynd.xlsx
+++ b/artfynd/A 39408-2026 artfynd.xlsx
@@ -1329,7 +1329,7 @@
         <v>136944274</v>
       </c>
       <c r="B8" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>136944277</v>
       </c>
       <c r="B9" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136944289</v>
       </c>
       <c r="B10" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>136944294</v>
       </c>
       <c r="B11" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136944332</v>
       </c>
       <c r="B12" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136944383</v>
       </c>
       <c r="B13" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>136944393</v>
       </c>
       <c r="B14" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>136949427</v>
       </c>
       <c r="B16" t="n">
-        <v>79571</v>
+        <v>79575</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136944346</v>
       </c>
       <c r="B17" t="n">
-        <v>81458</v>
+        <v>81462</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>136944293</v>
       </c>
       <c r="B22" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>136944300</v>
       </c>
       <c r="B25" t="n">
-        <v>92166</v>
+        <v>92168</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>136949422</v>
       </c>
       <c r="B26" t="n">
-        <v>92166</v>
+        <v>92168</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>136949472</v>
       </c>
       <c r="B27" t="n">
-        <v>92166</v>
+        <v>92168</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>136944371</v>
       </c>
       <c r="B28" t="n">
-        <v>93436</v>
+        <v>93438</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>136944298</v>
       </c>
       <c r="B30" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>136949477</v>
       </c>
       <c r="B31" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>136949486</v>
       </c>
       <c r="B32" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>136944279</v>
       </c>
       <c r="B33" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>136944287</v>
       </c>
       <c r="B34" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>136944296</v>
       </c>
       <c r="B35" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>136944348</v>
       </c>
       <c r="B36" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>136944358</v>
       </c>
       <c r="B37" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>136944367</v>
       </c>
       <c r="B38" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>136944369</v>
       </c>
       <c r="B39" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>136949431</v>
       </c>
       <c r="B40" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>136949435</v>
       </c>
       <c r="B41" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>136949473</v>
       </c>
       <c r="B42" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>136949475</v>
       </c>
       <c r="B43" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         <v>136944295</v>
       </c>
       <c r="B44" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>136944353</v>
       </c>
       <c r="B45" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>136944292</v>
       </c>
       <c r="B46" t="n">
-        <v>93055</v>
+        <v>93057</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>136944352</v>
       </c>
       <c r="B47" t="n">
-        <v>93055</v>
+        <v>93057</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>136949453</v>
       </c>
       <c r="B48" t="n">
-        <v>93055</v>
+        <v>93057</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>136949483</v>
       </c>
       <c r="B49" t="n">
-        <v>93055</v>
+        <v>93057</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>136949423</v>
       </c>
       <c r="B50" t="n">
-        <v>91033</v>
+        <v>91035</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>136949445</v>
       </c>
       <c r="B51" t="n">
-        <v>91033</v>
+        <v>91035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>136944382</v>
       </c>
       <c r="B52" t="n">
-        <v>91467</v>
+        <v>91469</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>136944286</v>
       </c>
       <c r="B53" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>136944357</v>
       </c>
       <c r="B54" t="n">
-        <v>93395</v>
+        <v>93397</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>136944374</v>
       </c>
       <c r="B55" t="n">
-        <v>90895</v>
+        <v>90897</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>136944390</v>
       </c>
       <c r="B56" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>136944338</v>
       </c>
       <c r="B57" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>136944283</v>
       </c>
       <c r="B63" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>136944318</v>
       </c>
       <c r="B64" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>136944320</v>
       </c>
       <c r="B65" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>136944340</v>
       </c>
       <c r="B66" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>136944344</v>
       </c>
       <c r="B67" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>136944365</v>
       </c>
       <c r="B68" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>136944380</v>
       </c>
       <c r="B69" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>136949416</v>
       </c>
       <c r="B70" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>136949418</v>
       </c>
       <c r="B71" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>136949429</v>
       </c>
       <c r="B72" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>136949433</v>
       </c>
       <c r="B73" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>136949436</v>
       </c>
       <c r="B74" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>136949440</v>
       </c>
       <c r="B75" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>136949441</v>
       </c>
       <c r="B76" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>136949480</v>
       </c>
       <c r="B77" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>136949482</v>
       </c>
       <c r="B78" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>136944282</v>
       </c>
       <c r="B79" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>136944308</v>
       </c>
       <c r="B80" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>136944323</v>
       </c>
       <c r="B81" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>136944342</v>
       </c>
       <c r="B82" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>136944356</v>
       </c>
       <c r="B83" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>136944363</v>
       </c>
       <c r="B84" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>136944379</v>
       </c>
       <c r="B85" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>136944385</v>
       </c>
       <c r="B86" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>136944275</v>
       </c>
       <c r="B87" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>136944280</v>
       </c>
       <c r="B88" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>136944288</v>
       </c>
       <c r="B89" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>136944290</v>
       </c>
       <c r="B90" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>136944297</v>
       </c>
       <c r="B91" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>136944301</v>
       </c>
       <c r="B92" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>136944305</v>
       </c>
       <c r="B93" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>136944307</v>
       </c>
       <c r="B94" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>136944310</v>
       </c>
       <c r="B95" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         <v>136944311</v>
       </c>
       <c r="B96" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>136944315</v>
       </c>
       <c r="B97" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>136944316</v>
       </c>
       <c r="B98" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>136944330</v>
       </c>
       <c r="B99" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         <v>136944331</v>
       </c>
       <c r="B100" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>136944333</v>
       </c>
       <c r="B101" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>136944347</v>
       </c>
       <c r="B102" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11928,7 +11928,7 @@
         <v>136944349</v>
       </c>
       <c r="B103" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>136944359</v>
       </c>
       <c r="B104" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>136944361</v>
       </c>
       <c r="B105" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>136944362</v>
       </c>
       <c r="B106" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>136944366</v>
       </c>
       <c r="B107" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>136944370</v>
       </c>
       <c r="B108" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>136944372</v>
       </c>
       <c r="B109" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>136944381</v>
       </c>
       <c r="B110" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>136944384</v>
       </c>
       <c r="B111" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>136944389</v>
       </c>
       <c r="B112" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>136944391</v>
       </c>
       <c r="B113" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>136944394</v>
       </c>
       <c r="B114" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>136949419</v>
       </c>
       <c r="B115" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>136949421</v>
       </c>
       <c r="B116" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>136949424</v>
       </c>
       <c r="B117" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>136949438</v>
       </c>
       <c r="B118" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>136949442</v>
       </c>
       <c r="B119" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>136949443</v>
       </c>
       <c r="B120" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>136949444</v>
       </c>
       <c r="B121" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>136949449</v>
       </c>
       <c r="B122" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>136949450</v>
       </c>
       <c r="B123" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>136949451</v>
       </c>
       <c r="B124" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>136949452</v>
       </c>
       <c r="B125" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>136949465</v>
       </c>
       <c r="B126" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>136949467</v>
       </c>
       <c r="B127" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>136949468</v>
       </c>
       <c r="B128" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>136949470</v>
       </c>
       <c r="B129" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>136949471</v>
       </c>
       <c r="B130" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>136949476</v>
       </c>
       <c r="B131" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>136949484</v>
       </c>
       <c r="B132" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>136944309</v>
       </c>
       <c r="B146" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>136944303</v>
       </c>
       <c r="B147" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>136944314</v>
       </c>
       <c r="B148" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>136944355</v>
       </c>
       <c r="B149" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>136944373</v>
       </c>
       <c r="B150" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>136944378</v>
       </c>
       <c r="B151" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>136944387</v>
       </c>
       <c r="B152" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>136944392</v>
       </c>
       <c r="B153" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>136944281</v>
       </c>
       <c r="B154" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>136944302</v>
       </c>
       <c r="B155" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>136944317</v>
       </c>
       <c r="B156" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
         <v>136944328</v>
       </c>
       <c r="B157" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>136944337</v>
       </c>
       <c r="B158" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>136944339</v>
       </c>
       <c r="B159" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>136944345</v>
       </c>
       <c r="B160" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>136944350</v>
       </c>
       <c r="B161" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>136944351</v>
       </c>
       <c r="B162" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>136944368</v>
       </c>
       <c r="B163" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>136944375</v>
       </c>
       <c r="B164" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>136944377</v>
       </c>
       <c r="B165" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>136944388</v>
       </c>
       <c r="B166" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>136949420</v>
       </c>
       <c r="B167" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>136949425</v>
       </c>
       <c r="B168" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>136949428</v>
       </c>
       <c r="B169" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>136949432</v>
       </c>
       <c r="B170" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>136949437</v>
       </c>
       <c r="B171" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>136949439</v>
       </c>
       <c r="B172" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>136949448</v>
       </c>
       <c r="B173" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>136949456</v>
       </c>
       <c r="B174" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>136949461</v>
       </c>
       <c r="B175" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
         <v>136949462</v>
       </c>
       <c r="B176" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>136949464</v>
       </c>
       <c r="B177" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>136949466</v>
       </c>
       <c r="B178" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>136949469</v>
       </c>
       <c r="B179" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>136949474</v>
       </c>
       <c r="B180" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>136949478</v>
       </c>
       <c r="B181" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>136949479</v>
       </c>
       <c r="B182" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>136949481</v>
       </c>
       <c r="B183" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>136949454</v>
       </c>
       <c r="B184" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>136949446</v>
       </c>
       <c r="B185" t="n">
-        <v>87367</v>
+        <v>87369</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>136949417</v>
       </c>
       <c r="B186" t="n">
-        <v>92535</v>
+        <v>92537</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>136944329</v>
       </c>
       <c r="B187" t="n">
-        <v>80370</v>
+        <v>80374</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>

--- a/artfynd/A 39408-2026 artfynd.xlsx
+++ b/artfynd/A 39408-2026 artfynd.xlsx
@@ -1329,7 +1329,7 @@
         <v>136944274</v>
       </c>
       <c r="B8" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>136944277</v>
       </c>
       <c r="B9" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136944289</v>
       </c>
       <c r="B10" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>136944294</v>
       </c>
       <c r="B11" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136944332</v>
       </c>
       <c r="B12" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136944383</v>
       </c>
       <c r="B13" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>136944393</v>
       </c>
       <c r="B14" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>136949427</v>
       </c>
       <c r="B16" t="n">
-        <v>79575</v>
+        <v>79577</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136944346</v>
       </c>
       <c r="B17" t="n">
-        <v>81462</v>
+        <v>81464</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>136944293</v>
       </c>
       <c r="B22" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>136944300</v>
       </c>
       <c r="B25" t="n">
-        <v>92168</v>
+        <v>92170</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>136949422</v>
       </c>
       <c r="B26" t="n">
-        <v>92168</v>
+        <v>92170</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>136949472</v>
       </c>
       <c r="B27" t="n">
-        <v>92168</v>
+        <v>92170</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>136944371</v>
       </c>
       <c r="B28" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>136944298</v>
       </c>
       <c r="B30" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>136949477</v>
       </c>
       <c r="B31" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>136949486</v>
       </c>
       <c r="B32" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>136944279</v>
       </c>
       <c r="B33" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>136944287</v>
       </c>
       <c r="B34" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>136944296</v>
       </c>
       <c r="B35" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>136944348</v>
       </c>
       <c r="B36" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>136944358</v>
       </c>
       <c r="B37" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>136944367</v>
       </c>
       <c r="B38" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>136944369</v>
       </c>
       <c r="B39" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>136949431</v>
       </c>
       <c r="B40" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>136949435</v>
       </c>
       <c r="B41" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>136949473</v>
       </c>
       <c r="B42" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>136949475</v>
       </c>
       <c r="B43" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         <v>136944295</v>
       </c>
       <c r="B44" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>136944353</v>
       </c>
       <c r="B45" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>136944292</v>
       </c>
       <c r="B46" t="n">
-        <v>93057</v>
+        <v>93059</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>136944352</v>
       </c>
       <c r="B47" t="n">
-        <v>93057</v>
+        <v>93059</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>136949453</v>
       </c>
       <c r="B48" t="n">
-        <v>93057</v>
+        <v>93059</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>136949483</v>
       </c>
       <c r="B49" t="n">
-        <v>93057</v>
+        <v>93059</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>136949423</v>
       </c>
       <c r="B50" t="n">
-        <v>91035</v>
+        <v>91037</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>136949445</v>
       </c>
       <c r="B51" t="n">
-        <v>91035</v>
+        <v>91037</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>136944382</v>
       </c>
       <c r="B52" t="n">
-        <v>91469</v>
+        <v>91471</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>136944286</v>
       </c>
       <c r="B53" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>136944357</v>
       </c>
       <c r="B54" t="n">
-        <v>93397</v>
+        <v>93399</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>136944374</v>
       </c>
       <c r="B55" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>136944390</v>
       </c>
       <c r="B56" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>136944338</v>
       </c>
       <c r="B57" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>136944283</v>
       </c>
       <c r="B63" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>136944318</v>
       </c>
       <c r="B64" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>136944320</v>
       </c>
       <c r="B65" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>136944340</v>
       </c>
       <c r="B66" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>136944344</v>
       </c>
       <c r="B67" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>136944365</v>
       </c>
       <c r="B68" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>136944380</v>
       </c>
       <c r="B69" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>136949416</v>
       </c>
       <c r="B70" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>136949418</v>
       </c>
       <c r="B71" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>136949429</v>
       </c>
       <c r="B72" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>136949433</v>
       </c>
       <c r="B73" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>136949436</v>
       </c>
       <c r="B74" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>136949440</v>
       </c>
       <c r="B75" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>136949441</v>
       </c>
       <c r="B76" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>136949480</v>
       </c>
       <c r="B77" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>136949482</v>
       </c>
       <c r="B78" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>136944282</v>
       </c>
       <c r="B79" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>136944308</v>
       </c>
       <c r="B80" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>136944323</v>
       </c>
       <c r="B81" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>136944342</v>
       </c>
       <c r="B82" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>136944356</v>
       </c>
       <c r="B83" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>136944363</v>
       </c>
       <c r="B84" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>136944379</v>
       </c>
       <c r="B85" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>136944385</v>
       </c>
       <c r="B86" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>136944275</v>
       </c>
       <c r="B87" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>136944280</v>
       </c>
       <c r="B88" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>136944288</v>
       </c>
       <c r="B89" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>136944290</v>
       </c>
       <c r="B90" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>136944297</v>
       </c>
       <c r="B91" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>136944301</v>
       </c>
       <c r="B92" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>136944305</v>
       </c>
       <c r="B93" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>136944307</v>
       </c>
       <c r="B94" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>136944310</v>
       </c>
       <c r="B95" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         <v>136944311</v>
       </c>
       <c r="B96" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>136944315</v>
       </c>
       <c r="B97" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>136944316</v>
       </c>
       <c r="B98" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>136944330</v>
       </c>
       <c r="B99" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         <v>136944331</v>
       </c>
       <c r="B100" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>136944333</v>
       </c>
       <c r="B101" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>136944347</v>
       </c>
       <c r="B102" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11928,7 +11928,7 @@
         <v>136944349</v>
       </c>
       <c r="B103" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>136944359</v>
       </c>
       <c r="B104" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>136944361</v>
       </c>
       <c r="B105" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>136944362</v>
       </c>
       <c r="B106" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>136944366</v>
       </c>
       <c r="B107" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>136944370</v>
       </c>
       <c r="B108" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>136944372</v>
       </c>
       <c r="B109" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>136944381</v>
       </c>
       <c r="B110" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>136944384</v>
       </c>
       <c r="B111" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>136944389</v>
       </c>
       <c r="B112" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>136944391</v>
       </c>
       <c r="B113" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>136944394</v>
       </c>
       <c r="B114" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>136949419</v>
       </c>
       <c r="B115" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>136949421</v>
       </c>
       <c r="B116" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>136949424</v>
       </c>
       <c r="B117" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>136949438</v>
       </c>
       <c r="B118" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>136949442</v>
       </c>
       <c r="B119" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>136949443</v>
       </c>
       <c r="B120" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>136949444</v>
       </c>
       <c r="B121" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>136949449</v>
       </c>
       <c r="B122" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>136949450</v>
       </c>
       <c r="B123" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>136949451</v>
       </c>
       <c r="B124" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>136949452</v>
       </c>
       <c r="B125" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>136949465</v>
       </c>
       <c r="B126" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>136949467</v>
       </c>
       <c r="B127" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>136949468</v>
       </c>
       <c r="B128" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>136949470</v>
       </c>
       <c r="B129" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>136949471</v>
       </c>
       <c r="B130" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>136949476</v>
       </c>
       <c r="B131" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>136949484</v>
       </c>
       <c r="B132" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>136949426</v>
       </c>
       <c r="B135" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>136949430</v>
       </c>
       <c r="B136" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>136949457</v>
       </c>
       <c r="B137" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>136949459</v>
       </c>
       <c r="B138" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>136949460</v>
       </c>
       <c r="B139" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>136944309</v>
       </c>
       <c r="B146" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>136944303</v>
       </c>
       <c r="B147" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>136944314</v>
       </c>
       <c r="B148" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>136944355</v>
       </c>
       <c r="B149" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>136944373</v>
       </c>
       <c r="B150" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>136944378</v>
       </c>
       <c r="B151" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>136944387</v>
       </c>
       <c r="B152" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>136944392</v>
       </c>
       <c r="B153" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>136944281</v>
       </c>
       <c r="B154" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>136944302</v>
       </c>
       <c r="B155" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>136944317</v>
       </c>
       <c r="B156" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
         <v>136944328</v>
       </c>
       <c r="B157" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>136944337</v>
       </c>
       <c r="B158" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>136944339</v>
       </c>
       <c r="B159" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>136944345</v>
       </c>
       <c r="B160" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>136944350</v>
       </c>
       <c r="B161" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>136944351</v>
       </c>
       <c r="B162" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>136944368</v>
       </c>
       <c r="B163" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>136944375</v>
       </c>
       <c r="B164" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>136944377</v>
       </c>
       <c r="B165" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>136944388</v>
       </c>
       <c r="B166" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>136949420</v>
       </c>
       <c r="B167" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>136949425</v>
       </c>
       <c r="B168" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>136949428</v>
       </c>
       <c r="B169" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>136949432</v>
       </c>
       <c r="B170" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>136949437</v>
       </c>
       <c r="B171" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>136949439</v>
       </c>
       <c r="B172" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>136949448</v>
       </c>
       <c r="B173" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>136949456</v>
       </c>
       <c r="B174" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>136949461</v>
       </c>
       <c r="B175" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
         <v>136949462</v>
       </c>
       <c r="B176" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>136949464</v>
       </c>
       <c r="B177" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>136949466</v>
       </c>
       <c r="B178" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>136949469</v>
       </c>
       <c r="B179" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>136949474</v>
       </c>
       <c r="B180" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>136949478</v>
       </c>
       <c r="B181" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>136949479</v>
       </c>
       <c r="B182" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>136949481</v>
       </c>
       <c r="B183" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>136949454</v>
       </c>
       <c r="B184" t="n">
-        <v>93444</v>
+        <v>93446</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>136949446</v>
       </c>
       <c r="B185" t="n">
-        <v>87369</v>
+        <v>87371</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>136949417</v>
       </c>
       <c r="B186" t="n">
-        <v>92537</v>
+        <v>92539</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>136944329</v>
       </c>
       <c r="B187" t="n">
-        <v>80374</v>
+        <v>80376</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>

--- a/artfynd/A 39408-2026 artfynd.xlsx
+++ b/artfynd/A 39408-2026 artfynd.xlsx
@@ -1329,7 +1329,7 @@
         <v>136944274</v>
       </c>
       <c r="B8" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>136944277</v>
       </c>
       <c r="B9" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136944289</v>
       </c>
       <c r="B10" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>136944294</v>
       </c>
       <c r="B11" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136944332</v>
       </c>
       <c r="B12" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136944383</v>
       </c>
       <c r="B13" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>136944393</v>
       </c>
       <c r="B14" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>136949427</v>
       </c>
       <c r="B16" t="n">
-        <v>79577</v>
+        <v>79578</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136944346</v>
       </c>
       <c r="B17" t="n">
-        <v>81464</v>
+        <v>81465</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>136944293</v>
       </c>
       <c r="B22" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>136944300</v>
       </c>
       <c r="B25" t="n">
-        <v>92170</v>
+        <v>92171</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>136949422</v>
       </c>
       <c r="B26" t="n">
-        <v>92170</v>
+        <v>92171</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>136949472</v>
       </c>
       <c r="B27" t="n">
-        <v>92170</v>
+        <v>92171</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>136944371</v>
       </c>
       <c r="B28" t="n">
-        <v>93440</v>
+        <v>93441</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>136944298</v>
       </c>
       <c r="B30" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>136949477</v>
       </c>
       <c r="B31" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>136949486</v>
       </c>
       <c r="B32" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>136944279</v>
       </c>
       <c r="B33" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>136944287</v>
       </c>
       <c r="B34" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>136944296</v>
       </c>
       <c r="B35" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>136944348</v>
       </c>
       <c r="B36" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>136944358</v>
       </c>
       <c r="B37" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>136944367</v>
       </c>
       <c r="B38" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>136944369</v>
       </c>
       <c r="B39" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>136949431</v>
       </c>
       <c r="B40" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>136949435</v>
       </c>
       <c r="B41" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>136949473</v>
       </c>
       <c r="B42" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>136949475</v>
       </c>
       <c r="B43" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         <v>136944295</v>
       </c>
       <c r="B44" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>136944353</v>
       </c>
       <c r="B45" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>136944292</v>
       </c>
       <c r="B46" t="n">
-        <v>93059</v>
+        <v>93060</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>136944352</v>
       </c>
       <c r="B47" t="n">
-        <v>93059</v>
+        <v>93060</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>136949453</v>
       </c>
       <c r="B48" t="n">
-        <v>93059</v>
+        <v>93060</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>136949483</v>
       </c>
       <c r="B49" t="n">
-        <v>93059</v>
+        <v>93060</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>136949423</v>
       </c>
       <c r="B50" t="n">
-        <v>91037</v>
+        <v>91038</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>136949445</v>
       </c>
       <c r="B51" t="n">
-        <v>91037</v>
+        <v>91038</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>136944382</v>
       </c>
       <c r="B52" t="n">
-        <v>91471</v>
+        <v>91472</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>136944286</v>
       </c>
       <c r="B53" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>136944357</v>
       </c>
       <c r="B54" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>136944374</v>
       </c>
       <c r="B55" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>136944390</v>
       </c>
       <c r="B56" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>136944338</v>
       </c>
       <c r="B57" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>136944283</v>
       </c>
       <c r="B63" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>136944318</v>
       </c>
       <c r="B64" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>136944320</v>
       </c>
       <c r="B65" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>136944340</v>
       </c>
       <c r="B66" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>136944344</v>
       </c>
       <c r="B67" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>136944365</v>
       </c>
       <c r="B68" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>136944380</v>
       </c>
       <c r="B69" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>136949416</v>
       </c>
       <c r="B70" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>136949418</v>
       </c>
       <c r="B71" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>136949429</v>
       </c>
       <c r="B72" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>136949433</v>
       </c>
       <c r="B73" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>136949436</v>
       </c>
       <c r="B74" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>136949440</v>
       </c>
       <c r="B75" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>136949441</v>
       </c>
       <c r="B76" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>136949480</v>
       </c>
       <c r="B77" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>136949482</v>
       </c>
       <c r="B78" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>136944282</v>
       </c>
       <c r="B79" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>136944308</v>
       </c>
       <c r="B80" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>136944323</v>
       </c>
       <c r="B81" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>136944342</v>
       </c>
       <c r="B82" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>136944356</v>
       </c>
       <c r="B83" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>136944363</v>
       </c>
       <c r="B84" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>136944379</v>
       </c>
       <c r="B85" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>136944385</v>
       </c>
       <c r="B86" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>136944275</v>
       </c>
       <c r="B87" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>136944280</v>
       </c>
       <c r="B88" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>136944288</v>
       </c>
       <c r="B89" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>136944290</v>
       </c>
       <c r="B90" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>136944297</v>
       </c>
       <c r="B91" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>136944301</v>
       </c>
       <c r="B92" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>136944305</v>
       </c>
       <c r="B93" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>136944307</v>
       </c>
       <c r="B94" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>136944310</v>
       </c>
       <c r="B95" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         <v>136944311</v>
       </c>
       <c r="B96" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>136944315</v>
       </c>
       <c r="B97" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>136944316</v>
       </c>
       <c r="B98" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>136944330</v>
       </c>
       <c r="B99" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         <v>136944331</v>
       </c>
       <c r="B100" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>136944333</v>
       </c>
       <c r="B101" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>136944347</v>
       </c>
       <c r="B102" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11928,7 +11928,7 @@
         <v>136944349</v>
       </c>
       <c r="B103" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>136944359</v>
       </c>
       <c r="B104" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>136944361</v>
       </c>
       <c r="B105" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>136944362</v>
       </c>
       <c r="B106" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>136944366</v>
       </c>
       <c r="B107" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>136944370</v>
       </c>
       <c r="B108" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>136944372</v>
       </c>
       <c r="B109" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>136944381</v>
       </c>
       <c r="B110" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>136944384</v>
       </c>
       <c r="B111" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>136944389</v>
       </c>
       <c r="B112" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>136944391</v>
       </c>
       <c r="B113" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>136944394</v>
       </c>
       <c r="B114" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>136949419</v>
       </c>
       <c r="B115" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>136949421</v>
       </c>
       <c r="B116" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>136949424</v>
       </c>
       <c r="B117" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>136949438</v>
       </c>
       <c r="B118" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>136949442</v>
       </c>
       <c r="B119" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>136949443</v>
       </c>
       <c r="B120" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>136949444</v>
       </c>
       <c r="B121" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>136949449</v>
       </c>
       <c r="B122" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>136949450</v>
       </c>
       <c r="B123" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>136949451</v>
       </c>
       <c r="B124" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>136949452</v>
       </c>
       <c r="B125" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>136949465</v>
       </c>
       <c r="B126" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>136949467</v>
       </c>
       <c r="B127" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>136949468</v>
       </c>
       <c r="B128" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>136949470</v>
       </c>
       <c r="B129" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>136949471</v>
       </c>
       <c r="B130" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>136949476</v>
       </c>
       <c r="B131" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>136949484</v>
       </c>
       <c r="B132" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>136949426</v>
       </c>
       <c r="B135" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>136949430</v>
       </c>
       <c r="B136" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>136949457</v>
       </c>
       <c r="B137" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>136949459</v>
       </c>
       <c r="B138" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>136949460</v>
       </c>
       <c r="B139" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>136944309</v>
       </c>
       <c r="B146" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>136944303</v>
       </c>
       <c r="B147" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>136944314</v>
       </c>
       <c r="B148" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>136944355</v>
       </c>
       <c r="B149" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>136944373</v>
       </c>
       <c r="B150" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>136944378</v>
       </c>
       <c r="B151" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>136944387</v>
       </c>
       <c r="B152" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>136944392</v>
       </c>
       <c r="B153" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>136944281</v>
       </c>
       <c r="B154" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>136944302</v>
       </c>
       <c r="B155" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>136944317</v>
       </c>
       <c r="B156" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
         <v>136944328</v>
       </c>
       <c r="B157" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>136944337</v>
       </c>
       <c r="B158" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>136944339</v>
       </c>
       <c r="B159" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>136944345</v>
       </c>
       <c r="B160" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>136944350</v>
       </c>
       <c r="B161" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>136944351</v>
       </c>
       <c r="B162" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>136944368</v>
       </c>
       <c r="B163" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>136944375</v>
       </c>
       <c r="B164" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>136944377</v>
       </c>
       <c r="B165" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>136944388</v>
       </c>
       <c r="B166" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>136949420</v>
       </c>
       <c r="B167" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>136949425</v>
       </c>
       <c r="B168" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>136949428</v>
       </c>
       <c r="B169" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>136949432</v>
       </c>
       <c r="B170" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>136949437</v>
       </c>
       <c r="B171" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>136949439</v>
       </c>
       <c r="B172" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>136949448</v>
       </c>
       <c r="B173" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>136949456</v>
       </c>
       <c r="B174" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>136949461</v>
       </c>
       <c r="B175" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
         <v>136949462</v>
       </c>
       <c r="B176" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>136949464</v>
       </c>
       <c r="B177" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>136949466</v>
       </c>
       <c r="B178" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>136949469</v>
       </c>
       <c r="B179" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>136949474</v>
       </c>
       <c r="B180" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>136949478</v>
       </c>
       <c r="B181" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>136949479</v>
       </c>
       <c r="B182" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>136949481</v>
       </c>
       <c r="B183" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>136949454</v>
       </c>
       <c r="B184" t="n">
-        <v>93446</v>
+        <v>93447</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>136949446</v>
       </c>
       <c r="B185" t="n">
-        <v>87371</v>
+        <v>87372</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>136949417</v>
       </c>
       <c r="B186" t="n">
-        <v>92539</v>
+        <v>92540</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>136944329</v>
       </c>
       <c r="B187" t="n">
-        <v>80376</v>
+        <v>80377</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>

--- a/artfynd/A 39408-2026 artfynd.xlsx
+++ b/artfynd/A 39408-2026 artfynd.xlsx
@@ -2872,7 +2872,7 @@
         <v>136944293</v>
       </c>
       <c r="B22" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>136944300</v>
       </c>
       <c r="B25" t="n">
-        <v>92171</v>
+        <v>92177</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>136949422</v>
       </c>
       <c r="B26" t="n">
-        <v>92171</v>
+        <v>92177</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>136949472</v>
       </c>
       <c r="B27" t="n">
-        <v>92171</v>
+        <v>92177</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>136944371</v>
       </c>
       <c r="B28" t="n">
-        <v>93441</v>
+        <v>93447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>136944298</v>
       </c>
       <c r="B30" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>136949477</v>
       </c>
       <c r="B31" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>136949486</v>
       </c>
       <c r="B32" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>136944279</v>
       </c>
       <c r="B33" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>136944287</v>
       </c>
       <c r="B34" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>136944296</v>
       </c>
       <c r="B35" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>136944348</v>
       </c>
       <c r="B36" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>136944358</v>
       </c>
       <c r="B37" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>136944367</v>
       </c>
       <c r="B38" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>136944369</v>
       </c>
       <c r="B39" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>136949431</v>
       </c>
       <c r="B40" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>136949435</v>
       </c>
       <c r="B41" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>136949473</v>
       </c>
       <c r="B42" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>136949475</v>
       </c>
       <c r="B43" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         <v>136944295</v>
       </c>
       <c r="B44" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>136944353</v>
       </c>
       <c r="B45" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>136944292</v>
       </c>
       <c r="B46" t="n">
-        <v>93060</v>
+        <v>93066</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>136944352</v>
       </c>
       <c r="B47" t="n">
-        <v>93060</v>
+        <v>93066</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>136949453</v>
       </c>
       <c r="B48" t="n">
-        <v>93060</v>
+        <v>93066</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>136949483</v>
       </c>
       <c r="B49" t="n">
-        <v>93060</v>
+        <v>93066</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>136949423</v>
       </c>
       <c r="B50" t="n">
-        <v>91038</v>
+        <v>91044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>136949445</v>
       </c>
       <c r="B51" t="n">
-        <v>91038</v>
+        <v>91044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>136944382</v>
       </c>
       <c r="B52" t="n">
-        <v>91472</v>
+        <v>91478</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>136944286</v>
       </c>
       <c r="B53" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>136944357</v>
       </c>
       <c r="B54" t="n">
-        <v>93400</v>
+        <v>93406</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>136944374</v>
       </c>
       <c r="B55" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>136944309</v>
       </c>
       <c r="B146" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>136949454</v>
       </c>
       <c r="B184" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>136949446</v>
       </c>
       <c r="B185" t="n">
-        <v>87372</v>
+        <v>87378</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>136949417</v>
       </c>
       <c r="B186" t="n">
-        <v>92540</v>
+        <v>92546</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/A 39408-2026 artfynd.xlsx
+++ b/artfynd/A 39408-2026 artfynd.xlsx
@@ -1329,7 +1329,7 @@
         <v>136944274</v>
       </c>
       <c r="B8" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>136944277</v>
       </c>
       <c r="B9" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136944289</v>
       </c>
       <c r="B10" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>136944294</v>
       </c>
       <c r="B11" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136944332</v>
       </c>
       <c r="B12" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136944383</v>
       </c>
       <c r="B13" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>136944393</v>
       </c>
       <c r="B14" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>136949427</v>
       </c>
       <c r="B16" t="n">
-        <v>79578</v>
+        <v>79580</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136944346</v>
       </c>
       <c r="B17" t="n">
-        <v>81465</v>
+        <v>81467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>136944293</v>
       </c>
       <c r="B22" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>136944300</v>
       </c>
       <c r="B25" t="n">
-        <v>92177</v>
+        <v>92181</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>136949422</v>
       </c>
       <c r="B26" t="n">
-        <v>92177</v>
+        <v>92181</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>136949472</v>
       </c>
       <c r="B27" t="n">
-        <v>92177</v>
+        <v>92181</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>136944371</v>
       </c>
       <c r="B28" t="n">
-        <v>93447</v>
+        <v>93451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>136944298</v>
       </c>
       <c r="B30" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>136949477</v>
       </c>
       <c r="B31" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>136949486</v>
       </c>
       <c r="B32" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>136944279</v>
       </c>
       <c r="B33" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>136944287</v>
       </c>
       <c r="B34" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>136944296</v>
       </c>
       <c r="B35" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>136944348</v>
       </c>
       <c r="B36" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>136944358</v>
       </c>
       <c r="B37" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>136944367</v>
       </c>
       <c r="B38" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>136944369</v>
       </c>
       <c r="B39" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>136949431</v>
       </c>
       <c r="B40" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>136949435</v>
       </c>
       <c r="B41" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>136949473</v>
       </c>
       <c r="B42" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>136949475</v>
       </c>
       <c r="B43" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         <v>136944295</v>
       </c>
       <c r="B44" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>136944353</v>
       </c>
       <c r="B45" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>136944292</v>
       </c>
       <c r="B46" t="n">
-        <v>93066</v>
+        <v>93070</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>136944352</v>
       </c>
       <c r="B47" t="n">
-        <v>93066</v>
+        <v>93070</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>136949453</v>
       </c>
       <c r="B48" t="n">
-        <v>93066</v>
+        <v>93070</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>136949483</v>
       </c>
       <c r="B49" t="n">
-        <v>93066</v>
+        <v>93070</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>136949423</v>
       </c>
       <c r="B50" t="n">
-        <v>91044</v>
+        <v>91048</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>136949445</v>
       </c>
       <c r="B51" t="n">
-        <v>91044</v>
+        <v>91048</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>136944382</v>
       </c>
       <c r="B52" t="n">
-        <v>91478</v>
+        <v>91482</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>136944286</v>
       </c>
       <c r="B53" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>136944357</v>
       </c>
       <c r="B54" t="n">
-        <v>93406</v>
+        <v>93410</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>136944374</v>
       </c>
       <c r="B55" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>136944390</v>
       </c>
       <c r="B56" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>136944338</v>
       </c>
       <c r="B57" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>136944283</v>
       </c>
       <c r="B63" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>136944318</v>
       </c>
       <c r="B64" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>136944320</v>
       </c>
       <c r="B65" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>136944340</v>
       </c>
       <c r="B66" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>136944344</v>
       </c>
       <c r="B67" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>136944365</v>
       </c>
       <c r="B68" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>136944380</v>
       </c>
       <c r="B69" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>136949416</v>
       </c>
       <c r="B70" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>136949418</v>
       </c>
       <c r="B71" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>136949429</v>
       </c>
       <c r="B72" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>136949433</v>
       </c>
       <c r="B73" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>136949436</v>
       </c>
       <c r="B74" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>136949440</v>
       </c>
       <c r="B75" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>136949441</v>
       </c>
       <c r="B76" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>136949480</v>
       </c>
       <c r="B77" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>136949482</v>
       </c>
       <c r="B78" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>136944282</v>
       </c>
       <c r="B79" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>136944308</v>
       </c>
       <c r="B80" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>136944323</v>
       </c>
       <c r="B81" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>136944342</v>
       </c>
       <c r="B82" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>136944356</v>
       </c>
       <c r="B83" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>136944363</v>
       </c>
       <c r="B84" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>136944379</v>
       </c>
       <c r="B85" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>136944385</v>
       </c>
       <c r="B86" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>136944275</v>
       </c>
       <c r="B87" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>136944280</v>
       </c>
       <c r="B88" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>136944288</v>
       </c>
       <c r="B89" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>136944290</v>
       </c>
       <c r="B90" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>136944297</v>
       </c>
       <c r="B91" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>136944301</v>
       </c>
       <c r="B92" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>136944305</v>
       </c>
       <c r="B93" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>136944307</v>
       </c>
       <c r="B94" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>136944310</v>
       </c>
       <c r="B95" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         <v>136944311</v>
       </c>
       <c r="B96" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>136944315</v>
       </c>
       <c r="B97" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>136944316</v>
       </c>
       <c r="B98" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>136944330</v>
       </c>
       <c r="B99" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         <v>136944331</v>
       </c>
       <c r="B100" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>136944333</v>
       </c>
       <c r="B101" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>136944347</v>
       </c>
       <c r="B102" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11928,7 +11928,7 @@
         <v>136944349</v>
       </c>
       <c r="B103" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>136944359</v>
       </c>
       <c r="B104" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>136944361</v>
       </c>
       <c r="B105" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>136944362</v>
       </c>
       <c r="B106" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>136944366</v>
       </c>
       <c r="B107" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>136944370</v>
       </c>
       <c r="B108" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>136944372</v>
       </c>
       <c r="B109" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>136944381</v>
       </c>
       <c r="B110" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>136944384</v>
       </c>
       <c r="B111" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>136944389</v>
       </c>
       <c r="B112" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>136944391</v>
       </c>
       <c r="B113" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>136944394</v>
       </c>
       <c r="B114" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>136949419</v>
       </c>
       <c r="B115" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>136949421</v>
       </c>
       <c r="B116" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>136949424</v>
       </c>
       <c r="B117" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>136949438</v>
       </c>
       <c r="B118" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>136949442</v>
       </c>
       <c r="B119" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>136949443</v>
       </c>
       <c r="B120" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>136949444</v>
       </c>
       <c r="B121" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>136949449</v>
       </c>
       <c r="B122" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>136949450</v>
       </c>
       <c r="B123" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>136949451</v>
       </c>
       <c r="B124" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>136949452</v>
       </c>
       <c r="B125" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>136949465</v>
       </c>
       <c r="B126" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>136949467</v>
       </c>
       <c r="B127" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>136949468</v>
       </c>
       <c r="B128" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>136949470</v>
       </c>
       <c r="B129" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>136949471</v>
       </c>
       <c r="B130" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>136949476</v>
       </c>
       <c r="B131" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>136949484</v>
       </c>
       <c r="B132" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>136949426</v>
       </c>
       <c r="B135" t="n">
-        <v>78483</v>
+        <v>78485</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>136949430</v>
       </c>
       <c r="B136" t="n">
-        <v>78483</v>
+        <v>78485</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>136949457</v>
       </c>
       <c r="B137" t="n">
-        <v>78483</v>
+        <v>78485</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>136949459</v>
       </c>
       <c r="B138" t="n">
-        <v>78483</v>
+        <v>78485</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>136949460</v>
       </c>
       <c r="B139" t="n">
-        <v>78483</v>
+        <v>78485</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>136944309</v>
       </c>
       <c r="B146" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>136944303</v>
       </c>
       <c r="B147" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>136944314</v>
       </c>
       <c r="B148" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>136944355</v>
       </c>
       <c r="B149" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>136944373</v>
       </c>
       <c r="B150" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>136944378</v>
       </c>
       <c r="B151" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>136944387</v>
       </c>
       <c r="B152" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>136944392</v>
       </c>
       <c r="B153" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>136944281</v>
       </c>
       <c r="B154" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>136944302</v>
       </c>
       <c r="B155" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>136944317</v>
       </c>
       <c r="B156" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
         <v>136944328</v>
       </c>
       <c r="B157" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>136944337</v>
       </c>
       <c r="B158" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>136944339</v>
       </c>
       <c r="B159" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>136944345</v>
       </c>
       <c r="B160" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>136944350</v>
       </c>
       <c r="B161" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>136944351</v>
       </c>
       <c r="B162" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>136944368</v>
       </c>
       <c r="B163" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>136944375</v>
       </c>
       <c r="B164" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>136944377</v>
       </c>
       <c r="B165" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>136944388</v>
       </c>
       <c r="B166" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>136949420</v>
       </c>
       <c r="B167" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>136949425</v>
       </c>
       <c r="B168" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>136949428</v>
       </c>
       <c r="B169" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>136949432</v>
       </c>
       <c r="B170" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>136949437</v>
       </c>
       <c r="B171" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>136949439</v>
       </c>
       <c r="B172" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>136949448</v>
       </c>
       <c r="B173" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>136949456</v>
       </c>
       <c r="B174" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>136949461</v>
       </c>
       <c r="B175" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
         <v>136949462</v>
       </c>
       <c r="B176" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>136949464</v>
       </c>
       <c r="B177" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>136949466</v>
       </c>
       <c r="B178" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>136949469</v>
       </c>
       <c r="B179" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>136949474</v>
       </c>
       <c r="B180" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>136949478</v>
       </c>
       <c r="B181" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>136949479</v>
       </c>
       <c r="B182" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>136949481</v>
       </c>
       <c r="B183" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>136949454</v>
       </c>
       <c r="B184" t="n">
-        <v>93453</v>
+        <v>93457</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>136949446</v>
       </c>
       <c r="B185" t="n">
-        <v>87378</v>
+        <v>87382</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>136949417</v>
       </c>
       <c r="B186" t="n">
-        <v>92546</v>
+        <v>92550</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>136944329</v>
       </c>
       <c r="B187" t="n">
-        <v>80377</v>
+        <v>80379</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>

--- a/artfynd/A 39408-2026 artfynd.xlsx
+++ b/artfynd/A 39408-2026 artfynd.xlsx
@@ -16758,7 +16758,7 @@
         <v>136944309</v>
       </c>
       <c r="B146" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>

--- a/artfynd/A 39408-2026 artfynd.xlsx
+++ b/artfynd/A 39408-2026 artfynd.xlsx
@@ -1329,7 +1329,7 @@
         <v>136944274</v>
       </c>
       <c r="B8" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>136944277</v>
       </c>
       <c r="B9" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136944289</v>
       </c>
       <c r="B10" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>136944294</v>
       </c>
       <c r="B11" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136944332</v>
       </c>
       <c r="B12" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136944383</v>
       </c>
       <c r="B13" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>136944393</v>
       </c>
       <c r="B14" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>136949427</v>
       </c>
       <c r="B16" t="n">
-        <v>79580</v>
+        <v>79583</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136944346</v>
       </c>
       <c r="B17" t="n">
-        <v>81467</v>
+        <v>81457</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>136944293</v>
       </c>
       <c r="B22" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>136944300</v>
       </c>
       <c r="B25" t="n">
-        <v>92181</v>
+        <v>92183</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>136949422</v>
       </c>
       <c r="B26" t="n">
-        <v>92181</v>
+        <v>92183</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>136949472</v>
       </c>
       <c r="B27" t="n">
-        <v>92181</v>
+        <v>92183</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>136944371</v>
       </c>
       <c r="B28" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>136944298</v>
       </c>
       <c r="B30" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>136949477</v>
       </c>
       <c r="B31" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>136949486</v>
       </c>
       <c r="B32" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>136944279</v>
       </c>
       <c r="B33" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>136944287</v>
       </c>
       <c r="B34" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>136944296</v>
       </c>
       <c r="B35" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>136944348</v>
       </c>
       <c r="B36" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>136944358</v>
       </c>
       <c r="B37" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>136944367</v>
       </c>
       <c r="B38" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>136944369</v>
       </c>
       <c r="B39" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>136949431</v>
       </c>
       <c r="B40" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>136949435</v>
       </c>
       <c r="B41" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>136949473</v>
       </c>
       <c r="B42" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>136949475</v>
       </c>
       <c r="B43" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         <v>136944295</v>
       </c>
       <c r="B44" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>136944353</v>
       </c>
       <c r="B45" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>136944292</v>
       </c>
       <c r="B46" t="n">
-        <v>93070</v>
+        <v>93072</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>136944352</v>
       </c>
       <c r="B47" t="n">
-        <v>93070</v>
+        <v>93072</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>136949453</v>
       </c>
       <c r="B48" t="n">
-        <v>93070</v>
+        <v>93072</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>136949483</v>
       </c>
       <c r="B49" t="n">
-        <v>93070</v>
+        <v>93072</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>136949423</v>
       </c>
       <c r="B50" t="n">
-        <v>91048</v>
+        <v>91050</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>136949445</v>
       </c>
       <c r="B51" t="n">
-        <v>91048</v>
+        <v>91050</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>136944382</v>
       </c>
       <c r="B52" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>136944286</v>
       </c>
       <c r="B53" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>136944357</v>
       </c>
       <c r="B54" t="n">
-        <v>93410</v>
+        <v>93412</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>136944374</v>
       </c>
       <c r="B55" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>136944390</v>
       </c>
       <c r="B56" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>136944338</v>
       </c>
       <c r="B57" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>136944283</v>
       </c>
       <c r="B63" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>136944318</v>
       </c>
       <c r="B64" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>136944320</v>
       </c>
       <c r="B65" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>136944340</v>
       </c>
       <c r="B66" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>136944344</v>
       </c>
       <c r="B67" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>136944365</v>
       </c>
       <c r="B68" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>136944380</v>
       </c>
       <c r="B69" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>136949416</v>
       </c>
       <c r="B70" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>136949418</v>
       </c>
       <c r="B71" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>136949429</v>
       </c>
       <c r="B72" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>136949433</v>
       </c>
       <c r="B73" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>136949436</v>
       </c>
       <c r="B74" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>136949440</v>
       </c>
       <c r="B75" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>136949441</v>
       </c>
       <c r="B76" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>136949480</v>
       </c>
       <c r="B77" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>136949482</v>
       </c>
       <c r="B78" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>136944282</v>
       </c>
       <c r="B79" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>136944308</v>
       </c>
       <c r="B80" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>136944323</v>
       </c>
       <c r="B81" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>136944342</v>
       </c>
       <c r="B82" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>136944356</v>
       </c>
       <c r="B83" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>136944363</v>
       </c>
       <c r="B84" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>136944379</v>
       </c>
       <c r="B85" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>136944385</v>
       </c>
       <c r="B86" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>136944275</v>
       </c>
       <c r="B87" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>136944280</v>
       </c>
       <c r="B88" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>136944288</v>
       </c>
       <c r="B89" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>136944290</v>
       </c>
       <c r="B90" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>136944297</v>
       </c>
       <c r="B91" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>136944301</v>
       </c>
       <c r="B92" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>136944305</v>
       </c>
       <c r="B93" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>136944307</v>
       </c>
       <c r="B94" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>136944310</v>
       </c>
       <c r="B95" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         <v>136944311</v>
       </c>
       <c r="B96" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>136944315</v>
       </c>
       <c r="B97" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>136944316</v>
       </c>
       <c r="B98" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>136944330</v>
       </c>
       <c r="B99" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         <v>136944331</v>
       </c>
       <c r="B100" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>136944333</v>
       </c>
       <c r="B101" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>136944347</v>
       </c>
       <c r="B102" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11928,7 +11928,7 @@
         <v>136944349</v>
       </c>
       <c r="B103" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>136944359</v>
       </c>
       <c r="B104" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>136944361</v>
       </c>
       <c r="B105" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>136944362</v>
       </c>
       <c r="B106" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>136944366</v>
       </c>
       <c r="B107" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>136944370</v>
       </c>
       <c r="B108" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>136944372</v>
       </c>
       <c r="B109" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>136944381</v>
       </c>
       <c r="B110" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>136944384</v>
       </c>
       <c r="B111" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>136944389</v>
       </c>
       <c r="B112" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>136944391</v>
       </c>
       <c r="B113" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>136944394</v>
       </c>
       <c r="B114" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>136949419</v>
       </c>
       <c r="B115" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>136949421</v>
       </c>
       <c r="B116" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>136949424</v>
       </c>
       <c r="B117" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>136949438</v>
       </c>
       <c r="B118" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>136949442</v>
       </c>
       <c r="B119" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>136949443</v>
       </c>
       <c r="B120" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>136949444</v>
       </c>
       <c r="B121" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>136949449</v>
       </c>
       <c r="B122" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>136949450</v>
       </c>
       <c r="B123" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>136949451</v>
       </c>
       <c r="B124" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>136949452</v>
       </c>
       <c r="B125" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>136949465</v>
       </c>
       <c r="B126" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>136949467</v>
       </c>
       <c r="B127" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>136949468</v>
       </c>
       <c r="B128" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>136949470</v>
       </c>
       <c r="B129" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>136949471</v>
       </c>
       <c r="B130" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>136949476</v>
       </c>
       <c r="B131" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>136949484</v>
       </c>
       <c r="B132" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>136949426</v>
       </c>
       <c r="B135" t="n">
-        <v>78485</v>
+        <v>78488</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>136949430</v>
       </c>
       <c r="B136" t="n">
-        <v>78485</v>
+        <v>78488</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>136949457</v>
       </c>
       <c r="B137" t="n">
-        <v>78485</v>
+        <v>78488</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>136949459</v>
       </c>
       <c r="B138" t="n">
-        <v>78485</v>
+        <v>78488</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>136949460</v>
       </c>
       <c r="B139" t="n">
-        <v>78485</v>
+        <v>78488</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>136944309</v>
       </c>
       <c r="B146" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>136944303</v>
       </c>
       <c r="B147" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>136944314</v>
       </c>
       <c r="B148" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>136944355</v>
       </c>
       <c r="B149" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>136944373</v>
       </c>
       <c r="B150" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>136944378</v>
       </c>
       <c r="B151" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>136944387</v>
       </c>
       <c r="B152" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>136944392</v>
       </c>
       <c r="B153" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>136944281</v>
       </c>
       <c r="B154" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>136944302</v>
       </c>
       <c r="B155" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>136944317</v>
       </c>
       <c r="B156" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
         <v>136944328</v>
       </c>
       <c r="B157" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>136944337</v>
       </c>
       <c r="B158" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>136944339</v>
       </c>
       <c r="B159" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>136944345</v>
       </c>
       <c r="B160" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>136944350</v>
       </c>
       <c r="B161" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>136944351</v>
       </c>
       <c r="B162" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>136944368</v>
       </c>
       <c r="B163" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>136944375</v>
       </c>
       <c r="B164" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>136944377</v>
       </c>
       <c r="B165" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>136944388</v>
       </c>
       <c r="B166" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>136949420</v>
       </c>
       <c r="B167" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>136949425</v>
       </c>
       <c r="B168" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>136949428</v>
       </c>
       <c r="B169" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>136949432</v>
       </c>
       <c r="B170" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>136949437</v>
       </c>
       <c r="B171" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>136949439</v>
       </c>
       <c r="B172" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>136949448</v>
       </c>
       <c r="B173" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>136949456</v>
       </c>
       <c r="B174" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>136949461</v>
       </c>
       <c r="B175" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
         <v>136949462</v>
       </c>
       <c r="B176" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>136949464</v>
       </c>
       <c r="B177" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>136949466</v>
       </c>
       <c r="B178" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>136949469</v>
       </c>
       <c r="B179" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>136949474</v>
       </c>
       <c r="B180" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>136949478</v>
       </c>
       <c r="B181" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>136949479</v>
       </c>
       <c r="B182" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>136949481</v>
       </c>
       <c r="B183" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>136949454</v>
       </c>
       <c r="B184" t="n">
-        <v>93457</v>
+        <v>93459</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>136949446</v>
       </c>
       <c r="B185" t="n">
-        <v>87382</v>
+        <v>87384</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>136949417</v>
       </c>
       <c r="B186" t="n">
-        <v>92550</v>
+        <v>92552</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>136944329</v>
       </c>
       <c r="B187" t="n">
-        <v>80379</v>
+        <v>80382</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>

--- a/artfynd/A 39408-2026 artfynd.xlsx
+++ b/artfynd/A 39408-2026 artfynd.xlsx
@@ -1329,7 +1329,7 @@
         <v>136944274</v>
       </c>
       <c r="B8" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>136944277</v>
       </c>
       <c r="B9" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136944289</v>
       </c>
       <c r="B10" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>136944294</v>
       </c>
       <c r="B11" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136944332</v>
       </c>
       <c r="B12" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136944383</v>
       </c>
       <c r="B13" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>136944393</v>
       </c>
       <c r="B14" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>136949427</v>
       </c>
       <c r="B16" t="n">
-        <v>79583</v>
+        <v>79596</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136944346</v>
       </c>
       <c r="B17" t="n">
-        <v>81457</v>
+        <v>81470</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>136944293</v>
       </c>
       <c r="B22" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>136944300</v>
       </c>
       <c r="B25" t="n">
-        <v>92183</v>
+        <v>92196</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>136949422</v>
       </c>
       <c r="B26" t="n">
-        <v>92183</v>
+        <v>92196</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>136949472</v>
       </c>
       <c r="B27" t="n">
-        <v>92183</v>
+        <v>92196</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>136944371</v>
       </c>
       <c r="B28" t="n">
-        <v>93453</v>
+        <v>93466</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>136944298</v>
       </c>
       <c r="B30" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>136949477</v>
       </c>
       <c r="B31" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>136949486</v>
       </c>
       <c r="B32" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>136944279</v>
       </c>
       <c r="B33" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>136944287</v>
       </c>
       <c r="B34" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>136944296</v>
       </c>
       <c r="B35" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>136944348</v>
       </c>
       <c r="B36" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>136944358</v>
       </c>
       <c r="B37" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>136944367</v>
       </c>
       <c r="B38" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>136944369</v>
       </c>
       <c r="B39" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>136949431</v>
       </c>
       <c r="B40" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>136949435</v>
       </c>
       <c r="B41" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>136949473</v>
       </c>
       <c r="B42" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>136949475</v>
       </c>
       <c r="B43" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         <v>136944295</v>
       </c>
       <c r="B44" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>136944353</v>
       </c>
       <c r="B45" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>136944292</v>
       </c>
       <c r="B46" t="n">
-        <v>93072</v>
+        <v>93085</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>136944352</v>
       </c>
       <c r="B47" t="n">
-        <v>93072</v>
+        <v>93085</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>136949453</v>
       </c>
       <c r="B48" t="n">
-        <v>93072</v>
+        <v>93085</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>136949483</v>
       </c>
       <c r="B49" t="n">
-        <v>93072</v>
+        <v>93085</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>136949423</v>
       </c>
       <c r="B50" t="n">
-        <v>91050</v>
+        <v>91063</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>136949445</v>
       </c>
       <c r="B51" t="n">
-        <v>91050</v>
+        <v>91063</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>136944382</v>
       </c>
       <c r="B52" t="n">
-        <v>91484</v>
+        <v>91497</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>136944286</v>
       </c>
       <c r="B53" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>136944357</v>
       </c>
       <c r="B54" t="n">
-        <v>93412</v>
+        <v>93425</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>136944374</v>
       </c>
       <c r="B55" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>136944390</v>
       </c>
       <c r="B56" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>136944338</v>
       </c>
       <c r="B57" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>136944283</v>
       </c>
       <c r="B63" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>136944318</v>
       </c>
       <c r="B64" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>136944320</v>
       </c>
       <c r="B65" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>136944340</v>
       </c>
       <c r="B66" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>136944344</v>
       </c>
       <c r="B67" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>136944365</v>
       </c>
       <c r="B68" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>136944380</v>
       </c>
       <c r="B69" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>136949416</v>
       </c>
       <c r="B70" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>136949418</v>
       </c>
       <c r="B71" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>136949429</v>
       </c>
       <c r="B72" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>136949433</v>
       </c>
       <c r="B73" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>136949436</v>
       </c>
       <c r="B74" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>136949440</v>
       </c>
       <c r="B75" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>136949441</v>
       </c>
       <c r="B76" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>136949480</v>
       </c>
       <c r="B77" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>136949482</v>
       </c>
       <c r="B78" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>136944282</v>
       </c>
       <c r="B79" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>136944308</v>
       </c>
       <c r="B80" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>136944323</v>
       </c>
       <c r="B81" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>136944342</v>
       </c>
       <c r="B82" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>136944356</v>
       </c>
       <c r="B83" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>136944363</v>
       </c>
       <c r="B84" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>136944379</v>
       </c>
       <c r="B85" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>136944385</v>
       </c>
       <c r="B86" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>136944275</v>
       </c>
       <c r="B87" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>136944280</v>
       </c>
       <c r="B88" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>136944288</v>
       </c>
       <c r="B89" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>136944290</v>
       </c>
       <c r="B90" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>136944297</v>
       </c>
       <c r="B91" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>136944301</v>
       </c>
       <c r="B92" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>136944305</v>
       </c>
       <c r="B93" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>136944307</v>
       </c>
       <c r="B94" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>136944310</v>
       </c>
       <c r="B95" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         <v>136944311</v>
       </c>
       <c r="B96" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>136944315</v>
       </c>
       <c r="B97" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>136944316</v>
       </c>
       <c r="B98" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>136944330</v>
       </c>
       <c r="B99" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         <v>136944331</v>
       </c>
       <c r="B100" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>136944333</v>
       </c>
       <c r="B101" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>136944347</v>
       </c>
       <c r="B102" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11928,7 +11928,7 @@
         <v>136944349</v>
       </c>
       <c r="B103" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>136944359</v>
       </c>
       <c r="B104" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>136944361</v>
       </c>
       <c r="B105" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>136944362</v>
       </c>
       <c r="B106" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>136944366</v>
       </c>
       <c r="B107" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>136944370</v>
       </c>
       <c r="B108" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>136944372</v>
       </c>
       <c r="B109" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>136944381</v>
       </c>
       <c r="B110" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>136944384</v>
       </c>
       <c r="B111" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>136944389</v>
       </c>
       <c r="B112" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>136944391</v>
       </c>
       <c r="B113" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>136944394</v>
       </c>
       <c r="B114" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>136949419</v>
       </c>
       <c r="B115" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>136949421</v>
       </c>
       <c r="B116" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>136949424</v>
       </c>
       <c r="B117" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>136949438</v>
       </c>
       <c r="B118" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>136949442</v>
       </c>
       <c r="B119" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>136949443</v>
       </c>
       <c r="B120" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>136949444</v>
       </c>
       <c r="B121" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>136949449</v>
       </c>
       <c r="B122" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>136949450</v>
       </c>
       <c r="B123" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>136949451</v>
       </c>
       <c r="B124" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>136949452</v>
       </c>
       <c r="B125" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>136949465</v>
       </c>
       <c r="B126" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>136949467</v>
       </c>
       <c r="B127" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>136949468</v>
       </c>
       <c r="B128" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>136949470</v>
       </c>
       <c r="B129" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>136949471</v>
       </c>
       <c r="B130" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>136949476</v>
       </c>
       <c r="B131" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>136949484</v>
       </c>
       <c r="B132" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>136949426</v>
       </c>
       <c r="B135" t="n">
-        <v>78488</v>
+        <v>78501</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>136949430</v>
       </c>
       <c r="B136" t="n">
-        <v>78488</v>
+        <v>78501</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>136949457</v>
       </c>
       <c r="B137" t="n">
-        <v>78488</v>
+        <v>78501</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>136949459</v>
       </c>
       <c r="B138" t="n">
-        <v>78488</v>
+        <v>78501</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>136949460</v>
       </c>
       <c r="B139" t="n">
-        <v>78488</v>
+        <v>78501</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>136944386</v>
       </c>
       <c r="B140" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>136944299</v>
       </c>
       <c r="B141" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16296,7 +16296,7 @@
         <v>136944334</v>
       </c>
       <c r="B142" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>136944336</v>
       </c>
       <c r="B143" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>136944376</v>
       </c>
       <c r="B144" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>136949455</v>
       </c>
       <c r="B145" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>136944309</v>
       </c>
       <c r="B146" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>136944303</v>
       </c>
       <c r="B147" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>136944314</v>
       </c>
       <c r="B148" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>136944355</v>
       </c>
       <c r="B149" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>136944373</v>
       </c>
       <c r="B150" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>136944378</v>
       </c>
       <c r="B151" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>136944387</v>
       </c>
       <c r="B152" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>136944392</v>
       </c>
       <c r="B153" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>136944281</v>
       </c>
       <c r="B154" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>136944302</v>
       </c>
       <c r="B155" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>136944317</v>
       </c>
       <c r="B156" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
         <v>136944328</v>
       </c>
       <c r="B157" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>136944337</v>
       </c>
       <c r="B158" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>136944339</v>
       </c>
       <c r="B159" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>136944345</v>
       </c>
       <c r="B160" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>136944350</v>
       </c>
       <c r="B161" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>136944351</v>
       </c>
       <c r="B162" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>136944368</v>
       </c>
       <c r="B163" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>136944375</v>
       </c>
       <c r="B164" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>136944377</v>
       </c>
       <c r="B165" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>136944388</v>
       </c>
       <c r="B166" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>136949420</v>
       </c>
       <c r="B167" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>136949425</v>
       </c>
       <c r="B168" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>136949428</v>
       </c>
       <c r="B169" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>136949432</v>
       </c>
       <c r="B170" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>136949437</v>
       </c>
       <c r="B171" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>136949439</v>
       </c>
       <c r="B172" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>136949448</v>
       </c>
       <c r="B173" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>136949456</v>
       </c>
       <c r="B174" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>136949461</v>
       </c>
       <c r="B175" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
         <v>136949462</v>
       </c>
       <c r="B176" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>136949464</v>
       </c>
       <c r="B177" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>136949466</v>
       </c>
       <c r="B178" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>136949469</v>
       </c>
       <c r="B179" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>136949474</v>
       </c>
       <c r="B180" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>136949478</v>
       </c>
       <c r="B181" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>136949479</v>
       </c>
       <c r="B182" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>136949481</v>
       </c>
       <c r="B183" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>136949454</v>
       </c>
       <c r="B184" t="n">
-        <v>93459</v>
+        <v>93472</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>136949446</v>
       </c>
       <c r="B185" t="n">
-        <v>87384</v>
+        <v>87397</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>136949417</v>
       </c>
       <c r="B186" t="n">
-        <v>92552</v>
+        <v>92565</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>136944329</v>
       </c>
       <c r="B187" t="n">
-        <v>80382</v>
+        <v>80395</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>

--- a/artfynd/A 39408-2026 artfynd.xlsx
+++ b/artfynd/A 39408-2026 artfynd.xlsx
@@ -1329,7 +1329,7 @@
         <v>136944274</v>
       </c>
       <c r="B8" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>136944277</v>
       </c>
       <c r="B9" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136944289</v>
       </c>
       <c r="B10" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>136944294</v>
       </c>
       <c r="B11" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136944332</v>
       </c>
       <c r="B12" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136944383</v>
       </c>
       <c r="B13" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>136944393</v>
       </c>
       <c r="B14" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>136949427</v>
       </c>
       <c r="B16" t="n">
-        <v>79596</v>
+        <v>79598</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136944346</v>
       </c>
       <c r="B17" t="n">
-        <v>81470</v>
+        <v>81472</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>136944293</v>
       </c>
       <c r="B22" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>136944300</v>
       </c>
       <c r="B25" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>136949422</v>
       </c>
       <c r="B26" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>136949472</v>
       </c>
       <c r="B27" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>136944371</v>
       </c>
       <c r="B28" t="n">
-        <v>93466</v>
+        <v>93467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         <v>136944298</v>
       </c>
       <c r="B30" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>136949477</v>
       </c>
       <c r="B31" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>136949486</v>
       </c>
       <c r="B32" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>136944279</v>
       </c>
       <c r="B33" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>136944287</v>
       </c>
       <c r="B34" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>136944296</v>
       </c>
       <c r="B35" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>136944348</v>
       </c>
       <c r="B36" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>136944358</v>
       </c>
       <c r="B37" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>136944367</v>
       </c>
       <c r="B38" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>136944369</v>
       </c>
       <c r="B39" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>136949431</v>
       </c>
       <c r="B40" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>136949435</v>
       </c>
       <c r="B41" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>136949473</v>
       </c>
       <c r="B42" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>136949475</v>
       </c>
       <c r="B43" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         <v>136944295</v>
       </c>
       <c r="B44" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>136944353</v>
       </c>
       <c r="B45" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>136944292</v>
       </c>
       <c r="B46" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>136944352</v>
       </c>
       <c r="B47" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>136949453</v>
       </c>
       <c r="B48" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>136949483</v>
       </c>
       <c r="B49" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>136949423</v>
       </c>
       <c r="B50" t="n">
-        <v>91063</v>
+        <v>91065</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>136949445</v>
       </c>
       <c r="B51" t="n">
-        <v>91063</v>
+        <v>91065</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>136944382</v>
       </c>
       <c r="B52" t="n">
-        <v>91497</v>
+        <v>91499</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>136944286</v>
       </c>
       <c r="B53" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>136944357</v>
       </c>
       <c r="B54" t="n">
-        <v>93425</v>
+        <v>93426</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>136944374</v>
       </c>
       <c r="B55" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
         <v>136944390</v>
       </c>
       <c r="B56" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>136944338</v>
       </c>
       <c r="B57" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>136944283</v>
       </c>
       <c r="B63" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>136944318</v>
       </c>
       <c r="B64" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>136944320</v>
       </c>
       <c r="B65" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>136944340</v>
       </c>
       <c r="B66" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>136944344</v>
       </c>
       <c r="B67" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>136944365</v>
       </c>
       <c r="B68" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         <v>136944380</v>
       </c>
       <c r="B69" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>136949416</v>
       </c>
       <c r="B70" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>136949418</v>
       </c>
       <c r="B71" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         <v>136949429</v>
       </c>
       <c r="B72" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>136949433</v>
       </c>
       <c r="B73" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>136949436</v>
       </c>
       <c r="B74" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>136949440</v>
       </c>
       <c r="B75" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>136949441</v>
       </c>
       <c r="B76" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>136949480</v>
       </c>
       <c r="B77" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>136949482</v>
       </c>
       <c r="B78" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>136944282</v>
       </c>
       <c r="B79" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>136944308</v>
       </c>
       <c r="B80" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>136944323</v>
       </c>
       <c r="B81" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>136944342</v>
       </c>
       <c r="B82" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>136944356</v>
       </c>
       <c r="B83" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>136944363</v>
       </c>
       <c r="B84" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>136944379</v>
       </c>
       <c r="B85" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>136944385</v>
       </c>
       <c r="B86" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>136944275</v>
       </c>
       <c r="B87" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>136944280</v>
       </c>
       <c r="B88" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>136944288</v>
       </c>
       <c r="B89" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>136944290</v>
       </c>
       <c r="B90" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>136944297</v>
       </c>
       <c r="B91" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>136944301</v>
       </c>
       <c r="B92" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>136944305</v>
       </c>
       <c r="B93" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>136944307</v>
       </c>
       <c r="B94" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>136944310</v>
       </c>
       <c r="B95" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         <v>136944311</v>
       </c>
       <c r="B96" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11256,7 +11256,7 @@
         <v>136944315</v>
       </c>
       <c r="B97" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11368,7 +11368,7 @@
         <v>136944316</v>
       </c>
       <c r="B98" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>136944330</v>
       </c>
       <c r="B99" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
         <v>136944331</v>
       </c>
       <c r="B100" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>136944333</v>
       </c>
       <c r="B101" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>136944347</v>
       </c>
       <c r="B102" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11928,7 +11928,7 @@
         <v>136944349</v>
       </c>
       <c r="B103" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>136944359</v>
       </c>
       <c r="B104" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>136944361</v>
       </c>
       <c r="B105" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>136944362</v>
       </c>
       <c r="B106" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>136944366</v>
       </c>
       <c r="B107" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>136944370</v>
       </c>
       <c r="B108" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>136944372</v>
       </c>
       <c r="B109" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>136944381</v>
       </c>
       <c r="B110" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>136944384</v>
       </c>
       <c r="B111" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>136944389</v>
       </c>
       <c r="B112" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>136944391</v>
       </c>
       <c r="B113" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>136944394</v>
       </c>
       <c r="B114" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13272,7 +13272,7 @@
         <v>136949419</v>
       </c>
       <c r="B115" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>136949421</v>
       </c>
       <c r="B116" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>136949424</v>
       </c>
       <c r="B117" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>136949438</v>
       </c>
       <c r="B118" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>136949442</v>
       </c>
       <c r="B119" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>136949443</v>
       </c>
       <c r="B120" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>136949444</v>
       </c>
       <c r="B121" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>136949449</v>
       </c>
       <c r="B122" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>136949450</v>
       </c>
       <c r="B123" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>136949451</v>
       </c>
       <c r="B124" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>136949452</v>
       </c>
       <c r="B125" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>136949465</v>
       </c>
       <c r="B126" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>136949467</v>
       </c>
       <c r="B127" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>136949468</v>
       </c>
       <c r="B128" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>136949470</v>
       </c>
       <c r="B129" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>136949471</v>
       </c>
       <c r="B130" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>136949476</v>
       </c>
       <c r="B131" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>136949484</v>
       </c>
       <c r="B132" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>136949426</v>
       </c>
       <c r="B135" t="n">
-        <v>78501</v>
+        <v>78503</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>136949430</v>
       </c>
       <c r="B136" t="n">
-        <v>78501</v>
+        <v>78503</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>136949457</v>
       </c>
       <c r="B137" t="n">
-        <v>78501</v>
+        <v>78503</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>136949459</v>
       </c>
       <c r="B138" t="n">
-        <v>78501</v>
+        <v>78503</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>136949460</v>
       </c>
       <c r="B139" t="n">
-        <v>78501</v>
+        <v>78503</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>136944386</v>
       </c>
       <c r="B140" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>136944299</v>
       </c>
       <c r="B141" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16296,7 +16296,7 @@
         <v>136944334</v>
       </c>
       <c r="B142" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>136944336</v>
       </c>
       <c r="B143" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>136944376</v>
       </c>
       <c r="B144" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>136949455</v>
       </c>
       <c r="B145" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>136944309</v>
       </c>
       <c r="B146" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>136944303</v>
       </c>
       <c r="B147" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>136944314</v>
       </c>
       <c r="B148" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>136944355</v>
       </c>
       <c r="B149" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>136944373</v>
       </c>
       <c r="B150" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>136944378</v>
       </c>
       <c r="B151" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>136944387</v>
       </c>
       <c r="B152" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>136944392</v>
       </c>
       <c r="B153" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>136944281</v>
       </c>
       <c r="B154" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>136944302</v>
       </c>
       <c r="B155" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>136944317</v>
       </c>
       <c r="B156" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
         <v>136944328</v>
       </c>
       <c r="B157" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>136944337</v>
       </c>
       <c r="B158" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>136944339</v>
       </c>
       <c r="B159" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>136944345</v>
       </c>
       <c r="B160" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>136944350</v>
       </c>
       <c r="B161" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>136944351</v>
       </c>
       <c r="B162" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>136944368</v>
       </c>
       <c r="B163" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>136944375</v>
       </c>
       <c r="B164" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>136944377</v>
       </c>
       <c r="B165" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>136944388</v>
       </c>
       <c r="B166" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>136949420</v>
       </c>
       <c r="B167" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>136949425</v>
       </c>
       <c r="B168" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>136949428</v>
       </c>
       <c r="B169" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>136949432</v>
       </c>
       <c r="B170" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>136949437</v>
       </c>
       <c r="B171" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>136949439</v>
       </c>
       <c r="B172" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>136949448</v>
       </c>
       <c r="B173" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>136949456</v>
       </c>
       <c r="B174" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>136949461</v>
       </c>
       <c r="B175" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20123,7 +20123,7 @@
         <v>136949462</v>
       </c>
       <c r="B176" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>136949464</v>
       </c>
       <c r="B177" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>136949466</v>
       </c>
       <c r="B178" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>136949469</v>
       </c>
       <c r="B179" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>136949474</v>
       </c>
       <c r="B180" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>136949478</v>
       </c>
       <c r="B181" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>136949479</v>
       </c>
       <c r="B182" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>136949481</v>
       </c>
       <c r="B183" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>136949454</v>
       </c>
       <c r="B184" t="n">
-        <v>93472</v>
+        <v>93473</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>136949446</v>
       </c>
       <c r="B185" t="n">
-        <v>87397</v>
+        <v>87399</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>136949417</v>
       </c>
       <c r="B186" t="n">
-        <v>92565</v>
+        <v>92567</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>136944329</v>
       </c>
       <c r="B187" t="n">
-        <v>80395</v>
+        <v>80397</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>

--- a/artfynd/A 39408-2026 artfynd.xlsx
+++ b/artfynd/A 39408-2026 artfynd.xlsx
@@ -16088,11 +16088,7 @@
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Dödåsen, Hjd</t>
@@ -16438,11 +16434,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Dödåsen, Hjd</t>
@@ -16667,11 +16659,7 @@
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Dödåsen, Hjd</t>

--- a/artfynd/A 39408-2026 artfynd.xlsx
+++ b/artfynd/A 39408-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ187"/>
+  <dimension ref="A1:AZ188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2872,7 +2872,7 @@
         <v>136944293</v>
       </c>
       <c r="B22" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2981,10 +2981,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>66498783</v>
+        <v>136949434</v>
       </c>
       <c r="B23" t="n">
-        <v>91962</v>
+        <v>93479</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2992,41 +2992,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2079</v>
+        <v>1968</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Dödåsen, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437209</v>
+        <v>437021</v>
       </c>
       <c r="R23" t="n">
-        <v>6851522</v>
+        <v>6851782</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3050,12 +3046,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2011-08-09</t>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2011-08-09</t>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3064,35 +3070,31 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>12101</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66498783</t>
+          <t>https://artportalen.se/Sighting/136949434</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>66498818</v>
+        <v>66498783</v>
       </c>
       <c r="B24" t="n">
         <v>91962</v>
@@ -3120,17 +3122,21 @@
           <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Dödåsen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436984</v>
+        <v>437209</v>
       </c>
       <c r="R24" t="n">
-        <v>6851518</v>
+        <v>6851522</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3176,7 +3182,7 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>12131</t>
+          <t>12101</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3187,22 +3193,22 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66498818</t>
+          <t>https://artportalen.se/Sighting/66498783</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136944300</v>
+        <v>66498818</v>
       </c>
       <c r="B25" t="n">
-        <v>92198</v>
+        <v>91962</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3234,13 +3240,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436905</v>
+        <v>436984</v>
       </c>
       <c r="R25" t="n">
-        <v>6851819</v>
+        <v>6851518</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3264,22 +3270,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:19</t>
+          <t>2011-08-09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:19</t>
+          <t>2011-08-09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3290,31 +3286,36 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>12131</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Mikael Gudrunsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944300</t>
+          <t>https://artportalen.se/Sighting/66498818</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136949422</v>
+        <v>136944300</v>
       </c>
       <c r="B26" t="n">
-        <v>92198</v>
+        <v>92201</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3346,13 +3347,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437069</v>
+        <v>436905</v>
       </c>
       <c r="R26" t="n">
-        <v>6851599</v>
+        <v>6851819</v>
       </c>
       <c r="S26" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3381,7 +3382,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3391,7 +3392,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3406,27 +3407,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949422</t>
+          <t>https://artportalen.se/Sighting/136944300</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136949472</v>
+        <v>136949422</v>
       </c>
       <c r="B27" t="n">
-        <v>92198</v>
+        <v>92201</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3458,13 +3459,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>437205</v>
+        <v>437069</v>
       </c>
       <c r="R27" t="n">
-        <v>6851517</v>
+        <v>6851599</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3493,7 +3494,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3503,7 +3504,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3529,16 +3530,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949472</t>
+          <t>https://artportalen.se/Sighting/136949422</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136944371</v>
+        <v>136949472</v>
       </c>
       <c r="B28" t="n">
-        <v>93467</v>
+        <v>92201</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3546,21 +3547,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3100</v>
+        <v>2079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3570,13 +3571,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>437192</v>
+        <v>437205</v>
       </c>
       <c r="R28" t="n">
-        <v>6851475</v>
+        <v>6851517</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3605,7 +3606,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3615,7 +3616,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3630,27 +3631,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944371</t>
+          <t>https://artportalen.se/Sighting/136949472</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>66498807</v>
+        <v>136944371</v>
       </c>
       <c r="B29" t="n">
-        <v>93191</v>
+        <v>93470</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3658,21 +3659,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3682,13 +3683,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>437015</v>
+        <v>437192</v>
       </c>
       <c r="R29" t="n">
-        <v>6851792</v>
+        <v>6851475</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3712,12 +3713,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2011-08-09</t>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2011-08-09</t>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3728,36 +3739,31 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>12122</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66498807</t>
+          <t>https://artportalen.se/Sighting/136944371</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136944298</v>
+        <v>66498807</v>
       </c>
       <c r="B30" t="n">
-        <v>93436</v>
+        <v>93191</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3789,13 +3795,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436814</v>
+        <v>437015</v>
       </c>
       <c r="R30" t="n">
-        <v>6851789</v>
+        <v>6851792</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3819,22 +3825,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:16</t>
+          <t>2011-08-09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:16</t>
+          <t>2011-08-09</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3845,31 +3841,36 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>12122</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944298</t>
+          <t>https://artportalen.se/Sighting/66498807</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136949477</v>
+        <v>136944298</v>
       </c>
       <c r="B31" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3901,13 +3902,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>437132</v>
+        <v>436814</v>
       </c>
       <c r="R31" t="n">
-        <v>6851558</v>
+        <v>6851789</v>
       </c>
       <c r="S31" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3936,7 +3937,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3946,7 +3947,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3961,27 +3962,27 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949477</t>
+          <t>https://artportalen.se/Sighting/136944298</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136949486</v>
+        <v>136949477</v>
       </c>
       <c r="B32" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4013,13 +4014,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436956</v>
+        <v>437132</v>
       </c>
       <c r="R32" t="n">
-        <v>6851496</v>
+        <v>6851558</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4048,7 +4049,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4058,7 +4059,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4084,16 +4085,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949486</t>
+          <t>https://artportalen.se/Sighting/136949477</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136944279</v>
+        <v>136949486</v>
       </c>
       <c r="B33" t="n">
-        <v>93442</v>
+        <v>93439</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4101,21 +4102,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4125,13 +4126,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436989</v>
+        <v>436956</v>
       </c>
       <c r="R33" t="n">
-        <v>6851621</v>
+        <v>6851496</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4160,7 +4161,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4170,7 +4171,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4185,27 +4186,27 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944279</t>
+          <t>https://artportalen.se/Sighting/136949486</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136944287</v>
+        <v>136944279</v>
       </c>
       <c r="B34" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4237,10 +4238,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436901</v>
+        <v>436989</v>
       </c>
       <c r="R34" t="n">
-        <v>6851679</v>
+        <v>6851621</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4272,7 +4273,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4282,7 +4283,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4308,16 +4309,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944287</t>
+          <t>https://artportalen.se/Sighting/136944279</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136944296</v>
+        <v>136944287</v>
       </c>
       <c r="B35" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4349,10 +4350,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436808</v>
+        <v>436901</v>
       </c>
       <c r="R35" t="n">
-        <v>6851765</v>
+        <v>6851679</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4384,7 +4385,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4394,7 +4395,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4420,16 +4421,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944296</t>
+          <t>https://artportalen.se/Sighting/136944287</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>136944348</v>
+        <v>136944296</v>
       </c>
       <c r="B36" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4461,10 +4462,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>437055</v>
+        <v>436808</v>
       </c>
       <c r="R36" t="n">
-        <v>6851836</v>
+        <v>6851765</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4496,7 +4497,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4506,7 +4507,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4532,16 +4533,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944348</t>
+          <t>https://artportalen.se/Sighting/136944296</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>136944358</v>
+        <v>136944348</v>
       </c>
       <c r="B37" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4573,10 +4574,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>437235</v>
+        <v>437055</v>
       </c>
       <c r="R37" t="n">
-        <v>6851634</v>
+        <v>6851836</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4608,7 +4609,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4618,12 +4619,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Under låga</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4649,16 +4645,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944358</t>
+          <t>https://artportalen.se/Sighting/136944348</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136944367</v>
+        <v>136944358</v>
       </c>
       <c r="B38" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4690,10 +4686,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>437307</v>
+        <v>437235</v>
       </c>
       <c r="R38" t="n">
-        <v>6851616</v>
+        <v>6851634</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4725,7 +4721,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4735,7 +4731,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Under låga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4761,16 +4762,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944367</t>
+          <t>https://artportalen.se/Sighting/136944358</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136944369</v>
+        <v>136944367</v>
       </c>
       <c r="B39" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,10 +4803,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>437275</v>
+        <v>437307</v>
       </c>
       <c r="R39" t="n">
-        <v>6851605</v>
+        <v>6851616</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4837,7 +4838,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4847,7 +4848,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4873,16 +4874,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944369</t>
+          <t>https://artportalen.se/Sighting/136944367</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136949431</v>
+        <v>136944369</v>
       </c>
       <c r="B40" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4914,10 +4915,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>437021</v>
+        <v>437275</v>
       </c>
       <c r="R40" t="n">
-        <v>6851750</v>
+        <v>6851605</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4949,7 +4950,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4959,7 +4960,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4974,27 +4975,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949431</t>
+          <t>https://artportalen.se/Sighting/136944369</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136949435</v>
+        <v>136949431</v>
       </c>
       <c r="B41" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5026,13 +5027,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>437023</v>
+        <v>437021</v>
       </c>
       <c r="R41" t="n">
-        <v>6851776</v>
+        <v>6851750</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5061,7 +5062,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5071,7 +5072,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5097,16 +5098,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949435</t>
+          <t>https://artportalen.se/Sighting/136949431</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>136949473</v>
+        <v>136949435</v>
       </c>
       <c r="B42" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5138,13 +5139,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>437205</v>
+        <v>437023</v>
       </c>
       <c r="R42" t="n">
-        <v>6851517</v>
+        <v>6851776</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5173,7 +5174,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5183,7 +5184,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5209,16 +5210,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949473</t>
+          <t>https://artportalen.se/Sighting/136949435</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>136949475</v>
+        <v>136949473</v>
       </c>
       <c r="B43" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5250,13 +5251,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>437141</v>
+        <v>437205</v>
       </c>
       <c r="R43" t="n">
-        <v>6851537</v>
+        <v>6851517</v>
       </c>
       <c r="S43" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5285,7 +5286,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5295,7 +5296,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5321,38 +5322,38 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949475</t>
+          <t>https://artportalen.se/Sighting/136949473</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>136944295</v>
+        <v>136949475</v>
       </c>
       <c r="B44" t="n">
-        <v>93446</v>
+        <v>93445</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5362,13 +5363,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436798</v>
+        <v>437141</v>
       </c>
       <c r="R44" t="n">
-        <v>6851764</v>
+        <v>6851537</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5397,7 +5398,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5407,12 +5408,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Under klen låga utan hänsyn</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5427,27 +5423,27 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944295</t>
+          <t>https://artportalen.se/Sighting/136949475</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>136944353</v>
+        <v>136944295</v>
       </c>
       <c r="B45" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5479,10 +5475,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>437219</v>
+        <v>436798</v>
       </c>
       <c r="R45" t="n">
-        <v>6851640</v>
+        <v>6851764</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5514,7 +5510,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5524,12 +5520,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Under låga utan hänsyn</t>
+          <t>Under klen låga utan hänsyn</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5555,38 +5551,38 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944353</t>
+          <t>https://artportalen.se/Sighting/136944295</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136944292</v>
+        <v>136944353</v>
       </c>
       <c r="B46" t="n">
-        <v>93087</v>
+        <v>93449</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4745</v>
+        <v>4365</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5596,10 +5592,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436808</v>
+        <v>437219</v>
       </c>
       <c r="R46" t="n">
-        <v>6851732</v>
+        <v>6851640</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5631,7 +5627,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5641,7 +5637,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Under låga utan hänsyn</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5667,16 +5668,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944292</t>
+          <t>https://artportalen.se/Sighting/136944353</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>136944352</v>
+        <v>136944292</v>
       </c>
       <c r="B47" t="n">
-        <v>93087</v>
+        <v>93090</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5708,7 +5709,7 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>437099</v>
+        <v>436808</v>
       </c>
       <c r="R47" t="n">
         <v>6851732</v>
@@ -5743,7 +5744,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5753,7 +5754,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5779,16 +5780,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944352</t>
+          <t>https://artportalen.se/Sighting/136944292</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>136949453</v>
+        <v>136944352</v>
       </c>
       <c r="B48" t="n">
-        <v>93087</v>
+        <v>93090</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5820,13 +5821,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>437404</v>
+        <v>437099</v>
       </c>
       <c r="R48" t="n">
-        <v>6851860</v>
+        <v>6851732</v>
       </c>
       <c r="S48" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5855,7 +5856,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5865,7 +5866,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5880,27 +5881,27 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949453</t>
+          <t>https://artportalen.se/Sighting/136944352</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>136949483</v>
+        <v>136949453</v>
       </c>
       <c r="B49" t="n">
-        <v>93087</v>
+        <v>93090</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5932,13 +5933,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>437041</v>
+        <v>437404</v>
       </c>
       <c r="R49" t="n">
-        <v>6851458</v>
+        <v>6851860</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5967,7 +5968,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5977,7 +5978,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6003,38 +6004,38 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949483</t>
+          <t>https://artportalen.se/Sighting/136949453</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>136949423</v>
+        <v>136949483</v>
       </c>
       <c r="B50" t="n">
-        <v>91065</v>
+        <v>93090</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5084</v>
+        <v>4745</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Storsporig dvärgpigg</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Mucronella bresadolae</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Quél.) Corner</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6044,13 +6045,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>437063</v>
+        <v>437041</v>
       </c>
       <c r="R50" t="n">
-        <v>6851605</v>
+        <v>6851458</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6079,7 +6080,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6089,7 +6090,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6115,16 +6116,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949423</t>
+          <t>https://artportalen.se/Sighting/136949483</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>136949445</v>
+        <v>136949423</v>
       </c>
       <c r="B51" t="n">
-        <v>91065</v>
+        <v>91068</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6156,13 +6157,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>437118</v>
+        <v>437063</v>
       </c>
       <c r="R51" t="n">
-        <v>6852067</v>
+        <v>6851605</v>
       </c>
       <c r="S51" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6191,7 +6192,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6201,7 +6202,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6227,38 +6228,38 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949445</t>
+          <t>https://artportalen.se/Sighting/136949423</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>136944382</v>
+        <v>136949445</v>
       </c>
       <c r="B52" t="n">
-        <v>91499</v>
+        <v>91068</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5685</v>
+        <v>5084</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Storsporig dvärgpigg</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Mucronella bresadolae</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Quél.) Corner</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6268,13 +6269,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>437128</v>
+        <v>437118</v>
       </c>
       <c r="R52" t="n">
-        <v>6851449</v>
+        <v>6852067</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6303,7 +6304,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6313,7 +6314,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6328,49 +6329,49 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944382</t>
+          <t>https://artportalen.se/Sighting/136949445</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>136944286</v>
+        <v>136944382</v>
       </c>
       <c r="B53" t="n">
-        <v>93480</v>
+        <v>91502</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5966</v>
+        <v>5685</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6380,10 +6381,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436871</v>
+        <v>437128</v>
       </c>
       <c r="R53" t="n">
-        <v>6851697</v>
+        <v>6851449</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6415,7 +6416,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6425,7 +6426,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6451,38 +6452,38 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944286</t>
+          <t>https://artportalen.se/Sighting/136944382</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>136944357</v>
+        <v>136944286</v>
       </c>
       <c r="B54" t="n">
-        <v>93426</v>
+        <v>93483</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6055</v>
+        <v>5966</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6492,10 +6493,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>437234</v>
+        <v>436871</v>
       </c>
       <c r="R54" t="n">
-        <v>6851637</v>
+        <v>6851697</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6527,7 +6528,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6537,12 +6538,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Under låga utan hänsyn</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6568,16 +6564,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944357</t>
+          <t>https://artportalen.se/Sighting/136944286</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>136944374</v>
+        <v>136944357</v>
       </c>
       <c r="B55" t="n">
-        <v>90927</v>
+        <v>93429</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6585,21 +6581,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6286</v>
+        <v>6055</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6609,10 +6605,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>437157</v>
+        <v>437234</v>
       </c>
       <c r="R55" t="n">
-        <v>6851503</v>
+        <v>6851637</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6644,7 +6640,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6654,7 +6650,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Under låga utan hänsyn</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6680,16 +6681,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944374</t>
+          <t>https://artportalen.se/Sighting/136944357</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>136944390</v>
+        <v>136944374</v>
       </c>
       <c r="B56" t="n">
-        <v>79503</v>
+        <v>90930</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6697,21 +6698,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6721,10 +6722,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>437269</v>
+        <v>437157</v>
       </c>
       <c r="R56" t="n">
-        <v>6851325</v>
+        <v>6851503</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6756,7 +6757,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6766,7 +6767,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6792,38 +6793,38 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944390</t>
+          <t>https://artportalen.se/Sighting/136944374</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>136944338</v>
+        <v>136944390</v>
       </c>
       <c r="B57" t="n">
-        <v>79527</v>
+        <v>79503</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6833,10 +6834,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>437174</v>
+        <v>437269</v>
       </c>
       <c r="R57" t="n">
-        <v>6851866</v>
+        <v>6851325</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6868,7 +6869,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6878,7 +6879,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6904,38 +6905,38 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944338</t>
+          <t>https://artportalen.se/Sighting/136944390</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>66498789</v>
+        <v>136944338</v>
       </c>
       <c r="B58" t="n">
-        <v>78730</v>
+        <v>79527</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6437</v>
+        <v>6434</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6945,13 +6946,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>437319</v>
+        <v>437174</v>
       </c>
       <c r="R58" t="n">
-        <v>6851608</v>
+        <v>6851866</v>
       </c>
       <c r="S58" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6975,12 +6976,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2011-08-09</t>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2011-08-09</t>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6991,33 +7002,28 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>12106</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66498789</t>
+          <t>https://artportalen.se/Sighting/136944338</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>66498792</v>
+        <v>66498789</v>
       </c>
       <c r="B59" t="n">
         <v>78730</v>
@@ -7052,10 +7058,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>437350</v>
+        <v>437319</v>
       </c>
       <c r="R59" t="n">
-        <v>6851669</v>
+        <v>6851608</v>
       </c>
       <c r="S59" t="n">
         <v>50</v>
@@ -7101,7 +7107,7 @@
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>12108</t>
+          <t>12106</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7118,13 +7124,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66498792</t>
+          <t>https://artportalen.se/Sighting/66498789</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>66498806</v>
+        <v>66498792</v>
       </c>
       <c r="B60" t="n">
         <v>78730</v>
@@ -7159,10 +7165,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437026</v>
+        <v>437350</v>
       </c>
       <c r="R60" t="n">
-        <v>6851819</v>
+        <v>6851669</v>
       </c>
       <c r="S60" t="n">
         <v>50</v>
@@ -7208,7 +7214,7 @@
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>12108</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7225,13 +7231,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66498806</t>
+          <t>https://artportalen.se/Sighting/66498792</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>66498812</v>
+        <v>66498806</v>
       </c>
       <c r="B61" t="n">
         <v>78730</v>
@@ -7266,10 +7272,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>437011</v>
+        <v>437026</v>
       </c>
       <c r="R61" t="n">
-        <v>6851737</v>
+        <v>6851819</v>
       </c>
       <c r="S61" t="n">
         <v>50</v>
@@ -7315,7 +7321,7 @@
       </c>
       <c r="AR61" t="inlineStr">
         <is>
-          <t>12126</t>
+          <t>12121</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7332,13 +7338,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66498812</t>
+          <t>https://artportalen.se/Sighting/66498806</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>66498815</v>
+        <v>66498812</v>
       </c>
       <c r="B62" t="n">
         <v>78730</v>
@@ -7373,10 +7379,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>437021</v>
+        <v>437011</v>
       </c>
       <c r="R62" t="n">
-        <v>6851615</v>
+        <v>6851737</v>
       </c>
       <c r="S62" t="n">
         <v>50</v>
@@ -7422,7 +7428,7 @@
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>12128</t>
+          <t>12126</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7439,16 +7445,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66498815</t>
+          <t>https://artportalen.se/Sighting/66498812</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>136944283</v>
+        <v>66498815</v>
       </c>
       <c r="B63" t="n">
-        <v>78906</v>
+        <v>78730</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7480,13 +7486,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>436909</v>
+        <v>437021</v>
       </c>
       <c r="R63" t="n">
-        <v>6851658</v>
+        <v>6851615</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7510,22 +7516,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:56</t>
+          <t>2011-08-09</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:56</t>
+          <t>2011-08-09</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7536,28 +7532,33 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>12128</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944283</t>
+          <t>https://artportalen.se/Sighting/66498815</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>136944318</v>
+        <v>136944283</v>
       </c>
       <c r="B64" t="n">
         <v>78906</v>
@@ -7592,10 +7593,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>437021</v>
+        <v>436909</v>
       </c>
       <c r="R64" t="n">
-        <v>6852088</v>
+        <v>6851658</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7627,7 +7628,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7637,7 +7638,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7663,13 +7664,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944318</t>
+          <t>https://artportalen.se/Sighting/136944283</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>136944320</v>
+        <v>136944318</v>
       </c>
       <c r="B65" t="n">
         <v>78906</v>
@@ -7704,10 +7705,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>437085</v>
+        <v>437021</v>
       </c>
       <c r="R65" t="n">
-        <v>6852022</v>
+        <v>6852088</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7739,7 +7740,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7749,7 +7750,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7775,13 +7776,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944320</t>
+          <t>https://artportalen.se/Sighting/136944318</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>136944340</v>
+        <v>136944320</v>
       </c>
       <c r="B66" t="n">
         <v>78906</v>
@@ -7816,10 +7817,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>437165</v>
+        <v>437085</v>
       </c>
       <c r="R66" t="n">
-        <v>6851882</v>
+        <v>6852022</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7851,7 +7852,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7861,7 +7862,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7887,13 +7888,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944340</t>
+          <t>https://artportalen.se/Sighting/136944320</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>136944344</v>
+        <v>136944340</v>
       </c>
       <c r="B67" t="n">
         <v>78906</v>
@@ -7928,10 +7929,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>437082</v>
+        <v>437165</v>
       </c>
       <c r="R67" t="n">
-        <v>6851914</v>
+        <v>6851882</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7963,7 +7964,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7973,7 +7974,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7999,13 +8000,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944344</t>
+          <t>https://artportalen.se/Sighting/136944340</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>136944365</v>
+        <v>136944344</v>
       </c>
       <c r="B68" t="n">
         <v>78906</v>
@@ -8040,10 +8041,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>437316</v>
+        <v>437082</v>
       </c>
       <c r="R68" t="n">
-        <v>6851630</v>
+        <v>6851914</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8075,7 +8076,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8085,7 +8086,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8111,13 +8112,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944365</t>
+          <t>https://artportalen.se/Sighting/136944344</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>136944380</v>
+        <v>136944365</v>
       </c>
       <c r="B69" t="n">
         <v>78906</v>
@@ -8152,10 +8153,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>437058</v>
+        <v>437316</v>
       </c>
       <c r="R69" t="n">
-        <v>6851469</v>
+        <v>6851630</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8187,7 +8188,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8197,7 +8198,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8223,13 +8224,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944380</t>
+          <t>https://artportalen.se/Sighting/136944365</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>136949416</v>
+        <v>136944380</v>
       </c>
       <c r="B70" t="n">
         <v>78906</v>
@@ -8264,13 +8265,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>437007</v>
+        <v>437058</v>
       </c>
       <c r="R70" t="n">
-        <v>6851582</v>
+        <v>6851469</v>
       </c>
       <c r="S70" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8299,7 +8300,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8309,7 +8310,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8324,24 +8325,24 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949416</t>
+          <t>https://artportalen.se/Sighting/136944380</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>136949418</v>
+        <v>136949416</v>
       </c>
       <c r="B71" t="n">
         <v>78906</v>
@@ -8376,13 +8377,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>437022</v>
+        <v>437007</v>
       </c>
       <c r="R71" t="n">
-        <v>6851593</v>
+        <v>6851582</v>
       </c>
       <c r="S71" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8411,7 +8412,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8421,7 +8422,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8447,13 +8448,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949418</t>
+          <t>https://artportalen.se/Sighting/136949416</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>136949429</v>
+        <v>136949418</v>
       </c>
       <c r="B72" t="n">
         <v>78906</v>
@@ -8488,13 +8489,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>437038</v>
+        <v>437022</v>
       </c>
       <c r="R72" t="n">
-        <v>6851684</v>
+        <v>6851593</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8523,7 +8524,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8533,7 +8534,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8559,13 +8560,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949429</t>
+          <t>https://artportalen.se/Sighting/136949418</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>136949433</v>
+        <v>136949429</v>
       </c>
       <c r="B73" t="n">
         <v>78906</v>
@@ -8600,13 +8601,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>437035</v>
+        <v>437038</v>
       </c>
       <c r="R73" t="n">
-        <v>6851766</v>
+        <v>6851684</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8635,7 +8636,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8645,7 +8646,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8671,13 +8672,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949433</t>
+          <t>https://artportalen.se/Sighting/136949429</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>136949436</v>
+        <v>136949433</v>
       </c>
       <c r="B74" t="n">
         <v>78906</v>
@@ -8712,13 +8713,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>436998</v>
+        <v>437035</v>
       </c>
       <c r="R74" t="n">
-        <v>6851824</v>
+        <v>6851766</v>
       </c>
       <c r="S74" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8747,7 +8748,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8757,7 +8758,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8783,13 +8784,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949436</t>
+          <t>https://artportalen.se/Sighting/136949433</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>136949440</v>
+        <v>136949436</v>
       </c>
       <c r="B75" t="n">
         <v>78906</v>
@@ -8824,13 +8825,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>436930</v>
+        <v>436998</v>
       </c>
       <c r="R75" t="n">
-        <v>6851889</v>
+        <v>6851824</v>
       </c>
       <c r="S75" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8859,7 +8860,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8869,7 +8870,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8895,13 +8896,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949440</t>
+          <t>https://artportalen.se/Sighting/136949436</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>136949441</v>
+        <v>136949440</v>
       </c>
       <c r="B76" t="n">
         <v>78906</v>
@@ -8936,13 +8937,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>436950</v>
+        <v>436930</v>
       </c>
       <c r="R76" t="n">
-        <v>6851917</v>
+        <v>6851889</v>
       </c>
       <c r="S76" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8971,7 +8972,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8981,7 +8982,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9007,13 +9008,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949441</t>
+          <t>https://artportalen.se/Sighting/136949440</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>136949480</v>
+        <v>136949441</v>
       </c>
       <c r="B77" t="n">
         <v>78906</v>
@@ -9048,13 +9049,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>437152</v>
+        <v>436950</v>
       </c>
       <c r="R77" t="n">
-        <v>6851619</v>
+        <v>6851917</v>
       </c>
       <c r="S77" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9083,7 +9084,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9093,7 +9094,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9119,13 +9120,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949480</t>
+          <t>https://artportalen.se/Sighting/136949441</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>136949482</v>
+        <v>136949480</v>
       </c>
       <c r="B78" t="n">
         <v>78906</v>
@@ -9160,13 +9161,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>437142</v>
+        <v>437152</v>
       </c>
       <c r="R78" t="n">
-        <v>6851632</v>
+        <v>6851619</v>
       </c>
       <c r="S78" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9231,16 +9232,16 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949482</t>
+          <t>https://artportalen.se/Sighting/136949480</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>136944282</v>
+        <v>136949482</v>
       </c>
       <c r="B79" t="n">
-        <v>79260</v>
+        <v>78906</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9248,21 +9249,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9272,13 +9273,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>436970</v>
+        <v>437142</v>
       </c>
       <c r="R79" t="n">
-        <v>6851631</v>
+        <v>6851632</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9307,7 +9308,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9317,7 +9318,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9332,24 +9333,24 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944282</t>
+          <t>https://artportalen.se/Sighting/136949482</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>136944308</v>
+        <v>136944282</v>
       </c>
       <c r="B80" t="n">
         <v>79260</v>
@@ -9384,10 +9385,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>436929</v>
+        <v>436970</v>
       </c>
       <c r="R80" t="n">
-        <v>6851930</v>
+        <v>6851631</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9419,7 +9420,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9429,7 +9430,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9455,13 +9456,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944308</t>
+          <t>https://artportalen.se/Sighting/136944282</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>136944323</v>
+        <v>136944308</v>
       </c>
       <c r="B81" t="n">
         <v>79260</v>
@@ -9496,10 +9497,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>437081</v>
+        <v>436929</v>
       </c>
       <c r="R81" t="n">
-        <v>6852018</v>
+        <v>6851930</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9531,7 +9532,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9541,7 +9542,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9567,13 +9568,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944323</t>
+          <t>https://artportalen.se/Sighting/136944308</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>136944342</v>
+        <v>136944323</v>
       </c>
       <c r="B82" t="n">
         <v>79260</v>
@@ -9608,10 +9609,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>437150</v>
+        <v>437081</v>
       </c>
       <c r="R82" t="n">
-        <v>6851899</v>
+        <v>6852018</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9643,7 +9644,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9653,7 +9654,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9679,13 +9680,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944342</t>
+          <t>https://artportalen.se/Sighting/136944323</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>136944356</v>
+        <v>136944342</v>
       </c>
       <c r="B83" t="n">
         <v>79260</v>
@@ -9720,10 +9721,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437217</v>
+        <v>437150</v>
       </c>
       <c r="R83" t="n">
-        <v>6851630</v>
+        <v>6851899</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9755,7 +9756,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9765,7 +9766,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9791,13 +9792,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944356</t>
+          <t>https://artportalen.se/Sighting/136944342</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>136944363</v>
+        <v>136944356</v>
       </c>
       <c r="B84" t="n">
         <v>79260</v>
@@ -9832,10 +9833,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>437314</v>
+        <v>437217</v>
       </c>
       <c r="R84" t="n">
-        <v>6851629</v>
+        <v>6851630</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9867,7 +9868,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9877,7 +9878,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9903,13 +9904,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944363</t>
+          <t>https://artportalen.se/Sighting/136944356</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>136944379</v>
+        <v>136944363</v>
       </c>
       <c r="B85" t="n">
         <v>79260</v>
@@ -9944,10 +9945,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>437058</v>
+        <v>437314</v>
       </c>
       <c r="R85" t="n">
-        <v>6851469</v>
+        <v>6851629</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9979,7 +9980,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9989,7 +9990,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10015,13 +10016,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944379</t>
+          <t>https://artportalen.se/Sighting/136944363</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>136944385</v>
+        <v>136944379</v>
       </c>
       <c r="B86" t="n">
         <v>79260</v>
@@ -10056,10 +10057,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>437202</v>
+        <v>437058</v>
       </c>
       <c r="R86" t="n">
-        <v>6851367</v>
+        <v>6851469</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10091,7 +10092,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10101,7 +10102,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10127,16 +10128,16 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944385</t>
+          <t>https://artportalen.se/Sighting/136944379</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>136944275</v>
+        <v>136944385</v>
       </c>
       <c r="B87" t="n">
-        <v>80122</v>
+        <v>79260</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10144,21 +10145,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10168,10 +10169,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>437001</v>
+        <v>437202</v>
       </c>
       <c r="R87" t="n">
-        <v>6851613</v>
+        <v>6851367</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10203,7 +10204,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10213,7 +10214,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10239,13 +10240,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944275</t>
+          <t>https://artportalen.se/Sighting/136944385</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>136944280</v>
+        <v>136944275</v>
       </c>
       <c r="B88" t="n">
         <v>80122</v>
@@ -10280,10 +10281,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>436930</v>
+        <v>437001</v>
       </c>
       <c r="R88" t="n">
-        <v>6851649</v>
+        <v>6851613</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10315,7 +10316,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10325,7 +10326,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10351,13 +10352,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944280</t>
+          <t>https://artportalen.se/Sighting/136944275</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>136944288</v>
+        <v>136944280</v>
       </c>
       <c r="B89" t="n">
         <v>80122</v>
@@ -10392,10 +10393,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>436860</v>
+        <v>436930</v>
       </c>
       <c r="R89" t="n">
-        <v>6851691</v>
+        <v>6851649</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10427,7 +10428,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10437,7 +10438,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10463,13 +10464,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944288</t>
+          <t>https://artportalen.se/Sighting/136944280</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>136944290</v>
+        <v>136944288</v>
       </c>
       <c r="B90" t="n">
         <v>80122</v>
@@ -10504,10 +10505,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>436856</v>
+        <v>436860</v>
       </c>
       <c r="R90" t="n">
-        <v>6851702</v>
+        <v>6851691</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10539,7 +10540,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10549,7 +10550,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10575,13 +10576,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944290</t>
+          <t>https://artportalen.se/Sighting/136944288</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>136944297</v>
+        <v>136944290</v>
       </c>
       <c r="B91" t="n">
         <v>80122</v>
@@ -10616,10 +10617,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>436800</v>
+        <v>436856</v>
       </c>
       <c r="R91" t="n">
-        <v>6851770</v>
+        <v>6851702</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10651,7 +10652,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10661,7 +10662,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10687,13 +10688,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944297</t>
+          <t>https://artportalen.se/Sighting/136944290</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>136944301</v>
+        <v>136944297</v>
       </c>
       <c r="B92" t="n">
         <v>80122</v>
@@ -10728,10 +10729,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>436994</v>
+        <v>436800</v>
       </c>
       <c r="R92" t="n">
-        <v>6851833</v>
+        <v>6851770</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10763,7 +10764,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10773,7 +10774,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10799,13 +10800,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944301</t>
+          <t>https://artportalen.se/Sighting/136944297</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>136944305</v>
+        <v>136944301</v>
       </c>
       <c r="B93" t="n">
         <v>80122</v>
@@ -10840,7 +10841,7 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>436978</v>
+        <v>436994</v>
       </c>
       <c r="R93" t="n">
         <v>6851833</v>
@@ -10875,7 +10876,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10885,7 +10886,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10911,13 +10912,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944305</t>
+          <t>https://artportalen.se/Sighting/136944301</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>136944307</v>
+        <v>136944305</v>
       </c>
       <c r="B94" t="n">
         <v>80122</v>
@@ -10952,10 +10953,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>436937</v>
+        <v>436978</v>
       </c>
       <c r="R94" t="n">
-        <v>6851887</v>
+        <v>6851833</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10987,7 +10988,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10997,7 +10998,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11023,13 +11024,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944307</t>
+          <t>https://artportalen.se/Sighting/136944305</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>136944310</v>
+        <v>136944307</v>
       </c>
       <c r="B95" t="n">
         <v>80122</v>
@@ -11064,10 +11065,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>436979</v>
+        <v>436937</v>
       </c>
       <c r="R95" t="n">
-        <v>6851956</v>
+        <v>6851887</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11099,7 +11100,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11109,7 +11110,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11135,13 +11136,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944310</t>
+          <t>https://artportalen.se/Sighting/136944307</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>136944311</v>
+        <v>136944310</v>
       </c>
       <c r="B96" t="n">
         <v>80122</v>
@@ -11176,10 +11177,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>436997</v>
+        <v>436979</v>
       </c>
       <c r="R96" t="n">
-        <v>6852001</v>
+        <v>6851956</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11211,7 +11212,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11221,7 +11222,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11247,13 +11248,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944311</t>
+          <t>https://artportalen.se/Sighting/136944310</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>136944315</v>
+        <v>136944311</v>
       </c>
       <c r="B97" t="n">
         <v>80122</v>
@@ -11288,10 +11289,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>436996</v>
+        <v>436997</v>
       </c>
       <c r="R97" t="n">
-        <v>6852032</v>
+        <v>6852001</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11323,7 +11324,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11333,7 +11334,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11359,13 +11360,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944315</t>
+          <t>https://artportalen.se/Sighting/136944311</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>136944316</v>
+        <v>136944315</v>
       </c>
       <c r="B98" t="n">
         <v>80122</v>
@@ -11400,10 +11401,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>436993</v>
+        <v>436996</v>
       </c>
       <c r="R98" t="n">
-        <v>6852037</v>
+        <v>6852032</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11435,7 +11436,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11445,7 +11446,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11471,13 +11472,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944316</t>
+          <t>https://artportalen.se/Sighting/136944315</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>136944330</v>
+        <v>136944316</v>
       </c>
       <c r="B99" t="n">
         <v>80122</v>
@@ -11512,10 +11513,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>437377</v>
+        <v>436993</v>
       </c>
       <c r="R99" t="n">
-        <v>6851914</v>
+        <v>6852037</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11547,7 +11548,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11557,7 +11558,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11583,13 +11584,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944330</t>
+          <t>https://artportalen.se/Sighting/136944316</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>136944331</v>
+        <v>136944330</v>
       </c>
       <c r="B100" t="n">
         <v>80122</v>
@@ -11624,10 +11625,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>437392</v>
+        <v>437377</v>
       </c>
       <c r="R100" t="n">
-        <v>6851880</v>
+        <v>6851914</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11659,7 +11660,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11669,7 +11670,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11695,13 +11696,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944331</t>
+          <t>https://artportalen.se/Sighting/136944330</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>136944333</v>
+        <v>136944331</v>
       </c>
       <c r="B101" t="n">
         <v>80122</v>
@@ -11736,10 +11737,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>437380</v>
+        <v>437392</v>
       </c>
       <c r="R101" t="n">
-        <v>6851888</v>
+        <v>6851880</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11771,7 +11772,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11781,7 +11782,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11807,13 +11808,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944333</t>
+          <t>https://artportalen.se/Sighting/136944331</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>136944347</v>
+        <v>136944333</v>
       </c>
       <c r="B102" t="n">
         <v>80122</v>
@@ -11848,10 +11849,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>437072</v>
+        <v>437380</v>
       </c>
       <c r="R102" t="n">
-        <v>6851877</v>
+        <v>6851888</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11883,7 +11884,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11893,7 +11894,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11919,13 +11920,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944347</t>
+          <t>https://artportalen.se/Sighting/136944333</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>136944349</v>
+        <v>136944347</v>
       </c>
       <c r="B103" t="n">
         <v>80122</v>
@@ -11960,10 +11961,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>437037</v>
+        <v>437072</v>
       </c>
       <c r="R103" t="n">
-        <v>6851831</v>
+        <v>6851877</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11995,7 +11996,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12005,7 +12006,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12031,13 +12032,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944349</t>
+          <t>https://artportalen.se/Sighting/136944347</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>136944359</v>
+        <v>136944349</v>
       </c>
       <c r="B104" t="n">
         <v>80122</v>
@@ -12072,10 +12073,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>437298</v>
+        <v>437037</v>
       </c>
       <c r="R104" t="n">
-        <v>6851651</v>
+        <v>6851831</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12107,7 +12108,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12117,7 +12118,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12143,13 +12144,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944359</t>
+          <t>https://artportalen.se/Sighting/136944349</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>136944361</v>
+        <v>136944359</v>
       </c>
       <c r="B105" t="n">
         <v>80122</v>
@@ -12184,10 +12185,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>437314</v>
+        <v>437298</v>
       </c>
       <c r="R105" t="n">
-        <v>6851644</v>
+        <v>6851651</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12219,7 +12220,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12229,7 +12230,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12255,13 +12256,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944361</t>
+          <t>https://artportalen.se/Sighting/136944359</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>136944362</v>
+        <v>136944361</v>
       </c>
       <c r="B106" t="n">
         <v>80122</v>
@@ -12299,7 +12300,7 @@
         <v>437314</v>
       </c>
       <c r="R106" t="n">
-        <v>6851629</v>
+        <v>6851644</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12331,7 +12332,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12341,7 +12342,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12367,13 +12368,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944362</t>
+          <t>https://artportalen.se/Sighting/136944361</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>136944366</v>
+        <v>136944362</v>
       </c>
       <c r="B107" t="n">
         <v>80122</v>
@@ -12408,10 +12409,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>437324</v>
+        <v>437314</v>
       </c>
       <c r="R107" t="n">
-        <v>6851620</v>
+        <v>6851629</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12443,7 +12444,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12453,7 +12454,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12479,13 +12480,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944366</t>
+          <t>https://artportalen.se/Sighting/136944362</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>136944370</v>
+        <v>136944366</v>
       </c>
       <c r="B108" t="n">
         <v>80122</v>
@@ -12520,10 +12521,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>437274</v>
+        <v>437324</v>
       </c>
       <c r="R108" t="n">
-        <v>6851595</v>
+        <v>6851620</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12555,7 +12556,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12565,7 +12566,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12591,13 +12592,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944370</t>
+          <t>https://artportalen.se/Sighting/136944366</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>136944372</v>
+        <v>136944370</v>
       </c>
       <c r="B109" t="n">
         <v>80122</v>
@@ -12632,10 +12633,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>437159</v>
+        <v>437274</v>
       </c>
       <c r="R109" t="n">
-        <v>6851508</v>
+        <v>6851595</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12667,7 +12668,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12677,7 +12678,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12703,13 +12704,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944372</t>
+          <t>https://artportalen.se/Sighting/136944370</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>136944381</v>
+        <v>136944372</v>
       </c>
       <c r="B110" t="n">
         <v>80122</v>
@@ -12744,10 +12745,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>437086</v>
+        <v>437159</v>
       </c>
       <c r="R110" t="n">
-        <v>6851465</v>
+        <v>6851508</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12779,7 +12780,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12789,7 +12790,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12815,13 +12816,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944381</t>
+          <t>https://artportalen.se/Sighting/136944372</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>136944384</v>
+        <v>136944381</v>
       </c>
       <c r="B111" t="n">
         <v>80122</v>
@@ -12856,10 +12857,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>437173</v>
+        <v>437086</v>
       </c>
       <c r="R111" t="n">
-        <v>6851402</v>
+        <v>6851465</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12891,7 +12892,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12901,7 +12902,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12927,13 +12928,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944384</t>
+          <t>https://artportalen.se/Sighting/136944381</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>136944389</v>
+        <v>136944384</v>
       </c>
       <c r="B112" t="n">
         <v>80122</v>
@@ -12968,10 +12969,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>437278</v>
+        <v>437173</v>
       </c>
       <c r="R112" t="n">
-        <v>6851318</v>
+        <v>6851402</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13003,7 +13004,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13013,7 +13014,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13039,13 +13040,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944389</t>
+          <t>https://artportalen.se/Sighting/136944384</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>136944391</v>
+        <v>136944389</v>
       </c>
       <c r="B113" t="n">
         <v>80122</v>
@@ -13080,10 +13081,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>437267</v>
+        <v>437278</v>
       </c>
       <c r="R113" t="n">
-        <v>6851308</v>
+        <v>6851318</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13115,7 +13116,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13125,7 +13126,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13151,13 +13152,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944391</t>
+          <t>https://artportalen.se/Sighting/136944389</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>136944394</v>
+        <v>136944391</v>
       </c>
       <c r="B114" t="n">
         <v>80122</v>
@@ -13192,10 +13193,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>436930</v>
+        <v>437267</v>
       </c>
       <c r="R114" t="n">
-        <v>6851527</v>
+        <v>6851308</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13227,7 +13228,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13237,7 +13238,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13263,13 +13264,13 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944394</t>
+          <t>https://artportalen.se/Sighting/136944391</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>136949419</v>
+        <v>136944394</v>
       </c>
       <c r="B115" t="n">
         <v>80122</v>
@@ -13304,13 +13305,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>437035</v>
+        <v>436930</v>
       </c>
       <c r="R115" t="n">
-        <v>6851586</v>
+        <v>6851527</v>
       </c>
       <c r="S115" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13339,7 +13340,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13349,7 +13350,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13364,24 +13365,24 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949419</t>
+          <t>https://artportalen.se/Sighting/136944394</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>136949421</v>
+        <v>136949419</v>
       </c>
       <c r="B116" t="n">
         <v>80122</v>
@@ -13416,13 +13417,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>437063</v>
+        <v>437035</v>
       </c>
       <c r="R116" t="n">
-        <v>6851578</v>
+        <v>6851586</v>
       </c>
       <c r="S116" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13451,7 +13452,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13461,7 +13462,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13487,13 +13488,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949421</t>
+          <t>https://artportalen.se/Sighting/136949419</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>136949424</v>
+        <v>136949421</v>
       </c>
       <c r="B117" t="n">
         <v>80122</v>
@@ -13528,13 +13529,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>437048</v>
+        <v>437063</v>
       </c>
       <c r="R117" t="n">
-        <v>6851638</v>
+        <v>6851578</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13563,7 +13564,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13573,7 +13574,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13599,13 +13600,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949424</t>
+          <t>https://artportalen.se/Sighting/136949421</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>136949438</v>
+        <v>136949424</v>
       </c>
       <c r="B118" t="n">
         <v>80122</v>
@@ -13640,13 +13641,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>436997</v>
+        <v>437048</v>
       </c>
       <c r="R118" t="n">
-        <v>6851827</v>
+        <v>6851638</v>
       </c>
       <c r="S118" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13675,7 +13676,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13685,7 +13686,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13711,13 +13712,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949438</t>
+          <t>https://artportalen.se/Sighting/136949424</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>136949442</v>
+        <v>136949438</v>
       </c>
       <c r="B119" t="n">
         <v>80122</v>
@@ -13752,10 +13753,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>436956</v>
+        <v>436997</v>
       </c>
       <c r="R119" t="n">
-        <v>6851909</v>
+        <v>6851827</v>
       </c>
       <c r="S119" t="n">
         <v>12</v>
@@ -13787,7 +13788,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13797,7 +13798,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13823,13 +13824,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949442</t>
+          <t>https://artportalen.se/Sighting/136949438</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>136949443</v>
+        <v>136949442</v>
       </c>
       <c r="B120" t="n">
         <v>80122</v>
@@ -13864,13 +13865,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>437013</v>
+        <v>436956</v>
       </c>
       <c r="R120" t="n">
-        <v>6852030</v>
+        <v>6851909</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13899,7 +13900,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13909,7 +13910,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13935,13 +13936,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949443</t>
+          <t>https://artportalen.se/Sighting/136949442</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>136949444</v>
+        <v>136949443</v>
       </c>
       <c r="B121" t="n">
         <v>80122</v>
@@ -13976,13 +13977,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>437046</v>
+        <v>437013</v>
       </c>
       <c r="R121" t="n">
-        <v>6852063</v>
+        <v>6852030</v>
       </c>
       <c r="S121" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14011,7 +14012,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14021,7 +14022,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14047,13 +14048,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949444</t>
+          <t>https://artportalen.se/Sighting/136949443</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>136949449</v>
+        <v>136949444</v>
       </c>
       <c r="B122" t="n">
         <v>80122</v>
@@ -14088,13 +14089,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>437232</v>
+        <v>437046</v>
       </c>
       <c r="R122" t="n">
-        <v>6851908</v>
+        <v>6852063</v>
       </c>
       <c r="S122" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14123,7 +14124,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14133,7 +14134,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14159,13 +14160,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949449</t>
+          <t>https://artportalen.se/Sighting/136949444</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>136949450</v>
+        <v>136949449</v>
       </c>
       <c r="B123" t="n">
         <v>80122</v>
@@ -14200,13 +14201,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>437316</v>
+        <v>437232</v>
       </c>
       <c r="R123" t="n">
-        <v>6851901</v>
+        <v>6851908</v>
       </c>
       <c r="S123" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14235,7 +14236,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14245,7 +14246,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14271,13 +14272,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949450</t>
+          <t>https://artportalen.se/Sighting/136949449</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>136949451</v>
+        <v>136949450</v>
       </c>
       <c r="B124" t="n">
         <v>80122</v>
@@ -14312,13 +14313,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>437362</v>
+        <v>437316</v>
       </c>
       <c r="R124" t="n">
-        <v>6851894</v>
+        <v>6851901</v>
       </c>
       <c r="S124" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14347,7 +14348,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14357,7 +14358,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14383,13 +14384,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949451</t>
+          <t>https://artportalen.se/Sighting/136949450</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>136949452</v>
+        <v>136949451</v>
       </c>
       <c r="B125" t="n">
         <v>80122</v>
@@ -14424,13 +14425,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>437363</v>
+        <v>437362</v>
       </c>
       <c r="R125" t="n">
         <v>6851894</v>
       </c>
       <c r="S125" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14459,7 +14460,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14469,7 +14470,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14495,13 +14496,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949452</t>
+          <t>https://artportalen.se/Sighting/136949451</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>136949465</v>
+        <v>136949452</v>
       </c>
       <c r="B126" t="n">
         <v>80122</v>
@@ -14536,13 +14537,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>437227</v>
+        <v>437363</v>
       </c>
       <c r="R126" t="n">
-        <v>6851551</v>
+        <v>6851894</v>
       </c>
       <c r="S126" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14571,7 +14572,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14581,7 +14582,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14607,13 +14608,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949465</t>
+          <t>https://artportalen.se/Sighting/136949452</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>136949467</v>
+        <v>136949465</v>
       </c>
       <c r="B127" t="n">
         <v>80122</v>
@@ -14648,13 +14649,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>437253</v>
+        <v>437227</v>
       </c>
       <c r="R127" t="n">
-        <v>6851544</v>
+        <v>6851551</v>
       </c>
       <c r="S127" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14683,7 +14684,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14693,7 +14694,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14719,13 +14720,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949467</t>
+          <t>https://artportalen.se/Sighting/136949465</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>136949468</v>
+        <v>136949467</v>
       </c>
       <c r="B128" t="n">
         <v>80122</v>
@@ -14760,13 +14761,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>437254</v>
+        <v>437253</v>
       </c>
       <c r="R128" t="n">
-        <v>6851513</v>
+        <v>6851544</v>
       </c>
       <c r="S128" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14795,7 +14796,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14805,7 +14806,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14831,13 +14832,13 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949468</t>
+          <t>https://artportalen.se/Sighting/136949467</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>136949470</v>
+        <v>136949468</v>
       </c>
       <c r="B129" t="n">
         <v>80122</v>
@@ -14872,13 +14873,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>437229</v>
+        <v>437254</v>
       </c>
       <c r="R129" t="n">
-        <v>6851515</v>
+        <v>6851513</v>
       </c>
       <c r="S129" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14907,7 +14908,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14917,7 +14918,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14943,13 +14944,13 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949470</t>
+          <t>https://artportalen.se/Sighting/136949468</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>136949471</v>
+        <v>136949470</v>
       </c>
       <c r="B130" t="n">
         <v>80122</v>
@@ -14984,13 +14985,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>437226</v>
+        <v>437229</v>
       </c>
       <c r="R130" t="n">
-        <v>6851508</v>
+        <v>6851515</v>
       </c>
       <c r="S130" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15055,13 +15056,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949471</t>
+          <t>https://artportalen.se/Sighting/136949470</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>136949476</v>
+        <v>136949471</v>
       </c>
       <c r="B131" t="n">
         <v>80122</v>
@@ -15096,13 +15097,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>437138</v>
+        <v>437226</v>
       </c>
       <c r="R131" t="n">
-        <v>6851539</v>
+        <v>6851508</v>
       </c>
       <c r="S131" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15131,7 +15132,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15141,7 +15142,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15167,13 +15168,13 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949476</t>
+          <t>https://artportalen.se/Sighting/136949471</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>136949484</v>
+        <v>136949476</v>
       </c>
       <c r="B132" t="n">
         <v>80122</v>
@@ -15208,13 +15209,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>437275</v>
+        <v>437138</v>
       </c>
       <c r="R132" t="n">
-        <v>6851334</v>
+        <v>6851539</v>
       </c>
       <c r="S132" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15243,7 +15244,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15253,7 +15254,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15279,16 +15280,16 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949484</t>
+          <t>https://artportalen.se/Sighting/136949476</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>66498805</v>
+        <v>136949484</v>
       </c>
       <c r="B133" t="n">
-        <v>78334</v>
+        <v>80122</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15296,21 +15297,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15320,13 +15321,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>437026</v>
+        <v>437275</v>
       </c>
       <c r="R133" t="n">
-        <v>6851819</v>
+        <v>6851334</v>
       </c>
       <c r="S133" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15350,12 +15351,22 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2011-08-09</t>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2011-08-09</t>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15366,33 +15377,28 @@
       </c>
       <c r="AG133" t="b">
         <v>0</v>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>12120</t>
-        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66498805</t>
+          <t>https://artportalen.se/Sighting/136949484</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>66498817</v>
+        <v>66498805</v>
       </c>
       <c r="B134" t="n">
         <v>78334</v>
@@ -15427,10 +15433,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>437015</v>
+        <v>437026</v>
       </c>
       <c r="R134" t="n">
-        <v>6851586</v>
+        <v>6851819</v>
       </c>
       <c r="S134" t="n">
         <v>50</v>
@@ -15476,7 +15482,7 @@
       </c>
       <c r="AR134" t="inlineStr">
         <is>
-          <t>12130</t>
+          <t>12120</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -15493,16 +15499,16 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66498817</t>
+          <t>https://artportalen.se/Sighting/66498805</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>136949426</v>
+        <v>66498817</v>
       </c>
       <c r="B135" t="n">
-        <v>78503</v>
+        <v>78334</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15534,13 +15540,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>437052</v>
+        <v>437015</v>
       </c>
       <c r="R135" t="n">
-        <v>6851658</v>
+        <v>6851586</v>
       </c>
       <c r="S135" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15564,22 +15570,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>12:11</t>
+          <t>2011-08-09</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>12:11</t>
+          <t>2011-08-09</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15590,28 +15586,33 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>12130</t>
+        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949426</t>
+          <t>https://artportalen.se/Sighting/66498817</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>136949430</v>
+        <v>136949426</v>
       </c>
       <c r="B136" t="n">
         <v>78503</v>
@@ -15646,13 +15647,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>437038</v>
+        <v>437052</v>
       </c>
       <c r="R136" t="n">
-        <v>6851684</v>
+        <v>6851658</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15681,7 +15682,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15691,7 +15692,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15717,13 +15718,13 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949430</t>
+          <t>https://artportalen.se/Sighting/136949426</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>136949457</v>
+        <v>136949430</v>
       </c>
       <c r="B137" t="n">
         <v>78503</v>
@@ -15758,13 +15759,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>437196</v>
+        <v>437038</v>
       </c>
       <c r="R137" t="n">
-        <v>6851778</v>
+        <v>6851684</v>
       </c>
       <c r="S137" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15793,7 +15794,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15803,7 +15804,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15829,13 +15830,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949457</t>
+          <t>https://artportalen.se/Sighting/136949430</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>136949459</v>
+        <v>136949457</v>
       </c>
       <c r="B138" t="n">
         <v>78503</v>
@@ -15870,13 +15871,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>437102</v>
+        <v>437196</v>
       </c>
       <c r="R138" t="n">
-        <v>6851741</v>
+        <v>6851778</v>
       </c>
       <c r="S138" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15905,7 +15906,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15915,7 +15916,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15941,13 +15942,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949459</t>
+          <t>https://artportalen.se/Sighting/136949457</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>136949460</v>
+        <v>136949459</v>
       </c>
       <c r="B139" t="n">
         <v>78503</v>
@@ -15982,13 +15983,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>437136</v>
+        <v>437102</v>
       </c>
       <c r="R139" t="n">
-        <v>6851708</v>
+        <v>6851741</v>
       </c>
       <c r="S139" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16017,7 +16018,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -16027,7 +16028,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16053,16 +16054,16 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949460</t>
+          <t>https://artportalen.se/Sighting/136949459</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>136944386</v>
+        <v>136949460</v>
       </c>
       <c r="B140" t="n">
-        <v>58023</v>
+        <v>78503</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16070,38 +16071,37 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Dödåsen, Hjd</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>437220</v>
+        <v>437136</v>
       </c>
       <c r="R140" t="n">
-        <v>6851349</v>
+        <v>6851708</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -16140,12 +16140,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16160,27 +16155,27 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944386</t>
+          <t>https://artportalen.se/Sighting/136949460</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>136944299</v>
+        <v>136944386</v>
       </c>
       <c r="B141" t="n">
-        <v>58184</v>
+        <v>58023</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16188,34 +16183,35 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Dödåsen, Hjd</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>436905</v>
+        <v>437220</v>
       </c>
       <c r="R141" t="n">
-        <v>6851819</v>
+        <v>6851349</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16247,7 +16243,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -16257,7 +16253,12 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16283,13 +16284,13 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944299</t>
+          <t>https://artportalen.se/Sighting/136944386</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>136944334</v>
+        <v>136944299</v>
       </c>
       <c r="B142" t="n">
         <v>58184</v>
@@ -16324,10 +16325,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>437375</v>
+        <v>436905</v>
       </c>
       <c r="R142" t="n">
-        <v>6851834</v>
+        <v>6851819</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16359,7 +16360,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -16369,7 +16370,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16395,13 +16396,13 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944334</t>
+          <t>https://artportalen.se/Sighting/136944299</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>136944336</v>
+        <v>136944334</v>
       </c>
       <c r="B143" t="n">
         <v>58184</v>
@@ -16429,22 +16430,17 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Dödåsen, Hjd</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>437252</v>
+        <v>437375</v>
       </c>
       <c r="R143" t="n">
-        <v>6851840</v>
+        <v>6851834</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16476,7 +16472,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16486,7 +16482,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16512,13 +16508,13 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944336</t>
+          <t>https://artportalen.se/Sighting/136944334</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>136944376</v>
+        <v>136944336</v>
       </c>
       <c r="B144" t="n">
         <v>58184</v>
@@ -16546,17 +16542,22 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Dödåsen, Hjd</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>437037</v>
+        <v>437252</v>
       </c>
       <c r="R144" t="n">
-        <v>6851492</v>
+        <v>6851840</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16588,7 +16589,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16598,7 +16599,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16624,13 +16625,13 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944376</t>
+          <t>https://artportalen.se/Sighting/136944336</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>136949455</v>
+        <v>136944376</v>
       </c>
       <c r="B145" t="n">
         <v>58184</v>
@@ -16659,17 +16660,16 @@
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Dödåsen, Hjd</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>437291</v>
+        <v>437037</v>
       </c>
       <c r="R145" t="n">
-        <v>6851813</v>
+        <v>6851492</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16701,7 +16701,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16711,7 +16711,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16726,62 +16726,63 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949455</t>
+          <t>https://artportalen.se/Sighting/136944376</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>136944309</v>
+        <v>136949455</v>
       </c>
       <c r="B146" t="n">
-        <v>98259</v>
+        <v>58184</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Dödåsen, Hjd</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>436934</v>
+        <v>437291</v>
       </c>
       <c r="R146" t="n">
-        <v>6851916</v>
+        <v>6851813</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16813,7 +16814,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16823,7 +16824,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16838,49 +16839,49 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944309</t>
+          <t>https://artportalen.se/Sighting/136949455</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>136944303</v>
+        <v>136944309</v>
       </c>
       <c r="B147" t="n">
-        <v>79261</v>
+        <v>98262</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16890,10 +16891,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>436978</v>
+        <v>436934</v>
       </c>
       <c r="R147" t="n">
-        <v>6851836</v>
+        <v>6851916</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16925,7 +16926,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16935,7 +16936,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16961,13 +16962,13 @@
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944303</t>
+          <t>https://artportalen.se/Sighting/136944309</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>136944314</v>
+        <v>136944303</v>
       </c>
       <c r="B148" t="n">
         <v>79261</v>
@@ -17002,10 +17003,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>436997</v>
+        <v>436978</v>
       </c>
       <c r="R148" t="n">
-        <v>6852001</v>
+        <v>6851836</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17037,7 +17038,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -17047,7 +17048,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17073,13 +17074,13 @@
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944314</t>
+          <t>https://artportalen.se/Sighting/136944303</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>136944355</v>
+        <v>136944314</v>
       </c>
       <c r="B149" t="n">
         <v>79261</v>
@@ -17114,10 +17115,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>437216</v>
+        <v>436997</v>
       </c>
       <c r="R149" t="n">
-        <v>6851632</v>
+        <v>6852001</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17149,7 +17150,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -17159,7 +17160,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17185,13 +17186,13 @@
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944355</t>
+          <t>https://artportalen.se/Sighting/136944314</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>136944373</v>
+        <v>136944355</v>
       </c>
       <c r="B150" t="n">
         <v>79261</v>
@@ -17226,10 +17227,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>437162</v>
+        <v>437216</v>
       </c>
       <c r="R150" t="n">
-        <v>6851507</v>
+        <v>6851632</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17261,7 +17262,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17271,7 +17272,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17297,13 +17298,13 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944373</t>
+          <t>https://artportalen.se/Sighting/136944355</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>136944378</v>
+        <v>136944373</v>
       </c>
       <c r="B151" t="n">
         <v>79261</v>
@@ -17338,10 +17339,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>437055</v>
+        <v>437162</v>
       </c>
       <c r="R151" t="n">
-        <v>6851469</v>
+        <v>6851507</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17373,7 +17374,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17383,7 +17384,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17409,13 +17410,13 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944378</t>
+          <t>https://artportalen.se/Sighting/136944373</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>136944387</v>
+        <v>136944378</v>
       </c>
       <c r="B152" t="n">
         <v>79261</v>
@@ -17450,10 +17451,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>437204</v>
+        <v>437055</v>
       </c>
       <c r="R152" t="n">
-        <v>6851360</v>
+        <v>6851469</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17485,7 +17486,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17495,7 +17496,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17521,13 +17522,13 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944387</t>
+          <t>https://artportalen.se/Sighting/136944378</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>136944392</v>
+        <v>136944387</v>
       </c>
       <c r="B153" t="n">
         <v>79261</v>
@@ -17562,10 +17563,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>437267</v>
+        <v>437204</v>
       </c>
       <c r="R153" t="n">
-        <v>6851308</v>
+        <v>6851360</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17597,7 +17598,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17607,7 +17608,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17633,16 +17634,16 @@
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944392</t>
+          <t>https://artportalen.se/Sighting/136944387</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>136944281</v>
+        <v>136944392</v>
       </c>
       <c r="B154" t="n">
-        <v>80093</v>
+        <v>79261</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17650,21 +17651,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17674,10 +17675,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>436906</v>
+        <v>437267</v>
       </c>
       <c r="R154" t="n">
-        <v>6851660</v>
+        <v>6851308</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17709,7 +17710,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17719,7 +17720,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17745,13 +17746,13 @@
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944281</t>
+          <t>https://artportalen.se/Sighting/136944392</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>136944302</v>
+        <v>136944281</v>
       </c>
       <c r="B155" t="n">
         <v>80093</v>
@@ -17786,10 +17787,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>437000</v>
+        <v>436906</v>
       </c>
       <c r="R155" t="n">
-        <v>6851836</v>
+        <v>6851660</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17821,7 +17822,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17831,7 +17832,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17857,13 +17858,13 @@
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944302</t>
+          <t>https://artportalen.se/Sighting/136944281</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>136944317</v>
+        <v>136944302</v>
       </c>
       <c r="B156" t="n">
         <v>80093</v>
@@ -17898,10 +17899,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>436993</v>
+        <v>437000</v>
       </c>
       <c r="R156" t="n">
-        <v>6852037</v>
+        <v>6851836</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17933,7 +17934,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17943,7 +17944,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17969,13 +17970,13 @@
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944317</t>
+          <t>https://artportalen.se/Sighting/136944302</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>136944328</v>
+        <v>136944317</v>
       </c>
       <c r="B157" t="n">
         <v>80093</v>
@@ -18010,10 +18011,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>437365</v>
+        <v>436993</v>
       </c>
       <c r="R157" t="n">
-        <v>6851913</v>
+        <v>6852037</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18045,7 +18046,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18055,7 +18056,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18081,13 +18082,13 @@
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944328</t>
+          <t>https://artportalen.se/Sighting/136944317</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>136944337</v>
+        <v>136944328</v>
       </c>
       <c r="B158" t="n">
         <v>80093</v>
@@ -18122,10 +18123,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>437172</v>
+        <v>437365</v>
       </c>
       <c r="R158" t="n">
-        <v>6851862</v>
+        <v>6851913</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18157,7 +18158,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -18167,7 +18168,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18193,13 +18194,13 @@
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944337</t>
+          <t>https://artportalen.se/Sighting/136944328</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>136944339</v>
+        <v>136944337</v>
       </c>
       <c r="B159" t="n">
         <v>80093</v>
@@ -18234,10 +18235,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>437163</v>
+        <v>437172</v>
       </c>
       <c r="R159" t="n">
-        <v>6851883</v>
+        <v>6851862</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18269,7 +18270,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -18279,7 +18280,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18305,13 +18306,13 @@
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944339</t>
+          <t>https://artportalen.se/Sighting/136944337</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>136944345</v>
+        <v>136944339</v>
       </c>
       <c r="B160" t="n">
         <v>80093</v>
@@ -18346,10 +18347,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>437095</v>
+        <v>437163</v>
       </c>
       <c r="R160" t="n">
-        <v>6851876</v>
+        <v>6851883</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18381,7 +18382,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18391,7 +18392,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18417,13 +18418,13 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944345</t>
+          <t>https://artportalen.se/Sighting/136944339</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>136944350</v>
+        <v>136944345</v>
       </c>
       <c r="B161" t="n">
         <v>80093</v>
@@ -18458,10 +18459,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>437050</v>
+        <v>437095</v>
       </c>
       <c r="R161" t="n">
-        <v>6851832</v>
+        <v>6851876</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18493,7 +18494,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -18503,7 +18504,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18529,13 +18530,13 @@
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944350</t>
+          <t>https://artportalen.se/Sighting/136944345</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>136944351</v>
+        <v>136944350</v>
       </c>
       <c r="B162" t="n">
         <v>80093</v>
@@ -18570,10 +18571,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>437080</v>
+        <v>437050</v>
       </c>
       <c r="R162" t="n">
-        <v>6851758</v>
+        <v>6851832</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18605,7 +18606,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -18615,12 +18616,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>På stubbe med sex brandljud</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18646,13 +18642,13 @@
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944351</t>
+          <t>https://artportalen.se/Sighting/136944350</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>136944368</v>
+        <v>136944351</v>
       </c>
       <c r="B163" t="n">
         <v>80093</v>
@@ -18687,10 +18683,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>437307</v>
+        <v>437080</v>
       </c>
       <c r="R163" t="n">
-        <v>6851612</v>
+        <v>6851758</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18722,7 +18718,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18732,7 +18728,12 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>På stubbe med sex brandljud</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18758,13 +18759,13 @@
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944368</t>
+          <t>https://artportalen.se/Sighting/136944351</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>136944375</v>
+        <v>136944368</v>
       </c>
       <c r="B164" t="n">
         <v>80093</v>
@@ -18799,10 +18800,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>437055</v>
+        <v>437307</v>
       </c>
       <c r="R164" t="n">
-        <v>6851589</v>
+        <v>6851612</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18834,7 +18835,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -18844,7 +18845,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18870,13 +18871,13 @@
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944375</t>
+          <t>https://artportalen.se/Sighting/136944368</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>136944377</v>
+        <v>136944375</v>
       </c>
       <c r="B165" t="n">
         <v>80093</v>
@@ -18911,10 +18912,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>437058</v>
+        <v>437055</v>
       </c>
       <c r="R165" t="n">
-        <v>6851470</v>
+        <v>6851589</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18946,7 +18947,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18956,7 +18957,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18982,13 +18983,13 @@
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944377</t>
+          <t>https://artportalen.se/Sighting/136944375</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>136944388</v>
+        <v>136944377</v>
       </c>
       <c r="B166" t="n">
         <v>80093</v>
@@ -19023,10 +19024,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>437270</v>
+        <v>437058</v>
       </c>
       <c r="R166" t="n">
-        <v>6851324</v>
+        <v>6851470</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19058,7 +19059,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -19068,7 +19069,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19094,13 +19095,13 @@
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136944388</t>
+          <t>https://artportalen.se/Sighting/136944377</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>136949420</v>
+        <v>136944388</v>
       </c>
       <c r="B167" t="n">
         <v>80093</v>
@@ -19135,13 +19136,13 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>437059</v>
+        <v>437270</v>
       </c>
       <c r="R167" t="n">
-        <v>6851585</v>
+        <v>6851324</v>
       </c>
       <c r="S167" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -19170,7 +19171,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -19180,7 +19181,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19195,24 +19196,24 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949420</t>
+          <t>https://artportalen.se/Sighting/136944388</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>136949425</v>
+        <v>136949420</v>
       </c>
       <c r="B168" t="n">
         <v>80093</v>
@@ -19247,13 +19248,13 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>437048</v>
+        <v>437059</v>
       </c>
       <c r="R168" t="n">
-        <v>6851655</v>
+        <v>6851585</v>
       </c>
       <c r="S168" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -19282,7 +19283,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -19292,7 +19293,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19318,13 +19319,13 @@
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949425</t>
+          <t>https://artportalen.se/Sighting/136949420</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>136949428</v>
+        <v>136949425</v>
       </c>
       <c r="B169" t="n">
         <v>80093</v>
@@ -19359,10 +19360,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>437036</v>
+        <v>437048</v>
       </c>
       <c r="R169" t="n">
-        <v>6851686</v>
+        <v>6851655</v>
       </c>
       <c r="S169" t="n">
         <v>12</v>
@@ -19394,7 +19395,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -19404,7 +19405,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19430,13 +19431,13 @@
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949428</t>
+          <t>https://artportalen.se/Sighting/136949425</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>136949432</v>
+        <v>136949428</v>
       </c>
       <c r="B170" t="n">
         <v>80093</v>
@@ -19471,13 +19472,13 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>437031</v>
+        <v>437036</v>
       </c>
       <c r="R170" t="n">
-        <v>6851765</v>
+        <v>6851686</v>
       </c>
       <c r="S170" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -19506,7 +19507,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -19516,7 +19517,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19542,13 +19543,13 @@
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949432</t>
+          <t>https://artportalen.se/Sighting/136949428</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>136949437</v>
+        <v>136949432</v>
       </c>
       <c r="B171" t="n">
         <v>80093</v>
@@ -19583,13 +19584,13 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>436997</v>
+        <v>437031</v>
       </c>
       <c r="R171" t="n">
-        <v>6851827</v>
+        <v>6851765</v>
       </c>
       <c r="S171" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -19618,7 +19619,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19628,7 +19629,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19654,13 +19655,13 @@
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949437</t>
+          <t>https://artportalen.se/Sighting/136949432</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>136949439</v>
+        <v>136949437</v>
       </c>
       <c r="B172" t="n">
         <v>80093</v>
@@ -19698,10 +19699,10 @@
         <v>436997</v>
       </c>
       <c r="R172" t="n">
-        <v>6851843</v>
+        <v>6851827</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -19730,7 +19731,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19740,7 +19741,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19766,13 +19767,13 @@
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949439</t>
+          <t>https://artportalen.se/Sighting/136949437</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>136949448</v>
+        <v>136949439</v>
       </c>
       <c r="B173" t="n">
         <v>80093</v>
@@ -19807,13 +19808,13 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>437232</v>
+        <v>436997</v>
       </c>
       <c r="R173" t="n">
-        <v>6851908</v>
+        <v>6851843</v>
       </c>
       <c r="S173" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -19842,7 +19843,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19852,7 +19853,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19878,13 +19879,13 @@
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949448</t>
+          <t>https://artportalen.se/Sighting/136949439</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>136949456</v>
+        <v>136949448</v>
       </c>
       <c r="B174" t="n">
         <v>80093</v>
@@ -19919,13 +19920,13 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>437192</v>
+        <v>437232</v>
       </c>
       <c r="R174" t="n">
-        <v>6851776</v>
+        <v>6851908</v>
       </c>
       <c r="S174" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -19954,7 +19955,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19964,7 +19965,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19990,13 +19991,13 @@
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949456</t>
+          <t>https://artportalen.se/Sighting/136949448</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>136949461</v>
+        <v>136949456</v>
       </c>
       <c r="B175" t="n">
         <v>80093</v>
@@ -20031,13 +20032,13 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>437181</v>
+        <v>437192</v>
       </c>
       <c r="R175" t="n">
-        <v>6851676</v>
+        <v>6851776</v>
       </c>
       <c r="S175" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -20066,7 +20067,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -20076,7 +20077,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20102,13 +20103,13 @@
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949461</t>
+          <t>https://artportalen.se/Sighting/136949456</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>136949462</v>
+        <v>136949461</v>
       </c>
       <c r="B176" t="n">
         <v>80093</v>
@@ -20143,13 +20144,13 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>437168</v>
+        <v>437181</v>
       </c>
       <c r="R176" t="n">
-        <v>6851622</v>
+        <v>6851676</v>
       </c>
       <c r="S176" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -20178,7 +20179,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -20188,7 +20189,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20214,13 +20215,13 @@
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949462</t>
+          <t>https://artportalen.se/Sighting/136949461</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>136949464</v>
+        <v>136949462</v>
       </c>
       <c r="B177" t="n">
         <v>80093</v>
@@ -20255,13 +20256,13 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>437216</v>
+        <v>437168</v>
       </c>
       <c r="R177" t="n">
-        <v>6851558</v>
+        <v>6851622</v>
       </c>
       <c r="S177" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -20290,7 +20291,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -20300,7 +20301,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20326,13 +20327,13 @@
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949464</t>
+          <t>https://artportalen.se/Sighting/136949462</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>136949466</v>
+        <v>136949464</v>
       </c>
       <c r="B178" t="n">
         <v>80093</v>
@@ -20367,13 +20368,13 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>437255</v>
+        <v>437216</v>
       </c>
       <c r="R178" t="n">
-        <v>6851547</v>
+        <v>6851558</v>
       </c>
       <c r="S178" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -20402,7 +20403,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -20412,7 +20413,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20438,13 +20439,13 @@
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949466</t>
+          <t>https://artportalen.se/Sighting/136949464</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>136949469</v>
+        <v>136949466</v>
       </c>
       <c r="B179" t="n">
         <v>80093</v>
@@ -20479,13 +20480,13 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>437234</v>
+        <v>437255</v>
       </c>
       <c r="R179" t="n">
-        <v>6851519</v>
+        <v>6851547</v>
       </c>
       <c r="S179" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -20514,7 +20515,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -20524,7 +20525,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20550,13 +20551,13 @@
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949469</t>
+          <t>https://artportalen.se/Sighting/136949466</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>136949474</v>
+        <v>136949469</v>
       </c>
       <c r="B180" t="n">
         <v>80093</v>
@@ -20591,13 +20592,13 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>437155</v>
+        <v>437234</v>
       </c>
       <c r="R180" t="n">
-        <v>6851528</v>
+        <v>6851519</v>
       </c>
       <c r="S180" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -20626,7 +20627,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -20636,7 +20637,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20662,13 +20663,13 @@
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949474</t>
+          <t>https://artportalen.se/Sighting/136949469</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>136949478</v>
+        <v>136949474</v>
       </c>
       <c r="B181" t="n">
         <v>80093</v>
@@ -20703,10 +20704,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>437139</v>
+        <v>437155</v>
       </c>
       <c r="R181" t="n">
-        <v>6851572</v>
+        <v>6851528</v>
       </c>
       <c r="S181" t="n">
         <v>11</v>
@@ -20738,7 +20739,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -20748,7 +20749,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20774,13 +20775,13 @@
       <c r="AY181" t="inlineStr"/>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949478</t>
+          <t>https://artportalen.se/Sighting/136949474</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>136949479</v>
+        <v>136949478</v>
       </c>
       <c r="B182" t="n">
         <v>80093</v>
@@ -20815,13 +20816,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>437148</v>
+        <v>437139</v>
       </c>
       <c r="R182" t="n">
-        <v>6851608</v>
+        <v>6851572</v>
       </c>
       <c r="S182" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -20850,7 +20851,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -20860,7 +20861,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20886,13 +20887,13 @@
       <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949479</t>
+          <t>https://artportalen.se/Sighting/136949478</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>136949481</v>
+        <v>136949479</v>
       </c>
       <c r="B183" t="n">
         <v>80093</v>
@@ -20927,13 +20928,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>437150</v>
+        <v>437148</v>
       </c>
       <c r="R183" t="n">
-        <v>6851621</v>
+        <v>6851608</v>
       </c>
       <c r="S183" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -20962,7 +20963,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -20972,7 +20973,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20998,38 +20999,38 @@
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949481</t>
+          <t>https://artportalen.se/Sighting/136949479</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>136949454</v>
+        <v>136949481</v>
       </c>
       <c r="B184" t="n">
-        <v>93473</v>
+        <v>80093</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>232140</v>
+        <v>229821</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -21039,13 +21040,13 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>437346</v>
+        <v>437150</v>
       </c>
       <c r="R184" t="n">
-        <v>6851823</v>
+        <v>6851621</v>
       </c>
       <c r="S184" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21074,7 +21075,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -21084,7 +21085,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21110,16 +21111,16 @@
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949454</t>
+          <t>https://artportalen.se/Sighting/136949481</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>136949446</v>
+        <v>136949454</v>
       </c>
       <c r="B185" t="n">
-        <v>87399</v>
+        <v>93476</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21127,21 +21128,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>249254</v>
+        <v>232140</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Mospindling</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Cortinarius areni-silvae</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Brandrud) Brandrud</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -21151,13 +21152,13 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>437118</v>
+        <v>437346</v>
       </c>
       <c r="R185" t="n">
-        <v>6852026</v>
+        <v>6851823</v>
       </c>
       <c r="S185" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21186,7 +21187,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -21196,16 +21197,15 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD185" t="b">
         <v>0</v>
       </c>
       <c r="AE185" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF185" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
@@ -21223,57 +21223,54 @@
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949446</t>
+          <t>https://artportalen.se/Sighting/136949454</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>136949417</v>
+        <v>136949446</v>
       </c>
       <c r="B186" t="n">
-        <v>92567</v>
+        <v>87402</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>260575</v>
+        <v>249254</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Laxrosa ticka</t>
+          <t>Mospindling</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Aurantiporus priscus</t>
+          <t>Cortinarius areni-silvae</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Niemelä &amp; al.</t>
+          <t>(Brandrud) Brandrud</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Dödåsen, Hjd</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>436999</v>
+        <v>437118</v>
       </c>
       <c r="R186" t="n">
-        <v>6851612</v>
+        <v>6852026</v>
       </c>
       <c r="S186" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21302,7 +21299,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -21312,19 +21309,14 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>Minst tvååriga fruktkropp på kolad keloved. Rosa porlager med tydligt orange subiculum som reagerar körsbärsrött på koh. Den kommer skickas på sekvensering.</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD186" t="b">
         <v>0</v>
       </c>
       <c r="AE186" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="b">
@@ -21338,55 +21330,63 @@
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136949417</t>
+          <t>https://artportalen.se/Sighting/136949446</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>136944329</v>
+        <v>136949417</v>
       </c>
       <c r="B187" t="n">
-        <v>80397</v>
+        <v>92570</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>266179</v>
+        <v>260575</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Laxrosa ticka</t>
+        </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Lecidea subhumida</t>
+          <t>Aurantiporus priscus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Vain.</t>
+          <t>Niemelä &amp; al.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Dödåsen, Hjd</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>437364</v>
+        <v>436999</v>
       </c>
       <c r="R187" t="n">
-        <v>6851913</v>
+        <v>6851612</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -21425,7 +21425,12 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>Minst tvååriga fruktkropp på kolad keloved. Rosa porlager med tydligt orange subiculum som reagerar körsbärsrött på koh. Den kommer skickas på sekvensering.</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21434,22 +21439,130 @@
       <c r="AE187" t="b">
         <v>0</v>
       </c>
+      <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="b">
         <v>0</v>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
       <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136949417</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>136944329</v>
+      </c>
+      <c r="B188" t="n">
+        <v>80397</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Dödåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q188" t="n">
+        <v>437364</v>
+      </c>
+      <c r="R188" t="n">
+        <v>6851913</v>
+      </c>
+      <c r="S188" t="n">
+        <v>10</v>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT188" t="inlineStr"/>
+      <c r="AW188" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX188" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136944329</t>
         </is>
@@ -21643,6 +21756,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39408-2026 artfynd.xlsx
+++ b/artfynd/A 39408-2026 artfynd.xlsx
@@ -1329,7 +1329,7 @@
         <v>136944274</v>
       </c>
       <c r="B8" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>136944277</v>
       </c>
       <c r="B9" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136944289</v>
       </c>
       <c r="B10" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>136944294</v>
       </c>
       <c r="B11" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136944332</v>
       </c>
       <c r="B12" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136944383</v>
       </c>
       <c r="B13" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>136944393</v>
       </c>
       <c r="B14" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>136949427</v>
       </c>
       <c r="B16" t="n">
-        <v>79598</v>
+        <v>79608</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136944346</v>
       </c>
       <c r="B17" t="n">
-        <v>81472</v>
+        <v>81482</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>136944293</v>
       </c>
       <c r="B22" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>136949434</v>
       </c>
       <c r="B23" t="n">
-        <v>93479</v>
+        <v>93489</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>136944300</v>
       </c>
       <c r="B26" t="n">
-        <v>92201</v>
+        <v>92211</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>136949422</v>
       </c>
       <c r="B27" t="n">
-        <v>92201</v>
+        <v>92211</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>136949472</v>
       </c>
       <c r="B28" t="n">
-        <v>92201</v>
+        <v>92211</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>136944371</v>
       </c>
       <c r="B29" t="n">
-        <v>93470</v>
+        <v>93480</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>136944298</v>
       </c>
       <c r="B31" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>136949477</v>
       </c>
       <c r="B32" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>136949486</v>
       </c>
       <c r="B33" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>136944279</v>
       </c>
       <c r="B34" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>136944287</v>
       </c>
       <c r="B35" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>136944296</v>
       </c>
       <c r="B36" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>136944348</v>
       </c>
       <c r="B37" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>136944358</v>
       </c>
       <c r="B38" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>136944367</v>
       </c>
       <c r="B39" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>136944369</v>
       </c>
       <c r="B40" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>136949431</v>
       </c>
       <c r="B41" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>136949435</v>
       </c>
       <c r="B42" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>136949473</v>
       </c>
       <c r="B43" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>136949475</v>
       </c>
       <c r="B44" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>136944295</v>
       </c>
       <c r="B45" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>136944353</v>
       </c>
       <c r="B46" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>136944292</v>
       </c>
       <c r="B47" t="n">
-        <v>93090</v>
+        <v>93100</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>136944352</v>
       </c>
       <c r="B48" t="n">
-        <v>93090</v>
+        <v>93100</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>136949453</v>
       </c>
       <c r="B49" t="n">
-        <v>93090</v>
+        <v>93100</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>136949483</v>
       </c>
       <c r="B50" t="n">
-        <v>93090</v>
+        <v>93100</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>136949423</v>
       </c>
       <c r="B51" t="n">
-        <v>91068</v>
+        <v>91078</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>136949445</v>
       </c>
       <c r="B52" t="n">
-        <v>91068</v>
+        <v>91078</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>136944382</v>
       </c>
       <c r="B53" t="n">
-        <v>91502</v>
+        <v>91512</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>136944286</v>
       </c>
       <c r="B54" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>136944357</v>
       </c>
       <c r="B55" t="n">
-        <v>93429</v>
+        <v>93439</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>136944374</v>
       </c>
       <c r="B56" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>136944390</v>
       </c>
       <c r="B57" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>136944338</v>
       </c>
       <c r="B58" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>136944283</v>
       </c>
       <c r="B64" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>136944318</v>
       </c>
       <c r="B65" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         <v>136944320</v>
       </c>
       <c r="B66" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>136944340</v>
       </c>
       <c r="B67" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>136944344</v>
       </c>
       <c r="B68" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>136944365</v>
       </c>
       <c r="B69" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>136944380</v>
       </c>
       <c r="B70" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>136949416</v>
       </c>
       <c r="B71" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>136949418</v>
       </c>
       <c r="B72" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>136949429</v>
       </c>
       <c r="B73" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>136949433</v>
       </c>
       <c r="B74" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>136949436</v>
       </c>
       <c r="B75" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>136949440</v>
       </c>
       <c r="B76" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>136949441</v>
       </c>
       <c r="B77" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>136949480</v>
       </c>
       <c r="B78" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>136949482</v>
       </c>
       <c r="B79" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>136944282</v>
       </c>
       <c r="B80" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>136944308</v>
       </c>
       <c r="B81" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>136944323</v>
       </c>
       <c r="B82" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>136944342</v>
       </c>
       <c r="B83" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>136944356</v>
       </c>
       <c r="B84" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>136944363</v>
       </c>
       <c r="B85" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>136944379</v>
       </c>
       <c r="B86" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>136944385</v>
       </c>
       <c r="B87" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>136944275</v>
       </c>
       <c r="B88" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>136944280</v>
       </c>
       <c r="B89" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>136944288</v>
       </c>
       <c r="B90" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>136944290</v>
       </c>
       <c r="B91" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>136944297</v>
       </c>
       <c r="B92" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>136944301</v>
       </c>
       <c r="B93" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>136944305</v>
       </c>
       <c r="B94" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>136944307</v>
       </c>
       <c r="B95" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>136944310</v>
       </c>
       <c r="B96" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>136944311</v>
       </c>
       <c r="B97" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>136944315</v>
       </c>
       <c r="B98" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>136944316</v>
       </c>
       <c r="B99" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>136944330</v>
       </c>
       <c r="B100" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>136944331</v>
       </c>
       <c r="B101" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>136944333</v>
       </c>
       <c r="B102" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>136944347</v>
       </c>
       <c r="B103" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>136944349</v>
       </c>
       <c r="B104" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>136944359</v>
       </c>
       <c r="B105" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>136944361</v>
       </c>
       <c r="B106" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>136944362</v>
       </c>
       <c r="B107" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>136944366</v>
       </c>
       <c r="B108" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>136944370</v>
       </c>
       <c r="B109" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>136944372</v>
       </c>
       <c r="B110" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>136944381</v>
       </c>
       <c r="B111" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>136944384</v>
       </c>
       <c r="B112" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>136944389</v>
       </c>
       <c r="B113" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>136944391</v>
       </c>
       <c r="B114" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>136944394</v>
       </c>
       <c r="B115" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>136949419</v>
       </c>
       <c r="B116" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>136949421</v>
       </c>
       <c r="B117" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>136949424</v>
       </c>
       <c r="B118" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>136949438</v>
       </c>
       <c r="B119" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>136949442</v>
       </c>
       <c r="B120" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>136949443</v>
       </c>
       <c r="B121" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>136949444</v>
       </c>
       <c r="B122" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>136949449</v>
       </c>
       <c r="B123" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>136949450</v>
       </c>
       <c r="B124" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>136949451</v>
       </c>
       <c r="B125" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>136949452</v>
       </c>
       <c r="B126" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>136949465</v>
       </c>
       <c r="B127" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>136949467</v>
       </c>
       <c r="B128" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>136949468</v>
       </c>
       <c r="B129" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>136949470</v>
       </c>
       <c r="B130" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>136949471</v>
       </c>
       <c r="B131" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>136949476</v>
       </c>
       <c r="B132" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>136949484</v>
       </c>
       <c r="B133" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>136949426</v>
       </c>
       <c r="B136" t="n">
-        <v>78503</v>
+        <v>78513</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>136949430</v>
       </c>
       <c r="B137" t="n">
-        <v>78503</v>
+        <v>78513</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15839,7 +15839,7 @@
         <v>136949457</v>
       </c>
       <c r="B138" t="n">
-        <v>78503</v>
+        <v>78513</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>136949459</v>
       </c>
       <c r="B139" t="n">
-        <v>78503</v>
+        <v>78513</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>136949460</v>
       </c>
       <c r="B140" t="n">
-        <v>78503</v>
+        <v>78513</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>136944386</v>
       </c>
       <c r="B141" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>136944299</v>
       </c>
       <c r="B142" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>136944334</v>
       </c>
       <c r="B143" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>136944336</v>
       </c>
       <c r="B144" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>136944376</v>
       </c>
       <c r="B145" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>136949455</v>
       </c>
       <c r="B146" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>136944309</v>
       </c>
       <c r="B147" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>136944303</v>
       </c>
       <c r="B148" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>136944314</v>
       </c>
       <c r="B149" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>136944355</v>
       </c>
       <c r="B150" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>136944373</v>
       </c>
       <c r="B151" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>136944378</v>
       </c>
       <c r="B152" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>136944387</v>
       </c>
       <c r="B153" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>136944392</v>
       </c>
       <c r="B154" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17755,7 +17755,7 @@
         <v>136944281</v>
       </c>
       <c r="B155" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>136944302</v>
       </c>
       <c r="B156" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17979,7 +17979,7 @@
         <v>136944317</v>
       </c>
       <c r="B157" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>136944328</v>
       </c>
       <c r="B158" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18203,7 +18203,7 @@
         <v>136944337</v>
       </c>
       <c r="B159" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>136944339</v>
       </c>
       <c r="B160" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>136944345</v>
       </c>
       <c r="B161" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>136944350</v>
       </c>
       <c r="B162" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>136944351</v>
       </c>
       <c r="B163" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>136944368</v>
       </c>
       <c r="B164" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>136944375</v>
       </c>
       <c r="B165" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>136944377</v>
       </c>
       <c r="B166" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>136944388</v>
       </c>
       <c r="B167" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>136949420</v>
       </c>
       <c r="B168" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>136949425</v>
       </c>
       <c r="B169" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>136949428</v>
       </c>
       <c r="B170" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>136949432</v>
       </c>
       <c r="B171" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>136949437</v>
       </c>
       <c r="B172" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>136949439</v>
       </c>
       <c r="B173" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>136949448</v>
       </c>
       <c r="B174" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>136949456</v>
       </c>
       <c r="B175" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>136949461</v>
       </c>
       <c r="B176" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>136949462</v>
       </c>
       <c r="B177" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>136949464</v>
       </c>
       <c r="B178" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>136949466</v>
       </c>
       <c r="B179" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>136949469</v>
       </c>
       <c r="B180" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>136949474</v>
       </c>
       <c r="B181" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20784,7 +20784,7 @@
         <v>136949478</v>
       </c>
       <c r="B182" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>136949479</v>
       </c>
       <c r="B183" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>136949481</v>
       </c>
       <c r="B184" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>136949454</v>
       </c>
       <c r="B185" t="n">
-        <v>93476</v>
+        <v>93486</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
         <v>136949446</v>
       </c>
       <c r="B186" t="n">
-        <v>87402</v>
+        <v>87412</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>136949417</v>
       </c>
       <c r="B187" t="n">
-        <v>92570</v>
+        <v>92580</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>136944329</v>
       </c>
       <c r="B188" t="n">
-        <v>80397</v>
+        <v>80407</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>

--- a/artfynd/A 39408-2026 artfynd.xlsx
+++ b/artfynd/A 39408-2026 artfynd.xlsx
@@ -2872,7 +2872,7 @@
         <v>136944293</v>
       </c>
       <c r="B22" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>136949434</v>
       </c>
       <c r="B23" t="n">
-        <v>93489</v>
+        <v>93490</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>136944300</v>
       </c>
       <c r="B26" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>136949422</v>
       </c>
       <c r="B27" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>136949472</v>
       </c>
       <c r="B28" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>136944371</v>
       </c>
       <c r="B29" t="n">
-        <v>93480</v>
+        <v>93481</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>136944298</v>
       </c>
       <c r="B31" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>136949477</v>
       </c>
       <c r="B32" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>136949486</v>
       </c>
       <c r="B33" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>136944279</v>
       </c>
       <c r="B34" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>136944287</v>
       </c>
       <c r="B35" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>136944296</v>
       </c>
       <c r="B36" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>136944348</v>
       </c>
       <c r="B37" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>136944358</v>
       </c>
       <c r="B38" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>136944367</v>
       </c>
       <c r="B39" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>136944369</v>
       </c>
       <c r="B40" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>136949431</v>
       </c>
       <c r="B41" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>136949435</v>
       </c>
       <c r="B42" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>136949473</v>
       </c>
       <c r="B43" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>136949475</v>
       </c>
       <c r="B44" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>136944295</v>
       </c>
       <c r="B45" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>136944353</v>
       </c>
       <c r="B46" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>136944292</v>
       </c>
       <c r="B47" t="n">
-        <v>93100</v>
+        <v>93101</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>136944352</v>
       </c>
       <c r="B48" t="n">
-        <v>93100</v>
+        <v>93101</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>136949453</v>
       </c>
       <c r="B49" t="n">
-        <v>93100</v>
+        <v>93101</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>136949483</v>
       </c>
       <c r="B50" t="n">
-        <v>93100</v>
+        <v>93101</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>136949423</v>
       </c>
       <c r="B51" t="n">
-        <v>91078</v>
+        <v>91079</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>136949445</v>
       </c>
       <c r="B52" t="n">
-        <v>91078</v>
+        <v>91079</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>136944382</v>
       </c>
       <c r="B53" t="n">
-        <v>91512</v>
+        <v>91513</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>136944286</v>
       </c>
       <c r="B54" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>136944357</v>
       </c>
       <c r="B55" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>136944374</v>
       </c>
       <c r="B56" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>136944309</v>
       </c>
       <c r="B147" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>136949454</v>
       </c>
       <c r="B185" t="n">
-        <v>93486</v>
+        <v>93487</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
         <v>136949446</v>
       </c>
       <c r="B186" t="n">
-        <v>87412</v>
+        <v>87413</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>136949417</v>
       </c>
       <c r="B187" t="n">
-        <v>92580</v>
+        <v>92581</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>

--- a/artfynd/A 39408-2026 artfynd.xlsx
+++ b/artfynd/A 39408-2026 artfynd.xlsx
@@ -1329,7 +1329,7 @@
         <v>136944274</v>
       </c>
       <c r="B8" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>136944277</v>
       </c>
       <c r="B9" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136944289</v>
       </c>
       <c r="B10" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>136944294</v>
       </c>
       <c r="B11" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136944332</v>
       </c>
       <c r="B12" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136944383</v>
       </c>
       <c r="B13" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>136944393</v>
       </c>
       <c r="B14" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>136949427</v>
       </c>
       <c r="B16" t="n">
-        <v>79608</v>
+        <v>79611</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136944346</v>
       </c>
       <c r="B17" t="n">
-        <v>81482</v>
+        <v>81485</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>136944293</v>
       </c>
       <c r="B22" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>136949434</v>
       </c>
       <c r="B23" t="n">
-        <v>93490</v>
+        <v>93495</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>136944300</v>
       </c>
       <c r="B26" t="n">
-        <v>92212</v>
+        <v>92215</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>136949422</v>
       </c>
       <c r="B27" t="n">
-        <v>92212</v>
+        <v>92215</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>136949472</v>
       </c>
       <c r="B28" t="n">
-        <v>92212</v>
+        <v>92215</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>136944371</v>
       </c>
       <c r="B29" t="n">
-        <v>93481</v>
+        <v>93486</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>136944298</v>
       </c>
       <c r="B31" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>136949477</v>
       </c>
       <c r="B32" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>136949486</v>
       </c>
       <c r="B33" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>136944279</v>
       </c>
       <c r="B34" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>136944287</v>
       </c>
       <c r="B35" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>136944296</v>
       </c>
       <c r="B36" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>136944348</v>
       </c>
       <c r="B37" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>136944358</v>
       </c>
       <c r="B38" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>136944367</v>
       </c>
       <c r="B39" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>136944369</v>
       </c>
       <c r="B40" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>136949431</v>
       </c>
       <c r="B41" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>136949435</v>
       </c>
       <c r="B42" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>136949473</v>
       </c>
       <c r="B43" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>136949475</v>
       </c>
       <c r="B44" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>136944295</v>
       </c>
       <c r="B45" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>136944353</v>
       </c>
       <c r="B46" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>136944292</v>
       </c>
       <c r="B47" t="n">
-        <v>93101</v>
+        <v>93104</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>136944352</v>
       </c>
       <c r="B48" t="n">
-        <v>93101</v>
+        <v>93104</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>136949453</v>
       </c>
       <c r="B49" t="n">
-        <v>93101</v>
+        <v>93104</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>136949483</v>
       </c>
       <c r="B50" t="n">
-        <v>93101</v>
+        <v>93104</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>136949423</v>
       </c>
       <c r="B51" t="n">
-        <v>91079</v>
+        <v>91082</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>136949445</v>
       </c>
       <c r="B52" t="n">
-        <v>91079</v>
+        <v>91082</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>136944382</v>
       </c>
       <c r="B53" t="n">
-        <v>91513</v>
+        <v>91516</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>136944286</v>
       </c>
       <c r="B54" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>136944357</v>
       </c>
       <c r="B55" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>136944374</v>
       </c>
       <c r="B56" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>136944390</v>
       </c>
       <c r="B57" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>136944338</v>
       </c>
       <c r="B58" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>136944283</v>
       </c>
       <c r="B64" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>136944318</v>
       </c>
       <c r="B65" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         <v>136944320</v>
       </c>
       <c r="B66" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>136944340</v>
       </c>
       <c r="B67" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>136944344</v>
       </c>
       <c r="B68" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>136944365</v>
       </c>
       <c r="B69" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>136944380</v>
       </c>
       <c r="B70" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>136949416</v>
       </c>
       <c r="B71" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>136949418</v>
       </c>
       <c r="B72" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>136949429</v>
       </c>
       <c r="B73" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>136949433</v>
       </c>
       <c r="B74" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>136949436</v>
       </c>
       <c r="B75" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>136949440</v>
       </c>
       <c r="B76" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>136949441</v>
       </c>
       <c r="B77" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>136949480</v>
       </c>
       <c r="B78" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>136949482</v>
       </c>
       <c r="B79" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>136944282</v>
       </c>
       <c r="B80" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>136944308</v>
       </c>
       <c r="B81" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>136944323</v>
       </c>
       <c r="B82" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>136944342</v>
       </c>
       <c r="B83" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>136944356</v>
       </c>
       <c r="B84" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>136944363</v>
       </c>
       <c r="B85" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>136944379</v>
       </c>
       <c r="B86" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>136944385</v>
       </c>
       <c r="B87" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>136944275</v>
       </c>
       <c r="B88" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>136944280</v>
       </c>
       <c r="B89" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>136944288</v>
       </c>
       <c r="B90" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>136944290</v>
       </c>
       <c r="B91" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>136944297</v>
       </c>
       <c r="B92" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>136944301</v>
       </c>
       <c r="B93" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>136944305</v>
       </c>
       <c r="B94" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>136944307</v>
       </c>
       <c r="B95" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>136944310</v>
       </c>
       <c r="B96" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>136944311</v>
       </c>
       <c r="B97" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>136944315</v>
       </c>
       <c r="B98" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>136944316</v>
       </c>
       <c r="B99" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>136944330</v>
       </c>
       <c r="B100" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>136944331</v>
       </c>
       <c r="B101" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>136944333</v>
       </c>
       <c r="B102" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>136944347</v>
       </c>
       <c r="B103" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>136944349</v>
       </c>
       <c r="B104" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>136944359</v>
       </c>
       <c r="B105" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>136944361</v>
       </c>
       <c r="B106" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>136944362</v>
       </c>
       <c r="B107" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>136944366</v>
       </c>
       <c r="B108" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>136944370</v>
       </c>
       <c r="B109" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>136944372</v>
       </c>
       <c r="B110" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>136944381</v>
       </c>
       <c r="B111" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>136944384</v>
       </c>
       <c r="B112" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>136944389</v>
       </c>
       <c r="B113" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>136944391</v>
       </c>
       <c r="B114" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>136944394</v>
       </c>
       <c r="B115" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>136949419</v>
       </c>
       <c r="B116" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>136949421</v>
       </c>
       <c r="B117" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>136949424</v>
       </c>
       <c r="B118" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>136949438</v>
       </c>
       <c r="B119" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>136949442</v>
       </c>
       <c r="B120" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>136949443</v>
       </c>
       <c r="B121" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>136949444</v>
       </c>
       <c r="B122" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>136949449</v>
       </c>
       <c r="B123" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>136949450</v>
       </c>
       <c r="B124" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>136949451</v>
       </c>
       <c r="B125" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>136949452</v>
       </c>
       <c r="B126" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>136949465</v>
       </c>
       <c r="B127" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>136949467</v>
       </c>
       <c r="B128" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>136949468</v>
       </c>
       <c r="B129" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>136949470</v>
       </c>
       <c r="B130" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>136949471</v>
       </c>
       <c r="B131" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>136949476</v>
       </c>
       <c r="B132" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>136949484</v>
       </c>
       <c r="B133" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>136949426</v>
       </c>
       <c r="B136" t="n">
-        <v>78513</v>
+        <v>78516</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>136949430</v>
       </c>
       <c r="B137" t="n">
-        <v>78513</v>
+        <v>78516</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15839,7 +15839,7 @@
         <v>136949457</v>
       </c>
       <c r="B138" t="n">
-        <v>78513</v>
+        <v>78516</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>136949459</v>
       </c>
       <c r="B139" t="n">
-        <v>78513</v>
+        <v>78516</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>136949460</v>
       </c>
       <c r="B140" t="n">
-        <v>78513</v>
+        <v>78516</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>136944386</v>
       </c>
       <c r="B141" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>136944299</v>
       </c>
       <c r="B142" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>136944334</v>
       </c>
       <c r="B143" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>136944336</v>
       </c>
       <c r="B144" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>136944376</v>
       </c>
       <c r="B145" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>136949455</v>
       </c>
       <c r="B146" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>136944309</v>
       </c>
       <c r="B147" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>136944303</v>
       </c>
       <c r="B148" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>136944314</v>
       </c>
       <c r="B149" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>136944355</v>
       </c>
       <c r="B150" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>136944373</v>
       </c>
       <c r="B151" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>136944378</v>
       </c>
       <c r="B152" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>136944387</v>
       </c>
       <c r="B153" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>136944392</v>
       </c>
       <c r="B154" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17755,7 +17755,7 @@
         <v>136944281</v>
       </c>
       <c r="B155" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>136944302</v>
       </c>
       <c r="B156" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17979,7 +17979,7 @@
         <v>136944317</v>
       </c>
       <c r="B157" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>136944328</v>
       </c>
       <c r="B158" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18203,7 +18203,7 @@
         <v>136944337</v>
       </c>
       <c r="B159" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>136944339</v>
       </c>
       <c r="B160" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>136944345</v>
       </c>
       <c r="B161" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>136944350</v>
       </c>
       <c r="B162" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>136944351</v>
       </c>
       <c r="B163" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>136944368</v>
       </c>
       <c r="B164" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>136944375</v>
       </c>
       <c r="B165" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>136944377</v>
       </c>
       <c r="B166" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>136944388</v>
       </c>
       <c r="B167" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>136949420</v>
       </c>
       <c r="B168" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>136949425</v>
       </c>
       <c r="B169" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>136949428</v>
       </c>
       <c r="B170" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>136949432</v>
       </c>
       <c r="B171" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>136949437</v>
       </c>
       <c r="B172" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>136949439</v>
       </c>
       <c r="B173" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>136949448</v>
       </c>
       <c r="B174" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>136949456</v>
       </c>
       <c r="B175" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>136949461</v>
       </c>
       <c r="B176" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>136949462</v>
       </c>
       <c r="B177" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>136949464</v>
       </c>
       <c r="B178" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>136949466</v>
       </c>
       <c r="B179" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>136949469</v>
       </c>
       <c r="B180" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>136949474</v>
       </c>
       <c r="B181" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20784,7 +20784,7 @@
         <v>136949478</v>
       </c>
       <c r="B182" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>136949479</v>
       </c>
       <c r="B183" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>136949481</v>
       </c>
       <c r="B184" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>136949454</v>
       </c>
       <c r="B185" t="n">
-        <v>93487</v>
+        <v>93492</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
         <v>136949446</v>
       </c>
       <c r="B186" t="n">
-        <v>87413</v>
+        <v>87416</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>136949417</v>
       </c>
       <c r="B187" t="n">
-        <v>92581</v>
+        <v>92584</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>136944329</v>
       </c>
       <c r="B188" t="n">
-        <v>80407</v>
+        <v>80410</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>

--- a/artfynd/A 39408-2026 artfynd.xlsx
+++ b/artfynd/A 39408-2026 artfynd.xlsx
@@ -2872,7 +2872,7 @@
         <v>136944293</v>
       </c>
       <c r="B22" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>136949434</v>
       </c>
       <c r="B23" t="n">
-        <v>93495</v>
+        <v>93497</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>136944300</v>
       </c>
       <c r="B26" t="n">
-        <v>92215</v>
+        <v>92217</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>136949422</v>
       </c>
       <c r="B27" t="n">
-        <v>92215</v>
+        <v>92217</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>136949472</v>
       </c>
       <c r="B28" t="n">
-        <v>92215</v>
+        <v>92217</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>136944371</v>
       </c>
       <c r="B29" t="n">
-        <v>93486</v>
+        <v>93488</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>136944298</v>
       </c>
       <c r="B31" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>136949477</v>
       </c>
       <c r="B32" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>136949486</v>
       </c>
       <c r="B33" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>136944279</v>
       </c>
       <c r="B34" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>136944287</v>
       </c>
       <c r="B35" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>136944296</v>
       </c>
       <c r="B36" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>136944348</v>
       </c>
       <c r="B37" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>136944358</v>
       </c>
       <c r="B38" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>136944367</v>
       </c>
       <c r="B39" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>136944369</v>
       </c>
       <c r="B40" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>136949431</v>
       </c>
       <c r="B41" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>136949435</v>
       </c>
       <c r="B42" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>136949473</v>
       </c>
       <c r="B43" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>136949475</v>
       </c>
       <c r="B44" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>136944295</v>
       </c>
       <c r="B45" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>136944353</v>
       </c>
       <c r="B46" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>136944292</v>
       </c>
       <c r="B47" t="n">
-        <v>93104</v>
+        <v>93106</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>136944352</v>
       </c>
       <c r="B48" t="n">
-        <v>93104</v>
+        <v>93106</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>136949453</v>
       </c>
       <c r="B49" t="n">
-        <v>93104</v>
+        <v>93106</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>136949483</v>
       </c>
       <c r="B50" t="n">
-        <v>93104</v>
+        <v>93106</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>136949423</v>
       </c>
       <c r="B51" t="n">
-        <v>91082</v>
+        <v>91084</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>136949445</v>
       </c>
       <c r="B52" t="n">
-        <v>91082</v>
+        <v>91084</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>136944382</v>
       </c>
       <c r="B53" t="n">
-        <v>91516</v>
+        <v>91518</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>136944286</v>
       </c>
       <c r="B54" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>136944357</v>
       </c>
       <c r="B55" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>136944374</v>
       </c>
       <c r="B56" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>136944309</v>
       </c>
       <c r="B147" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>136949454</v>
       </c>
       <c r="B185" t="n">
-        <v>93492</v>
+        <v>93494</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>136949417</v>
       </c>
       <c r="B187" t="n">
-        <v>92584</v>
+        <v>92586</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>

--- a/artfynd/A 39408-2026 artfynd.xlsx
+++ b/artfynd/A 39408-2026 artfynd.xlsx
@@ -1329,7 +1329,7 @@
         <v>136944274</v>
       </c>
       <c r="B8" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>136944277</v>
       </c>
       <c r="B9" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136944289</v>
       </c>
       <c r="B10" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>136944294</v>
       </c>
       <c r="B11" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136944332</v>
       </c>
       <c r="B12" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136944383</v>
       </c>
       <c r="B13" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>136944393</v>
       </c>
       <c r="B14" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>136949427</v>
       </c>
       <c r="B16" t="n">
-        <v>79611</v>
+        <v>79616</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136944346</v>
       </c>
       <c r="B17" t="n">
-        <v>81485</v>
+        <v>81490</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>136944293</v>
       </c>
       <c r="B22" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>136949434</v>
       </c>
       <c r="B23" t="n">
-        <v>93497</v>
+        <v>93503</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>136944300</v>
       </c>
       <c r="B26" t="n">
-        <v>92217</v>
+        <v>92222</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>136949422</v>
       </c>
       <c r="B27" t="n">
-        <v>92217</v>
+        <v>92222</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>136949472</v>
       </c>
       <c r="B28" t="n">
-        <v>92217</v>
+        <v>92222</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>136944371</v>
       </c>
       <c r="B29" t="n">
-        <v>93488</v>
+        <v>93494</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>136944298</v>
       </c>
       <c r="B31" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>136949477</v>
       </c>
       <c r="B32" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>136949486</v>
       </c>
       <c r="B33" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>136944279</v>
       </c>
       <c r="B34" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>136944287</v>
       </c>
       <c r="B35" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>136944296</v>
       </c>
       <c r="B36" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>136944348</v>
       </c>
       <c r="B37" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>136944358</v>
       </c>
       <c r="B38" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>136944367</v>
       </c>
       <c r="B39" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>136944369</v>
       </c>
       <c r="B40" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>136949431</v>
       </c>
       <c r="B41" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>136949435</v>
       </c>
       <c r="B42" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>136949473</v>
       </c>
       <c r="B43" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>136949475</v>
       </c>
       <c r="B44" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>136944295</v>
       </c>
       <c r="B45" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>136944353</v>
       </c>
       <c r="B46" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>136944292</v>
       </c>
       <c r="B47" t="n">
-        <v>93106</v>
+        <v>93112</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>136944352</v>
       </c>
       <c r="B48" t="n">
-        <v>93106</v>
+        <v>93112</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>136949453</v>
       </c>
       <c r="B49" t="n">
-        <v>93106</v>
+        <v>93112</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>136949483</v>
       </c>
       <c r="B50" t="n">
-        <v>93106</v>
+        <v>93112</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>136949423</v>
       </c>
       <c r="B51" t="n">
-        <v>91084</v>
+        <v>91089</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>136949445</v>
       </c>
       <c r="B52" t="n">
-        <v>91084</v>
+        <v>91089</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>136944382</v>
       </c>
       <c r="B53" t="n">
-        <v>91518</v>
+        <v>91523</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>136944286</v>
       </c>
       <c r="B54" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>136944357</v>
       </c>
       <c r="B55" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>136944374</v>
       </c>
       <c r="B56" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>136944390</v>
       </c>
       <c r="B57" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>136944338</v>
       </c>
       <c r="B58" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>136944283</v>
       </c>
       <c r="B64" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>136944318</v>
       </c>
       <c r="B65" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         <v>136944320</v>
       </c>
       <c r="B66" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>136944340</v>
       </c>
       <c r="B67" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>136944344</v>
       </c>
       <c r="B68" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>136944365</v>
       </c>
       <c r="B69" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>136944380</v>
       </c>
       <c r="B70" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>136949416</v>
       </c>
       <c r="B71" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>136949418</v>
       </c>
       <c r="B72" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>136949429</v>
       </c>
       <c r="B73" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>136949433</v>
       </c>
       <c r="B74" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>136949436</v>
       </c>
       <c r="B75" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>136949440</v>
       </c>
       <c r="B76" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>136949441</v>
       </c>
       <c r="B77" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>136949480</v>
       </c>
       <c r="B78" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>136949482</v>
       </c>
       <c r="B79" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>136944282</v>
       </c>
       <c r="B80" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>136944308</v>
       </c>
       <c r="B81" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>136944323</v>
       </c>
       <c r="B82" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>136944342</v>
       </c>
       <c r="B83" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>136944356</v>
       </c>
       <c r="B84" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>136944363</v>
       </c>
       <c r="B85" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>136944379</v>
       </c>
       <c r="B86" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>136944385</v>
       </c>
       <c r="B87" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>136944275</v>
       </c>
       <c r="B88" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>136944280</v>
       </c>
       <c r="B89" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>136944288</v>
       </c>
       <c r="B90" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>136944290</v>
       </c>
       <c r="B91" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>136944297</v>
       </c>
       <c r="B92" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>136944301</v>
       </c>
       <c r="B93" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>136944305</v>
       </c>
       <c r="B94" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>136944307</v>
       </c>
       <c r="B95" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>136944310</v>
       </c>
       <c r="B96" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>136944311</v>
       </c>
       <c r="B97" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>136944315</v>
       </c>
       <c r="B98" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>136944316</v>
       </c>
       <c r="B99" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>136944330</v>
       </c>
       <c r="B100" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>136944331</v>
       </c>
       <c r="B101" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>136944333</v>
       </c>
       <c r="B102" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>136944347</v>
       </c>
       <c r="B103" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>136944349</v>
       </c>
       <c r="B104" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>136944359</v>
       </c>
       <c r="B105" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>136944361</v>
       </c>
       <c r="B106" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>136944362</v>
       </c>
       <c r="B107" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>136944366</v>
       </c>
       <c r="B108" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>136944370</v>
       </c>
       <c r="B109" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>136944372</v>
       </c>
       <c r="B110" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>136944381</v>
       </c>
       <c r="B111" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>136944384</v>
       </c>
       <c r="B112" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>136944389</v>
       </c>
       <c r="B113" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>136944391</v>
       </c>
       <c r="B114" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>136944394</v>
       </c>
       <c r="B115" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>136949419</v>
       </c>
       <c r="B116" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>136949421</v>
       </c>
       <c r="B117" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>136949424</v>
       </c>
       <c r="B118" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>136949438</v>
       </c>
       <c r="B119" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>136949442</v>
       </c>
       <c r="B120" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>136949443</v>
       </c>
       <c r="B121" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>136949444</v>
       </c>
       <c r="B122" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>136949449</v>
       </c>
       <c r="B123" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>136949450</v>
       </c>
       <c r="B124" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>136949451</v>
       </c>
       <c r="B125" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>136949452</v>
       </c>
       <c r="B126" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>136949465</v>
       </c>
       <c r="B127" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>136949467</v>
       </c>
       <c r="B128" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>136949468</v>
       </c>
       <c r="B129" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>136949470</v>
       </c>
       <c r="B130" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>136949471</v>
       </c>
       <c r="B131" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>136949476</v>
       </c>
       <c r="B132" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>136949484</v>
       </c>
       <c r="B133" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>136949426</v>
       </c>
       <c r="B136" t="n">
-        <v>78516</v>
+        <v>78521</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>136949430</v>
       </c>
       <c r="B137" t="n">
-        <v>78516</v>
+        <v>78521</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15839,7 +15839,7 @@
         <v>136949457</v>
       </c>
       <c r="B138" t="n">
-        <v>78516</v>
+        <v>78521</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>136949459</v>
       </c>
       <c r="B139" t="n">
-        <v>78516</v>
+        <v>78521</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>136949460</v>
       </c>
       <c r="B140" t="n">
-        <v>78516</v>
+        <v>78521</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>136944386</v>
       </c>
       <c r="B141" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>136944299</v>
       </c>
       <c r="B142" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>136944334</v>
       </c>
       <c r="B143" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>136944336</v>
       </c>
       <c r="B144" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>136944376</v>
       </c>
       <c r="B145" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>136949455</v>
       </c>
       <c r="B146" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>136944309</v>
       </c>
       <c r="B147" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>136944303</v>
       </c>
       <c r="B148" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>136944314</v>
       </c>
       <c r="B149" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>136944355</v>
       </c>
       <c r="B150" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>136944373</v>
       </c>
       <c r="B151" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>136944378</v>
       </c>
       <c r="B152" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>136944387</v>
       </c>
       <c r="B153" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>136944392</v>
       </c>
       <c r="B154" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17755,7 +17755,7 @@
         <v>136944281</v>
       </c>
       <c r="B155" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>136944302</v>
       </c>
       <c r="B156" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17979,7 +17979,7 @@
         <v>136944317</v>
       </c>
       <c r="B157" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>136944328</v>
       </c>
       <c r="B158" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18203,7 +18203,7 @@
         <v>136944337</v>
       </c>
       <c r="B159" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>136944339</v>
       </c>
       <c r="B160" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>136944345</v>
       </c>
       <c r="B161" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>136944350</v>
       </c>
       <c r="B162" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>136944351</v>
       </c>
       <c r="B163" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>136944368</v>
       </c>
       <c r="B164" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>136944375</v>
       </c>
       <c r="B165" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>136944377</v>
       </c>
       <c r="B166" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>136944388</v>
       </c>
       <c r="B167" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>136949420</v>
       </c>
       <c r="B168" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>136949425</v>
       </c>
       <c r="B169" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>136949428</v>
       </c>
       <c r="B170" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>136949432</v>
       </c>
       <c r="B171" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>136949437</v>
       </c>
       <c r="B172" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>136949439</v>
       </c>
       <c r="B173" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>136949448</v>
       </c>
       <c r="B174" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>136949456</v>
       </c>
       <c r="B175" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>136949461</v>
       </c>
       <c r="B176" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>136949462</v>
       </c>
       <c r="B177" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>136949464</v>
       </c>
       <c r="B178" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>136949466</v>
       </c>
       <c r="B179" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>136949469</v>
       </c>
       <c r="B180" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>136949474</v>
       </c>
       <c r="B181" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20784,7 +20784,7 @@
         <v>136949478</v>
       </c>
       <c r="B182" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>136949479</v>
       </c>
       <c r="B183" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>136949481</v>
       </c>
       <c r="B184" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>136949454</v>
       </c>
       <c r="B185" t="n">
-        <v>93494</v>
+        <v>93500</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
         <v>136949446</v>
       </c>
       <c r="B186" t="n">
-        <v>87416</v>
+        <v>87421</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>136949417</v>
       </c>
       <c r="B187" t="n">
-        <v>92586</v>
+        <v>92591</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>136944329</v>
       </c>
       <c r="B188" t="n">
-        <v>80410</v>
+        <v>80415</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>

--- a/artfynd/A 39408-2026 artfynd.xlsx
+++ b/artfynd/A 39408-2026 artfynd.xlsx
@@ -1329,7 +1329,7 @@
         <v>136944274</v>
       </c>
       <c r="B8" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>136944277</v>
       </c>
       <c r="B9" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136944289</v>
       </c>
       <c r="B10" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>136944294</v>
       </c>
       <c r="B11" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136944332</v>
       </c>
       <c r="B12" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136944383</v>
       </c>
       <c r="B13" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>136944393</v>
       </c>
       <c r="B14" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>136949427</v>
       </c>
       <c r="B16" t="n">
-        <v>79616</v>
+        <v>79627</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136944346</v>
       </c>
       <c r="B17" t="n">
-        <v>81490</v>
+        <v>81501</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>136944293</v>
       </c>
       <c r="B22" t="n">
-        <v>92348</v>
+        <v>92360</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>136949434</v>
       </c>
       <c r="B23" t="n">
-        <v>93503</v>
+        <v>93515</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>136944300</v>
       </c>
       <c r="B26" t="n">
-        <v>92222</v>
+        <v>92234</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>136949422</v>
       </c>
       <c r="B27" t="n">
-        <v>92222</v>
+        <v>92234</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>136949472</v>
       </c>
       <c r="B28" t="n">
-        <v>92222</v>
+        <v>92234</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>136944371</v>
       </c>
       <c r="B29" t="n">
-        <v>93494</v>
+        <v>93506</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>136944298</v>
       </c>
       <c r="B31" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>136949477</v>
       </c>
       <c r="B32" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>136949486</v>
       </c>
       <c r="B33" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>136944279</v>
       </c>
       <c r="B34" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>136944287</v>
       </c>
       <c r="B35" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>136944296</v>
       </c>
       <c r="B36" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>136944348</v>
       </c>
       <c r="B37" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>136944358</v>
       </c>
       <c r="B38" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>136944367</v>
       </c>
       <c r="B39" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>136944369</v>
       </c>
       <c r="B40" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>136949431</v>
       </c>
       <c r="B41" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>136949435</v>
       </c>
       <c r="B42" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>136949473</v>
       </c>
       <c r="B43" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>136949475</v>
       </c>
       <c r="B44" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>136944295</v>
       </c>
       <c r="B45" t="n">
-        <v>93473</v>
+        <v>93485</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>136944353</v>
       </c>
       <c r="B46" t="n">
-        <v>93473</v>
+        <v>93485</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>136944292</v>
       </c>
       <c r="B47" t="n">
-        <v>93112</v>
+        <v>93124</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>136944352</v>
       </c>
       <c r="B48" t="n">
-        <v>93112</v>
+        <v>93124</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>136949453</v>
       </c>
       <c r="B49" t="n">
-        <v>93112</v>
+        <v>93124</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>136949483</v>
       </c>
       <c r="B50" t="n">
-        <v>93112</v>
+        <v>93124</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>136949423</v>
       </c>
       <c r="B51" t="n">
-        <v>91089</v>
+        <v>91101</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>136949445</v>
       </c>
       <c r="B52" t="n">
-        <v>91089</v>
+        <v>91101</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>136944382</v>
       </c>
       <c r="B53" t="n">
-        <v>91523</v>
+        <v>91535</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>136944286</v>
       </c>
       <c r="B54" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>136944357</v>
       </c>
       <c r="B55" t="n">
-        <v>93453</v>
+        <v>93465</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>136944374</v>
       </c>
       <c r="B56" t="n">
-        <v>90951</v>
+        <v>90963</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>136944390</v>
       </c>
       <c r="B57" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>136944338</v>
       </c>
       <c r="B58" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>136944283</v>
       </c>
       <c r="B64" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>136944318</v>
       </c>
       <c r="B65" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         <v>136944320</v>
       </c>
       <c r="B66" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>136944340</v>
       </c>
       <c r="B67" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>136944344</v>
       </c>
       <c r="B68" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>136944365</v>
       </c>
       <c r="B69" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>136944380</v>
       </c>
       <c r="B70" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>136949416</v>
       </c>
       <c r="B71" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>136949418</v>
       </c>
       <c r="B72" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>136949429</v>
       </c>
       <c r="B73" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>136949433</v>
       </c>
       <c r="B74" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>136949436</v>
       </c>
       <c r="B75" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>136949440</v>
       </c>
       <c r="B76" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>136949441</v>
       </c>
       <c r="B77" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>136949480</v>
       </c>
       <c r="B78" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>136949482</v>
       </c>
       <c r="B79" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>136944282</v>
       </c>
       <c r="B80" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>136944308</v>
       </c>
       <c r="B81" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>136944323</v>
       </c>
       <c r="B82" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>136944342</v>
       </c>
       <c r="B83" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>136944356</v>
       </c>
       <c r="B84" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>136944363</v>
       </c>
       <c r="B85" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>136944379</v>
       </c>
       <c r="B86" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>136944385</v>
       </c>
       <c r="B87" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>136944275</v>
       </c>
       <c r="B88" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>136944280</v>
       </c>
       <c r="B89" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>136944288</v>
       </c>
       <c r="B90" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>136944290</v>
       </c>
       <c r="B91" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>136944297</v>
       </c>
       <c r="B92" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>136944301</v>
       </c>
       <c r="B93" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>136944305</v>
       </c>
       <c r="B94" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>136944307</v>
       </c>
       <c r="B95" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>136944310</v>
       </c>
       <c r="B96" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>136944311</v>
       </c>
       <c r="B97" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>136944315</v>
       </c>
       <c r="B98" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>136944316</v>
       </c>
       <c r="B99" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>136944330</v>
       </c>
       <c r="B100" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>136944331</v>
       </c>
       <c r="B101" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>136944333</v>
       </c>
       <c r="B102" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>136944347</v>
       </c>
       <c r="B103" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>136944349</v>
       </c>
       <c r="B104" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>136944359</v>
       </c>
       <c r="B105" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>136944361</v>
       </c>
       <c r="B106" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>136944362</v>
       </c>
       <c r="B107" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>136944366</v>
       </c>
       <c r="B108" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>136944370</v>
       </c>
       <c r="B109" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>136944372</v>
       </c>
       <c r="B110" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>136944381</v>
       </c>
       <c r="B111" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>136944384</v>
       </c>
       <c r="B112" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>136944389</v>
       </c>
       <c r="B113" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>136944391</v>
       </c>
       <c r="B114" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>136944394</v>
       </c>
       <c r="B115" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>136949419</v>
       </c>
       <c r="B116" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>136949421</v>
       </c>
       <c r="B117" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>136949424</v>
       </c>
       <c r="B118" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>136949438</v>
       </c>
       <c r="B119" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>136949442</v>
       </c>
       <c r="B120" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>136949443</v>
       </c>
       <c r="B121" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>136949444</v>
       </c>
       <c r="B122" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>136949449</v>
       </c>
       <c r="B123" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>136949450</v>
       </c>
       <c r="B124" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>136949451</v>
       </c>
       <c r="B125" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>136949452</v>
       </c>
       <c r="B126" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>136949465</v>
       </c>
       <c r="B127" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>136949467</v>
       </c>
       <c r="B128" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>136949468</v>
       </c>
       <c r="B129" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>136949470</v>
       </c>
       <c r="B130" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>136949471</v>
       </c>
       <c r="B131" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>136949476</v>
       </c>
       <c r="B132" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>136949484</v>
       </c>
       <c r="B133" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>136949426</v>
       </c>
       <c r="B136" t="n">
-        <v>78521</v>
+        <v>78532</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>136949430</v>
       </c>
       <c r="B137" t="n">
-        <v>78521</v>
+        <v>78532</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15839,7 +15839,7 @@
         <v>136949457</v>
       </c>
       <c r="B138" t="n">
-        <v>78521</v>
+        <v>78532</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>136949459</v>
       </c>
       <c r="B139" t="n">
-        <v>78521</v>
+        <v>78532</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>136949460</v>
       </c>
       <c r="B140" t="n">
-        <v>78521</v>
+        <v>78532</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>136944309</v>
       </c>
       <c r="B147" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>136944303</v>
       </c>
       <c r="B148" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>136944314</v>
       </c>
       <c r="B149" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>136944355</v>
       </c>
       <c r="B150" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>136944373</v>
       </c>
       <c r="B151" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>136944378</v>
       </c>
       <c r="B152" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>136944387</v>
       </c>
       <c r="B153" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>136944392</v>
       </c>
       <c r="B154" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17755,7 +17755,7 @@
         <v>136944281</v>
       </c>
       <c r="B155" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>136944302</v>
       </c>
       <c r="B156" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17979,7 +17979,7 @@
         <v>136944317</v>
       </c>
       <c r="B157" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>136944328</v>
       </c>
       <c r="B158" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18203,7 +18203,7 @@
         <v>136944337</v>
       </c>
       <c r="B159" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>136944339</v>
       </c>
       <c r="B160" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>136944345</v>
       </c>
       <c r="B161" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>136944350</v>
       </c>
       <c r="B162" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>136944351</v>
       </c>
       <c r="B163" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>136944368</v>
       </c>
       <c r="B164" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>136944375</v>
       </c>
       <c r="B165" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>136944377</v>
       </c>
       <c r="B166" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>136944388</v>
       </c>
       <c r="B167" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>136949420</v>
       </c>
       <c r="B168" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>136949425</v>
       </c>
       <c r="B169" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>136949428</v>
       </c>
       <c r="B170" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>136949432</v>
       </c>
       <c r="B171" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>136949437</v>
       </c>
       <c r="B172" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>136949439</v>
       </c>
       <c r="B173" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>136949448</v>
       </c>
       <c r="B174" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>136949456</v>
       </c>
       <c r="B175" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>136949461</v>
       </c>
       <c r="B176" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>136949462</v>
       </c>
       <c r="B177" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>136949464</v>
       </c>
       <c r="B178" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>136949466</v>
       </c>
       <c r="B179" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>136949469</v>
       </c>
       <c r="B180" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>136949474</v>
       </c>
       <c r="B181" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20784,7 +20784,7 @@
         <v>136949478</v>
       </c>
       <c r="B182" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>136949479</v>
       </c>
       <c r="B183" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>136949481</v>
       </c>
       <c r="B184" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>136949454</v>
       </c>
       <c r="B185" t="n">
-        <v>93500</v>
+        <v>93512</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
         <v>136949446</v>
       </c>
       <c r="B186" t="n">
-        <v>87421</v>
+        <v>87432</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>136949417</v>
       </c>
       <c r="B187" t="n">
-        <v>92591</v>
+        <v>92603</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>136944329</v>
       </c>
       <c r="B188" t="n">
-        <v>80415</v>
+        <v>80426</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>

--- a/artfynd/A 39408-2026 artfynd.xlsx
+++ b/artfynd/A 39408-2026 artfynd.xlsx
@@ -1329,7 +1329,7 @@
         <v>136944274</v>
       </c>
       <c r="B8" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>136944277</v>
       </c>
       <c r="B9" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136944289</v>
       </c>
       <c r="B10" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>136944294</v>
       </c>
       <c r="B11" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136944332</v>
       </c>
       <c r="B12" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136944383</v>
       </c>
       <c r="B13" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>136944393</v>
       </c>
       <c r="B14" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>136949427</v>
       </c>
       <c r="B16" t="n">
-        <v>79627</v>
+        <v>79628</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136944346</v>
       </c>
       <c r="B17" t="n">
-        <v>81501</v>
+        <v>81502</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>136944293</v>
       </c>
       <c r="B22" t="n">
-        <v>92360</v>
+        <v>92361</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>136949434</v>
       </c>
       <c r="B23" t="n">
-        <v>93515</v>
+        <v>93516</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>136944300</v>
       </c>
       <c r="B26" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>136949422</v>
       </c>
       <c r="B27" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>136949472</v>
       </c>
       <c r="B28" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>136944371</v>
       </c>
       <c r="B29" t="n">
-        <v>93506</v>
+        <v>93507</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>136944298</v>
       </c>
       <c r="B31" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>136949477</v>
       </c>
       <c r="B32" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>136949486</v>
       </c>
       <c r="B33" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>136944279</v>
       </c>
       <c r="B34" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>136944287</v>
       </c>
       <c r="B35" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>136944296</v>
       </c>
       <c r="B36" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>136944348</v>
       </c>
       <c r="B37" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>136944358</v>
       </c>
       <c r="B38" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>136944367</v>
       </c>
       <c r="B39" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>136944369</v>
       </c>
       <c r="B40" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>136949431</v>
       </c>
       <c r="B41" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>136949435</v>
       </c>
       <c r="B42" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>136949473</v>
       </c>
       <c r="B43" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>136949475</v>
       </c>
       <c r="B44" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>136944295</v>
       </c>
       <c r="B45" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>136944353</v>
       </c>
       <c r="B46" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>136944292</v>
       </c>
       <c r="B47" t="n">
-        <v>93124</v>
+        <v>93125</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>136944352</v>
       </c>
       <c r="B48" t="n">
-        <v>93124</v>
+        <v>93125</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>136949453</v>
       </c>
       <c r="B49" t="n">
-        <v>93124</v>
+        <v>93125</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>136949483</v>
       </c>
       <c r="B50" t="n">
-        <v>93124</v>
+        <v>93125</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>136949423</v>
       </c>
       <c r="B51" t="n">
-        <v>91101</v>
+        <v>91102</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>136949445</v>
       </c>
       <c r="B52" t="n">
-        <v>91101</v>
+        <v>91102</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>136944382</v>
       </c>
       <c r="B53" t="n">
-        <v>91535</v>
+        <v>91536</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>136944286</v>
       </c>
       <c r="B54" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>136944357</v>
       </c>
       <c r="B55" t="n">
-        <v>93465</v>
+        <v>93466</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>136944374</v>
       </c>
       <c r="B56" t="n">
-        <v>90963</v>
+        <v>90964</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>136944390</v>
       </c>
       <c r="B57" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>136944338</v>
       </c>
       <c r="B58" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>136944283</v>
       </c>
       <c r="B64" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>136944318</v>
       </c>
       <c r="B65" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         <v>136944320</v>
       </c>
       <c r="B66" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>136944340</v>
       </c>
       <c r="B67" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>136944344</v>
       </c>
       <c r="B68" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>136944365</v>
       </c>
       <c r="B69" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>136944380</v>
       </c>
       <c r="B70" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>136949416</v>
       </c>
       <c r="B71" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>136949418</v>
       </c>
       <c r="B72" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>136949429</v>
       </c>
       <c r="B73" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>136949433</v>
       </c>
       <c r="B74" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>136949436</v>
       </c>
       <c r="B75" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>136949440</v>
       </c>
       <c r="B76" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>136949441</v>
       </c>
       <c r="B77" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>136949480</v>
       </c>
       <c r="B78" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>136949482</v>
       </c>
       <c r="B79" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>136944282</v>
       </c>
       <c r="B80" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>136944308</v>
       </c>
       <c r="B81" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>136944323</v>
       </c>
       <c r="B82" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>136944342</v>
       </c>
       <c r="B83" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>136944356</v>
       </c>
       <c r="B84" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>136944363</v>
       </c>
       <c r="B85" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>136944379</v>
       </c>
       <c r="B86" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>136944385</v>
       </c>
       <c r="B87" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>136944275</v>
       </c>
       <c r="B88" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>136944280</v>
       </c>
       <c r="B89" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>136944288</v>
       </c>
       <c r="B90" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>136944290</v>
       </c>
       <c r="B91" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>136944297</v>
       </c>
       <c r="B92" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>136944301</v>
       </c>
       <c r="B93" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>136944305</v>
       </c>
       <c r="B94" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>136944307</v>
       </c>
       <c r="B95" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>136944310</v>
       </c>
       <c r="B96" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>136944311</v>
       </c>
       <c r="B97" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>136944315</v>
       </c>
       <c r="B98" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>136944316</v>
       </c>
       <c r="B99" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>136944330</v>
       </c>
       <c r="B100" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>136944331</v>
       </c>
       <c r="B101" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>136944333</v>
       </c>
       <c r="B102" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>136944347</v>
       </c>
       <c r="B103" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>136944349</v>
       </c>
       <c r="B104" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>136944359</v>
       </c>
       <c r="B105" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>136944361</v>
       </c>
       <c r="B106" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>136944362</v>
       </c>
       <c r="B107" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>136944366</v>
       </c>
       <c r="B108" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>136944370</v>
       </c>
       <c r="B109" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>136944372</v>
       </c>
       <c r="B110" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>136944381</v>
       </c>
       <c r="B111" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>136944384</v>
       </c>
       <c r="B112" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>136944389</v>
       </c>
       <c r="B113" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>136944391</v>
       </c>
       <c r="B114" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>136944394</v>
       </c>
       <c r="B115" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>136949419</v>
       </c>
       <c r="B116" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>136949421</v>
       </c>
       <c r="B117" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>136949424</v>
       </c>
       <c r="B118" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>136949438</v>
       </c>
       <c r="B119" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>136949442</v>
       </c>
       <c r="B120" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>136949443</v>
       </c>
       <c r="B121" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>136949444</v>
       </c>
       <c r="B122" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>136949449</v>
       </c>
       <c r="B123" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>136949450</v>
       </c>
       <c r="B124" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>136949451</v>
       </c>
       <c r="B125" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>136949452</v>
       </c>
       <c r="B126" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>136949465</v>
       </c>
       <c r="B127" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>136949467</v>
       </c>
       <c r="B128" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>136949468</v>
       </c>
       <c r="B129" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>136949470</v>
       </c>
       <c r="B130" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>136949471</v>
       </c>
       <c r="B131" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>136949476</v>
       </c>
       <c r="B132" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>136949484</v>
       </c>
       <c r="B133" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>136949426</v>
       </c>
       <c r="B136" t="n">
-        <v>78532</v>
+        <v>78533</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>136949430</v>
       </c>
       <c r="B137" t="n">
-        <v>78532</v>
+        <v>78533</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15839,7 +15839,7 @@
         <v>136949457</v>
       </c>
       <c r="B138" t="n">
-        <v>78532</v>
+        <v>78533</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>136949459</v>
       </c>
       <c r="B139" t="n">
-        <v>78532</v>
+        <v>78533</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>136949460</v>
       </c>
       <c r="B140" t="n">
-        <v>78532</v>
+        <v>78533</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>136944309</v>
       </c>
       <c r="B147" t="n">
-        <v>98298</v>
+        <v>98299</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>136944303</v>
       </c>
       <c r="B148" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>136944314</v>
       </c>
       <c r="B149" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>136944355</v>
       </c>
       <c r="B150" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>136944373</v>
       </c>
       <c r="B151" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>136944378</v>
       </c>
       <c r="B152" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>136944387</v>
       </c>
       <c r="B153" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>136944392</v>
       </c>
       <c r="B154" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17755,7 +17755,7 @@
         <v>136944281</v>
       </c>
       <c r="B155" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>136944302</v>
       </c>
       <c r="B156" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17979,7 +17979,7 @@
         <v>136944317</v>
       </c>
       <c r="B157" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>136944328</v>
       </c>
       <c r="B158" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18203,7 +18203,7 @@
         <v>136944337</v>
       </c>
       <c r="B159" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>136944339</v>
       </c>
       <c r="B160" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>136944345</v>
       </c>
       <c r="B161" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>136944350</v>
       </c>
       <c r="B162" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>136944351</v>
       </c>
       <c r="B163" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>136944368</v>
       </c>
       <c r="B164" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>136944375</v>
       </c>
       <c r="B165" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>136944377</v>
       </c>
       <c r="B166" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>136944388</v>
       </c>
       <c r="B167" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>136949420</v>
       </c>
       <c r="B168" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>136949425</v>
       </c>
       <c r="B169" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>136949428</v>
       </c>
       <c r="B170" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>136949432</v>
       </c>
       <c r="B171" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>136949437</v>
       </c>
       <c r="B172" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>136949439</v>
       </c>
       <c r="B173" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>136949448</v>
       </c>
       <c r="B174" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>136949456</v>
       </c>
       <c r="B175" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>136949461</v>
       </c>
       <c r="B176" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>136949462</v>
       </c>
       <c r="B177" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>136949464</v>
       </c>
       <c r="B178" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>136949466</v>
       </c>
       <c r="B179" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>136949469</v>
       </c>
       <c r="B180" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>136949474</v>
       </c>
       <c r="B181" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20784,7 +20784,7 @@
         <v>136949478</v>
       </c>
       <c r="B182" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>136949479</v>
       </c>
       <c r="B183" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>136949481</v>
       </c>
       <c r="B184" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>136949454</v>
       </c>
       <c r="B185" t="n">
-        <v>93512</v>
+        <v>93513</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
         <v>136949446</v>
       </c>
       <c r="B186" t="n">
-        <v>87432</v>
+        <v>87433</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>136949417</v>
       </c>
       <c r="B187" t="n">
-        <v>92603</v>
+        <v>92604</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21451,7 +21451,7 @@
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
@@ -21466,7 +21466,7 @@
         <v>136944329</v>
       </c>
       <c r="B188" t="n">
-        <v>80426</v>
+        <v>80427</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>

--- a/artfynd/A 39408-2026 artfynd.xlsx
+++ b/artfynd/A 39408-2026 artfynd.xlsx
@@ -1329,7 +1329,7 @@
         <v>136944274</v>
       </c>
       <c r="B8" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>136944277</v>
       </c>
       <c r="B9" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136944289</v>
       </c>
       <c r="B10" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>136944294</v>
       </c>
       <c r="B11" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136944332</v>
       </c>
       <c r="B12" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136944383</v>
       </c>
       <c r="B13" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>136944393</v>
       </c>
       <c r="B14" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>136949427</v>
       </c>
       <c r="B16" t="n">
-        <v>79628</v>
+        <v>79630</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136944346</v>
       </c>
       <c r="B17" t="n">
-        <v>81502</v>
+        <v>81504</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>136944293</v>
       </c>
       <c r="B22" t="n">
-        <v>92361</v>
+        <v>92364</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>136949434</v>
       </c>
       <c r="B23" t="n">
-        <v>93516</v>
+        <v>93519</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>136944300</v>
       </c>
       <c r="B26" t="n">
-        <v>92235</v>
+        <v>92238</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>136949422</v>
       </c>
       <c r="B27" t="n">
-        <v>92235</v>
+        <v>92238</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>136949472</v>
       </c>
       <c r="B28" t="n">
-        <v>92235</v>
+        <v>92238</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>136944371</v>
       </c>
       <c r="B29" t="n">
-        <v>93507</v>
+        <v>93510</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>136944298</v>
       </c>
       <c r="B31" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>136949477</v>
       </c>
       <c r="B32" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>136949486</v>
       </c>
       <c r="B33" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>136944279</v>
       </c>
       <c r="B34" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>136944287</v>
       </c>
       <c r="B35" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>136944296</v>
       </c>
       <c r="B36" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>136944348</v>
       </c>
       <c r="B37" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>136944358</v>
       </c>
       <c r="B38" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>136944367</v>
       </c>
       <c r="B39" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>136944369</v>
       </c>
       <c r="B40" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>136949431</v>
       </c>
       <c r="B41" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>136949435</v>
       </c>
       <c r="B42" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>136949473</v>
       </c>
       <c r="B43" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>136949475</v>
       </c>
       <c r="B44" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>136944295</v>
       </c>
       <c r="B45" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>136944353</v>
       </c>
       <c r="B46" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>136944292</v>
       </c>
       <c r="B47" t="n">
-        <v>93125</v>
+        <v>93128</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>136944352</v>
       </c>
       <c r="B48" t="n">
-        <v>93125</v>
+        <v>93128</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>136949453</v>
       </c>
       <c r="B49" t="n">
-        <v>93125</v>
+        <v>93128</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>136949483</v>
       </c>
       <c r="B50" t="n">
-        <v>93125</v>
+        <v>93128</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>136949423</v>
       </c>
       <c r="B51" t="n">
-        <v>91102</v>
+        <v>91105</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>136949445</v>
       </c>
       <c r="B52" t="n">
-        <v>91102</v>
+        <v>91105</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>136944382</v>
       </c>
       <c r="B53" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>136944286</v>
       </c>
       <c r="B54" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>136944357</v>
       </c>
       <c r="B55" t="n">
-        <v>93466</v>
+        <v>93469</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>136944374</v>
       </c>
       <c r="B56" t="n">
-        <v>90964</v>
+        <v>90967</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>136944390</v>
       </c>
       <c r="B57" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>136944338</v>
       </c>
       <c r="B58" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>136944283</v>
       </c>
       <c r="B64" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>136944318</v>
       </c>
       <c r="B65" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         <v>136944320</v>
       </c>
       <c r="B66" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>136944340</v>
       </c>
       <c r="B67" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>136944344</v>
       </c>
       <c r="B68" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>136944365</v>
       </c>
       <c r="B69" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>136944380</v>
       </c>
       <c r="B70" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>136949416</v>
       </c>
       <c r="B71" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>136949418</v>
       </c>
       <c r="B72" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>136949429</v>
       </c>
       <c r="B73" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>136949433</v>
       </c>
       <c r="B74" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>136949436</v>
       </c>
       <c r="B75" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>136949440</v>
       </c>
       <c r="B76" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>136949441</v>
       </c>
       <c r="B77" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>136949480</v>
       </c>
       <c r="B78" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>136949482</v>
       </c>
       <c r="B79" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>136944282</v>
       </c>
       <c r="B80" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>136944308</v>
       </c>
       <c r="B81" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>136944323</v>
       </c>
       <c r="B82" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>136944342</v>
       </c>
       <c r="B83" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>136944356</v>
       </c>
       <c r="B84" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>136944363</v>
       </c>
       <c r="B85" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>136944379</v>
       </c>
       <c r="B86" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>136944385</v>
       </c>
       <c r="B87" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>136944275</v>
       </c>
       <c r="B88" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>136944280</v>
       </c>
       <c r="B89" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>136944288</v>
       </c>
       <c r="B90" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>136944290</v>
       </c>
       <c r="B91" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>136944297</v>
       </c>
       <c r="B92" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>136944301</v>
       </c>
       <c r="B93" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>136944305</v>
       </c>
       <c r="B94" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>136944307</v>
       </c>
       <c r="B95" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>136944310</v>
       </c>
       <c r="B96" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>136944311</v>
       </c>
       <c r="B97" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>136944315</v>
       </c>
       <c r="B98" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>136944316</v>
       </c>
       <c r="B99" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>136944330</v>
       </c>
       <c r="B100" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>136944331</v>
       </c>
       <c r="B101" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>136944333</v>
       </c>
       <c r="B102" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>136944347</v>
       </c>
       <c r="B103" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>136944349</v>
       </c>
       <c r="B104" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>136944359</v>
       </c>
       <c r="B105" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>136944361</v>
       </c>
       <c r="B106" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>136944362</v>
       </c>
       <c r="B107" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>136944366</v>
       </c>
       <c r="B108" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>136944370</v>
       </c>
       <c r="B109" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>136944372</v>
       </c>
       <c r="B110" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>136944381</v>
       </c>
       <c r="B111" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>136944384</v>
       </c>
       <c r="B112" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>136944389</v>
       </c>
       <c r="B113" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>136944391</v>
       </c>
       <c r="B114" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>136944394</v>
       </c>
       <c r="B115" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>136949419</v>
       </c>
       <c r="B116" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>136949421</v>
       </c>
       <c r="B117" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>136949424</v>
       </c>
       <c r="B118" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>136949438</v>
       </c>
       <c r="B119" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>136949442</v>
       </c>
       <c r="B120" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>136949443</v>
       </c>
       <c r="B121" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>136949444</v>
       </c>
       <c r="B122" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>136949449</v>
       </c>
       <c r="B123" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>136949450</v>
       </c>
       <c r="B124" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>136949451</v>
       </c>
       <c r="B125" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>136949452</v>
       </c>
       <c r="B126" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>136949465</v>
       </c>
       <c r="B127" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>136949467</v>
       </c>
       <c r="B128" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>136949468</v>
       </c>
       <c r="B129" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>136949470</v>
       </c>
       <c r="B130" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>136949471</v>
       </c>
       <c r="B131" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>136949476</v>
       </c>
       <c r="B132" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>136949484</v>
       </c>
       <c r="B133" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>136949426</v>
       </c>
       <c r="B136" t="n">
-        <v>78533</v>
+        <v>78535</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>136949430</v>
       </c>
       <c r="B137" t="n">
-        <v>78533</v>
+        <v>78535</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15839,7 +15839,7 @@
         <v>136949457</v>
       </c>
       <c r="B138" t="n">
-        <v>78533</v>
+        <v>78535</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>136949459</v>
       </c>
       <c r="B139" t="n">
-        <v>78533</v>
+        <v>78535</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>136949460</v>
       </c>
       <c r="B140" t="n">
-        <v>78533</v>
+        <v>78535</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>136944309</v>
       </c>
       <c r="B147" t="n">
-        <v>98299</v>
+        <v>98302</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>136944303</v>
       </c>
       <c r="B148" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>136944314</v>
       </c>
       <c r="B149" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>136944355</v>
       </c>
       <c r="B150" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>136944373</v>
       </c>
       <c r="B151" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>136944378</v>
       </c>
       <c r="B152" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>136944387</v>
       </c>
       <c r="B153" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>136944392</v>
       </c>
       <c r="B154" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17755,7 +17755,7 @@
         <v>136944281</v>
       </c>
       <c r="B155" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>136944302</v>
       </c>
       <c r="B156" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17979,7 +17979,7 @@
         <v>136944317</v>
       </c>
       <c r="B157" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>136944328</v>
       </c>
       <c r="B158" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18203,7 +18203,7 @@
         <v>136944337</v>
       </c>
       <c r="B159" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>136944339</v>
       </c>
       <c r="B160" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>136944345</v>
       </c>
       <c r="B161" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>136944350</v>
       </c>
       <c r="B162" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>136944351</v>
       </c>
       <c r="B163" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>136944368</v>
       </c>
       <c r="B164" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>136944375</v>
       </c>
       <c r="B165" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>136944377</v>
       </c>
       <c r="B166" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>136944388</v>
       </c>
       <c r="B167" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>136949420</v>
       </c>
       <c r="B168" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>136949425</v>
       </c>
       <c r="B169" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>136949428</v>
       </c>
       <c r="B170" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>136949432</v>
       </c>
       <c r="B171" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>136949437</v>
       </c>
       <c r="B172" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>136949439</v>
       </c>
       <c r="B173" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>136949448</v>
       </c>
       <c r="B174" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>136949456</v>
       </c>
       <c r="B175" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>136949461</v>
       </c>
       <c r="B176" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>136949462</v>
       </c>
       <c r="B177" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>136949464</v>
       </c>
       <c r="B178" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>136949466</v>
       </c>
       <c r="B179" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>136949469</v>
       </c>
       <c r="B180" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>136949474</v>
       </c>
       <c r="B181" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20784,7 +20784,7 @@
         <v>136949478</v>
       </c>
       <c r="B182" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>136949479</v>
       </c>
       <c r="B183" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>136949481</v>
       </c>
       <c r="B184" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>136949454</v>
       </c>
       <c r="B185" t="n">
-        <v>93513</v>
+        <v>93516</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
         <v>136949446</v>
       </c>
       <c r="B186" t="n">
-        <v>87433</v>
+        <v>87436</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>136949417</v>
       </c>
       <c r="B187" t="n">
-        <v>92604</v>
+        <v>92607</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21451,7 +21451,7 @@
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
@@ -21466,7 +21466,7 @@
         <v>136944329</v>
       </c>
       <c r="B188" t="n">
-        <v>80427</v>
+        <v>80429</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>

--- a/artfynd/A 39408-2026 artfynd.xlsx
+++ b/artfynd/A 39408-2026 artfynd.xlsx
@@ -1329,7 +1329,7 @@
         <v>136944274</v>
       </c>
       <c r="B8" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>136944277</v>
       </c>
       <c r="B9" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136944289</v>
       </c>
       <c r="B10" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>136944294</v>
       </c>
       <c r="B11" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136944332</v>
       </c>
       <c r="B12" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136944383</v>
       </c>
       <c r="B13" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>136944393</v>
       </c>
       <c r="B14" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>136949427</v>
       </c>
       <c r="B16" t="n">
-        <v>79630</v>
+        <v>79631</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136944346</v>
       </c>
       <c r="B17" t="n">
-        <v>81504</v>
+        <v>81505</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>136944293</v>
       </c>
       <c r="B22" t="n">
-        <v>92364</v>
+        <v>92365</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>136944300</v>
       </c>
       <c r="B26" t="n">
-        <v>92238</v>
+        <v>92239</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>136949422</v>
       </c>
       <c r="B27" t="n">
-        <v>92238</v>
+        <v>92239</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>136949472</v>
       </c>
       <c r="B28" t="n">
-        <v>92238</v>
+        <v>92239</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>136944371</v>
       </c>
       <c r="B29" t="n">
-        <v>93510</v>
+        <v>93511</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>136944298</v>
       </c>
       <c r="B31" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>136949477</v>
       </c>
       <c r="B32" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>136949486</v>
       </c>
       <c r="B33" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>136944279</v>
       </c>
       <c r="B34" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>136944287</v>
       </c>
       <c r="B35" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>136944296</v>
       </c>
       <c r="B36" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>136944348</v>
       </c>
       <c r="B37" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>136944358</v>
       </c>
       <c r="B38" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>136944367</v>
       </c>
       <c r="B39" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>136944369</v>
       </c>
       <c r="B40" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>136949431</v>
       </c>
       <c r="B41" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>136949435</v>
       </c>
       <c r="B42" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>136949473</v>
       </c>
       <c r="B43" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>136949475</v>
       </c>
       <c r="B44" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>136944295</v>
       </c>
       <c r="B45" t="n">
-        <v>93489</v>
+        <v>93490</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>136944353</v>
       </c>
       <c r="B46" t="n">
-        <v>93489</v>
+        <v>93490</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>136944292</v>
       </c>
       <c r="B47" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>136944352</v>
       </c>
       <c r="B48" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>136949453</v>
       </c>
       <c r="B49" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>136949483</v>
       </c>
       <c r="B50" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>136949423</v>
       </c>
       <c r="B51" t="n">
-        <v>91105</v>
+        <v>91106</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>136949445</v>
       </c>
       <c r="B52" t="n">
-        <v>91105</v>
+        <v>91106</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>136944382</v>
       </c>
       <c r="B53" t="n">
-        <v>91539</v>
+        <v>91540</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>136944286</v>
       </c>
       <c r="B54" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>136944357</v>
       </c>
       <c r="B55" t="n">
-        <v>93469</v>
+        <v>93470</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>136944374</v>
       </c>
       <c r="B56" t="n">
-        <v>90967</v>
+        <v>90968</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>136944390</v>
       </c>
       <c r="B57" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>136944338</v>
       </c>
       <c r="B58" t="n">
-        <v>79559</v>
+        <v>79560</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>136944283</v>
       </c>
       <c r="B64" t="n">
-        <v>78938</v>
+        <v>78939</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>136944318</v>
       </c>
       <c r="B65" t="n">
-        <v>78938</v>
+        <v>78939</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         <v>136944320</v>
       </c>
       <c r="B66" t="n">
-        <v>78938</v>
+        <v>78939</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>136944340</v>
       </c>
       <c r="B67" t="n">
-        <v>78938</v>
+        <v>78939</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>136944344</v>
       </c>
       <c r="B68" t="n">
-        <v>78938</v>
+        <v>78939</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>136944365</v>
       </c>
       <c r="B69" t="n">
-        <v>78938</v>
+        <v>78939</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>136944380</v>
       </c>
       <c r="B70" t="n">
-        <v>78938</v>
+        <v>78939</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>136949416</v>
       </c>
       <c r="B71" t="n">
-        <v>78938</v>
+        <v>78939</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>136949418</v>
       </c>
       <c r="B72" t="n">
-        <v>78938</v>
+        <v>78939</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>136949429</v>
       </c>
       <c r="B73" t="n">
-        <v>78938</v>
+        <v>78939</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>136949433</v>
       </c>
       <c r="B74" t="n">
-        <v>78938</v>
+        <v>78939</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>136949436</v>
       </c>
       <c r="B75" t="n">
-        <v>78938</v>
+        <v>78939</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>136949440</v>
       </c>
       <c r="B76" t="n">
-        <v>78938</v>
+        <v>78939</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>136949441</v>
       </c>
       <c r="B77" t="n">
-        <v>78938</v>
+        <v>78939</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>136949480</v>
       </c>
       <c r="B78" t="n">
-        <v>78938</v>
+        <v>78939</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>136949482</v>
       </c>
       <c r="B79" t="n">
-        <v>78938</v>
+        <v>78939</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>136944282</v>
       </c>
       <c r="B80" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>136944308</v>
       </c>
       <c r="B81" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>136944323</v>
       </c>
       <c r="B82" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>136944342</v>
       </c>
       <c r="B83" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>136944356</v>
       </c>
       <c r="B84" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>136944363</v>
       </c>
       <c r="B85" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>136944379</v>
       </c>
       <c r="B86" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>136944385</v>
       </c>
       <c r="B87" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>136944275</v>
       </c>
       <c r="B88" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>136944280</v>
       </c>
       <c r="B89" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>136944288</v>
       </c>
       <c r="B90" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>136944290</v>
       </c>
       <c r="B91" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>136944297</v>
       </c>
       <c r="B92" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>136944301</v>
       </c>
       <c r="B93" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>136944305</v>
       </c>
       <c r="B94" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>136944307</v>
       </c>
       <c r="B95" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>136944310</v>
       </c>
       <c r="B96" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>136944311</v>
       </c>
       <c r="B97" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>136944315</v>
       </c>
       <c r="B98" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>136944316</v>
       </c>
       <c r="B99" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>136944330</v>
       </c>
       <c r="B100" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>136944331</v>
       </c>
       <c r="B101" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>136944333</v>
       </c>
       <c r="B102" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>136944347</v>
       </c>
       <c r="B103" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>136944349</v>
       </c>
       <c r="B104" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>136944359</v>
       </c>
       <c r="B105" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>136944361</v>
       </c>
       <c r="B106" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>136944362</v>
       </c>
       <c r="B107" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>136944366</v>
       </c>
       <c r="B108" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>136944370</v>
       </c>
       <c r="B109" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>136944372</v>
       </c>
       <c r="B110" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>136944381</v>
       </c>
       <c r="B111" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>136944384</v>
       </c>
       <c r="B112" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>136944389</v>
       </c>
       <c r="B113" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>136944391</v>
       </c>
       <c r="B114" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>136944394</v>
       </c>
       <c r="B115" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>136949419</v>
       </c>
       <c r="B116" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>136949421</v>
       </c>
       <c r="B117" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>136949424</v>
       </c>
       <c r="B118" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>136949438</v>
       </c>
       <c r="B119" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>136949442</v>
       </c>
       <c r="B120" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>136949443</v>
       </c>
       <c r="B121" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>136949444</v>
       </c>
       <c r="B122" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>136949449</v>
       </c>
       <c r="B123" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>136949450</v>
       </c>
       <c r="B124" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>136949451</v>
       </c>
       <c r="B125" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>136949452</v>
       </c>
       <c r="B126" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>136949465</v>
       </c>
       <c r="B127" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>136949467</v>
       </c>
       <c r="B128" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>136949468</v>
       </c>
       <c r="B129" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>136949470</v>
       </c>
       <c r="B130" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>136949471</v>
       </c>
       <c r="B131" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>136949476</v>
       </c>
       <c r="B132" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>136949484</v>
       </c>
       <c r="B133" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>136949426</v>
       </c>
       <c r="B136" t="n">
-        <v>78535</v>
+        <v>78536</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>136949430</v>
       </c>
       <c r="B137" t="n">
-        <v>78535</v>
+        <v>78536</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15839,7 +15839,7 @@
         <v>136949457</v>
       </c>
       <c r="B138" t="n">
-        <v>78535</v>
+        <v>78536</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>136949459</v>
       </c>
       <c r="B139" t="n">
-        <v>78535</v>
+        <v>78536</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>136949460</v>
       </c>
       <c r="B140" t="n">
-        <v>78535</v>
+        <v>78536</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>136944309</v>
       </c>
       <c r="B147" t="n">
-        <v>98302</v>
+        <v>98303</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>136944303</v>
       </c>
       <c r="B148" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>136944314</v>
       </c>
       <c r="B149" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>136944355</v>
       </c>
       <c r="B150" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>136944373</v>
       </c>
       <c r="B151" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>136944378</v>
       </c>
       <c r="B152" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>136944387</v>
       </c>
       <c r="B153" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>136944392</v>
       </c>
       <c r="B154" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17755,7 +17755,7 @@
         <v>136944281</v>
       </c>
       <c r="B155" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>136944302</v>
       </c>
       <c r="B156" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17979,7 +17979,7 @@
         <v>136944317</v>
       </c>
       <c r="B157" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>136944328</v>
       </c>
       <c r="B158" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18203,7 +18203,7 @@
         <v>136944337</v>
       </c>
       <c r="B159" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>136944339</v>
       </c>
       <c r="B160" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>136944345</v>
       </c>
       <c r="B161" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>136944350</v>
       </c>
       <c r="B162" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>136944351</v>
       </c>
       <c r="B163" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>136944368</v>
       </c>
       <c r="B164" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>136944375</v>
       </c>
       <c r="B165" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>136944377</v>
       </c>
       <c r="B166" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>136944388</v>
       </c>
       <c r="B167" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>136949420</v>
       </c>
       <c r="B168" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>136949425</v>
       </c>
       <c r="B169" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>136949428</v>
       </c>
       <c r="B170" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>136949432</v>
       </c>
       <c r="B171" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>136949437</v>
       </c>
       <c r="B172" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>136949439</v>
       </c>
       <c r="B173" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>136949448</v>
       </c>
       <c r="B174" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>136949456</v>
       </c>
       <c r="B175" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>136949461</v>
       </c>
       <c r="B176" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>136949462</v>
       </c>
       <c r="B177" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>136949464</v>
       </c>
       <c r="B178" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>136949466</v>
       </c>
       <c r="B179" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>136949469</v>
       </c>
       <c r="B180" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>136949474</v>
       </c>
       <c r="B181" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20784,7 +20784,7 @@
         <v>136949478</v>
       </c>
       <c r="B182" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>136949479</v>
       </c>
       <c r="B183" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>136949481</v>
       </c>
       <c r="B184" t="n">
-        <v>80125</v>
+        <v>80126</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>136949454</v>
       </c>
       <c r="B185" t="n">
-        <v>93516</v>
+        <v>93517</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
         <v>136949446</v>
       </c>
       <c r="B186" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>136949417</v>
       </c>
       <c r="B187" t="n">
-        <v>92607</v>
+        <v>92608</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>136944329</v>
       </c>
       <c r="B188" t="n">
-        <v>80429</v>
+        <v>80430</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>

--- a/artfynd/A 39408-2026 artfynd.xlsx
+++ b/artfynd/A 39408-2026 artfynd.xlsx
@@ -1329,7 +1329,7 @@
         <v>136944274</v>
       </c>
       <c r="B8" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>136944277</v>
       </c>
       <c r="B9" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136944289</v>
       </c>
       <c r="B10" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>136944294</v>
       </c>
       <c r="B11" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136944332</v>
       </c>
       <c r="B12" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>136944383</v>
       </c>
       <c r="B13" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>136944393</v>
       </c>
       <c r="B14" t="n">
-        <v>79202</v>
+        <v>79205</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>136949427</v>
       </c>
       <c r="B16" t="n">
-        <v>79631</v>
+        <v>79634</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>136944346</v>
       </c>
       <c r="B17" t="n">
-        <v>81505</v>
+        <v>81508</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>136944293</v>
       </c>
       <c r="B22" t="n">
-        <v>92365</v>
+        <v>92368</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>136949434</v>
       </c>
       <c r="B23" t="n">
-        <v>93519</v>
+        <v>93523</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>136944300</v>
       </c>
       <c r="B26" t="n">
-        <v>92239</v>
+        <v>92242</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>136949422</v>
       </c>
       <c r="B27" t="n">
-        <v>92239</v>
+        <v>92242</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>136949472</v>
       </c>
       <c r="B28" t="n">
-        <v>92239</v>
+        <v>92242</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>136944371</v>
       </c>
       <c r="B29" t="n">
-        <v>93511</v>
+        <v>93514</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>136944298</v>
       </c>
       <c r="B31" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>136949477</v>
       </c>
       <c r="B32" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>136949486</v>
       </c>
       <c r="B33" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>136944279</v>
       </c>
       <c r="B34" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>136944287</v>
       </c>
       <c r="B35" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>136944296</v>
       </c>
       <c r="B36" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>136944348</v>
       </c>
       <c r="B37" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>136944358</v>
       </c>
       <c r="B38" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>136944367</v>
       </c>
       <c r="B39" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>136944369</v>
       </c>
       <c r="B40" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>136949431</v>
       </c>
       <c r="B41" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>136949435</v>
       </c>
       <c r="B42" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>136949473</v>
       </c>
       <c r="B43" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>136949475</v>
       </c>
       <c r="B44" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>136944295</v>
       </c>
       <c r="B45" t="n">
-        <v>93490</v>
+        <v>93493</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>136944353</v>
       </c>
       <c r="B46" t="n">
-        <v>93490</v>
+        <v>93493</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>136944292</v>
       </c>
       <c r="B47" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>136944352</v>
       </c>
       <c r="B48" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>136949453</v>
       </c>
       <c r="B49" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>136949483</v>
       </c>
       <c r="B50" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>136949423</v>
       </c>
       <c r="B51" t="n">
-        <v>91106</v>
+        <v>91109</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>136949445</v>
       </c>
       <c r="B52" t="n">
-        <v>91106</v>
+        <v>91109</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>136944382</v>
       </c>
       <c r="B53" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>136944286</v>
       </c>
       <c r="B54" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>136944357</v>
       </c>
       <c r="B55" t="n">
-        <v>93470</v>
+        <v>93473</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>136944374</v>
       </c>
       <c r="B56" t="n">
-        <v>90968</v>
+        <v>90971</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>136944390</v>
       </c>
       <c r="B57" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>136944338</v>
       </c>
       <c r="B58" t="n">
-        <v>79560</v>
+        <v>79563</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>136944283</v>
       </c>
       <c r="B64" t="n">
-        <v>78939</v>
+        <v>78942</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>136944318</v>
       </c>
       <c r="B65" t="n">
-        <v>78939</v>
+        <v>78942</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         <v>136944320</v>
       </c>
       <c r="B66" t="n">
-        <v>78939</v>
+        <v>78942</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>136944340</v>
       </c>
       <c r="B67" t="n">
-        <v>78939</v>
+        <v>78942</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         <v>136944344</v>
       </c>
       <c r="B68" t="n">
-        <v>78939</v>
+        <v>78942</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>136944365</v>
       </c>
       <c r="B69" t="n">
-        <v>78939</v>
+        <v>78942</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>136944380</v>
       </c>
       <c r="B70" t="n">
-        <v>78939</v>
+        <v>78942</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>136949416</v>
       </c>
       <c r="B71" t="n">
-        <v>78939</v>
+        <v>78942</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>136949418</v>
       </c>
       <c r="B72" t="n">
-        <v>78939</v>
+        <v>78942</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>136949429</v>
       </c>
       <c r="B73" t="n">
-        <v>78939</v>
+        <v>78942</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>136949433</v>
       </c>
       <c r="B74" t="n">
-        <v>78939</v>
+        <v>78942</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>136949436</v>
       </c>
       <c r="B75" t="n">
-        <v>78939</v>
+        <v>78942</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>136949440</v>
       </c>
       <c r="B76" t="n">
-        <v>78939</v>
+        <v>78942</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>136949441</v>
       </c>
       <c r="B77" t="n">
-        <v>78939</v>
+        <v>78942</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>136949480</v>
       </c>
       <c r="B78" t="n">
-        <v>78939</v>
+        <v>78942</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>136949482</v>
       </c>
       <c r="B79" t="n">
-        <v>78939</v>
+        <v>78942</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>136944282</v>
       </c>
       <c r="B80" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>136944308</v>
       </c>
       <c r="B81" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>136944323</v>
       </c>
       <c r="B82" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>136944342</v>
       </c>
       <c r="B83" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>136944356</v>
       </c>
       <c r="B84" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>136944363</v>
       </c>
       <c r="B85" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>136944379</v>
       </c>
       <c r="B86" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>136944385</v>
       </c>
       <c r="B87" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>136944275</v>
       </c>
       <c r="B88" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>136944280</v>
       </c>
       <c r="B89" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>136944288</v>
       </c>
       <c r="B90" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>136944290</v>
       </c>
       <c r="B91" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>136944297</v>
       </c>
       <c r="B92" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>136944301</v>
       </c>
       <c r="B93" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>136944305</v>
       </c>
       <c r="B94" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>136944307</v>
       </c>
       <c r="B95" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>136944310</v>
       </c>
       <c r="B96" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>136944311</v>
       </c>
       <c r="B97" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>136944315</v>
       </c>
       <c r="B98" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>136944316</v>
       </c>
       <c r="B99" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>136944330</v>
       </c>
       <c r="B100" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>136944331</v>
       </c>
       <c r="B101" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>136944333</v>
       </c>
       <c r="B102" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>136944347</v>
       </c>
       <c r="B103" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>136944349</v>
       </c>
       <c r="B104" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>136944359</v>
       </c>
       <c r="B105" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>136944361</v>
       </c>
       <c r="B106" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         <v>136944362</v>
       </c>
       <c r="B107" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>136944366</v>
       </c>
       <c r="B108" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>136944370</v>
       </c>
       <c r="B109" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>136944372</v>
       </c>
       <c r="B110" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>136944381</v>
       </c>
       <c r="B111" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>136944384</v>
       </c>
       <c r="B112" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>136944389</v>
       </c>
       <c r="B113" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>136944391</v>
       </c>
       <c r="B114" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>136944394</v>
       </c>
       <c r="B115" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>136949419</v>
       </c>
       <c r="B116" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>136949421</v>
       </c>
       <c r="B117" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>136949424</v>
       </c>
       <c r="B118" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>136949438</v>
       </c>
       <c r="B119" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>136949442</v>
       </c>
       <c r="B120" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>136949443</v>
       </c>
       <c r="B121" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>136949444</v>
       </c>
       <c r="B122" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>136949449</v>
       </c>
       <c r="B123" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>136949450</v>
       </c>
       <c r="B124" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>136949451</v>
       </c>
       <c r="B125" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>136949452</v>
       </c>
       <c r="B126" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>136949465</v>
       </c>
       <c r="B127" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14729,7 +14729,7 @@
         <v>136949467</v>
       </c>
       <c r="B128" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14841,7 +14841,7 @@
         <v>136949468</v>
       </c>
       <c r="B129" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>136949470</v>
       </c>
       <c r="B130" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>136949471</v>
       </c>
       <c r="B131" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>136949476</v>
       </c>
       <c r="B132" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>136949484</v>
       </c>
       <c r="B133" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15615,7 +15615,7 @@
         <v>136949426</v>
       </c>
       <c r="B136" t="n">
-        <v>78536</v>
+        <v>78539</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>136949430</v>
       </c>
       <c r="B137" t="n">
-        <v>78536</v>
+        <v>78539</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15839,7 +15839,7 @@
         <v>136949457</v>
       </c>
       <c r="B138" t="n">
-        <v>78536</v>
+        <v>78539</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>136949459</v>
       </c>
       <c r="B139" t="n">
-        <v>78536</v>
+        <v>78539</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>136949460</v>
       </c>
       <c r="B140" t="n">
-        <v>78536</v>
+        <v>78539</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>136944386</v>
       </c>
       <c r="B141" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>136944299</v>
       </c>
       <c r="B142" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>136944334</v>
       </c>
       <c r="B143" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>136944336</v>
       </c>
       <c r="B144" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>136944376</v>
       </c>
       <c r="B145" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>136949455</v>
       </c>
       <c r="B146" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>136944309</v>
       </c>
       <c r="B147" t="n">
-        <v>98303</v>
+        <v>98306</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>136944303</v>
       </c>
       <c r="B148" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>136944314</v>
       </c>
       <c r="B149" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>136944355</v>
       </c>
       <c r="B150" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>136944373</v>
       </c>
       <c r="B151" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>136944378</v>
       </c>
       <c r="B152" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>136944387</v>
       </c>
       <c r="B153" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>136944392</v>
       </c>
       <c r="B154" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17755,7 +17755,7 @@
         <v>136944281</v>
       </c>
       <c r="B155" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>136944302</v>
       </c>
       <c r="B156" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17979,7 +17979,7 @@
         <v>136944317</v>
       </c>
       <c r="B157" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>136944328</v>
       </c>
       <c r="B158" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18203,7 +18203,7 @@
         <v>136944337</v>
       </c>
       <c r="B159" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18315,7 +18315,7 @@
         <v>136944339</v>
       </c>
       <c r="B160" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>136944345</v>
       </c>
       <c r="B161" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>136944350</v>
       </c>
       <c r="B162" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>136944351</v>
       </c>
       <c r="B163" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>136944368</v>
       </c>
       <c r="B164" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>136944375</v>
       </c>
       <c r="B165" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>136944377</v>
       </c>
       <c r="B166" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>136944388</v>
       </c>
       <c r="B167" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>136949420</v>
       </c>
       <c r="B168" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>136949425</v>
       </c>
       <c r="B169" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>136949428</v>
       </c>
       <c r="B170" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>136949432</v>
       </c>
       <c r="B171" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>136949437</v>
       </c>
       <c r="B172" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>136949439</v>
       </c>
       <c r="B173" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>136949448</v>
       </c>
       <c r="B174" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>136949456</v>
       </c>
       <c r="B175" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>136949461</v>
       </c>
       <c r="B176" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>136949462</v>
       </c>
       <c r="B177" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>136949464</v>
       </c>
       <c r="B178" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20448,7 +20448,7 @@
         <v>136949466</v>
       </c>
       <c r="B179" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>136949469</v>
       </c>
       <c r="B180" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>136949474</v>
       </c>
       <c r="B181" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20784,7 +20784,7 @@
         <v>136949478</v>
       </c>
       <c r="B182" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>136949479</v>
       </c>
       <c r="B183" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>136949481</v>
       </c>
       <c r="B184" t="n">
-        <v>80126</v>
+        <v>80129</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>136949454</v>
       </c>
       <c r="B185" t="n">
-        <v>93517</v>
+        <v>93520</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
         <v>136949446</v>
       </c>
       <c r="B186" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>136949417</v>
       </c>
       <c r="B187" t="n">
-        <v>92608</v>
+        <v>92611</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>136944329</v>
       </c>
       <c r="B188" t="n">
-        <v>80430</v>
+        <v>80433</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
